--- a/tables/Flexible CUE/Local_perf_matrix_protection_False_vo_False_CUE_False.xlsx
+++ b/tables/Flexible CUE/Local_perf_matrix_protection_False_vo_False_CUE_False.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -668,10 +668,10 @@
         <v>0.01736455621136393</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4756359890550633</v>
+        <v>0.4820009970627345</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5490436758326586</v>
+        <v>0.5552417873022963</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -680,16 +680,16 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.403789484409526</v>
+        <v>4.465606698018054</v>
       </c>
       <c r="P2" t="n">
-        <v>4.392176170994017</v>
+        <v>4.439419994930735</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9940645303415307</v>
+        <v>0.9944747925766798</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00473577457943506</v>
+        <v>0.004569174776725734</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
@@ -699,38 +699,38 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.9947573973329442</v>
+        <v>0.9962385148023404</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.005250799926021826</v>
+        <v>0.00444766098947113</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.9589577844831737</v>
+        <v>0.9602885112983912</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.001333005040479703</v>
+        <v>0.001311216716686438</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>0.9984833501034159</v>
+        <v>0.9988116672678174</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.001643187205128637</v>
+        <v>0.001454498924824368</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>0.9600410586855772</v>
+        <v>0.9593854736932543</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.008506011571381651</v>
+        <v>0.008575504490409844</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>0.9056770412831564</v>
+        <v>0.9066936900173973</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0009242035391215513</v>
+        <v>0.0009192093366300093</v>
       </c>
       <c r="AN2" t="inlineStr"/>
     </row>
@@ -772,10 +772,10 @@
         <v>0.02342462405894816</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3970292459420693</v>
+        <v>0.4085894186420144</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5228844077977931</v>
+        <v>0.5338988315833292</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -784,16 +784,16 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.313657841931784</v>
+        <v>4.378970833950168</v>
       </c>
       <c r="P3" t="n">
-        <v>4.320967115517672</v>
+        <v>4.397004243933332</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.991188783496306</v>
+        <v>0.9912810293563251</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005708049170149822</v>
+        <v>0.005678091372530199</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -803,38 +803,38 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9922188406125086</v>
+        <v>0.9924031317098851</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00566825914738828</v>
+        <v>0.005600732625962754</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>0.3904234902868839</v>
+        <v>0.3878782706913023</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.00191186800616118</v>
+        <v>0.001915855245598459</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>0.9829133920388204</v>
+        <v>0.9835676470597937</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.006339790271251473</v>
+        <v>0.00621722866551922</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0.8826167491685881</v>
+        <v>0.8813375979691237</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.008309082610915531</v>
+        <v>0.008354232894866861</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>0.5045124459535448</v>
+        <v>0.5077790291095217</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.002872061235224264</v>
+        <v>0.002862578312022976</v>
       </c>
       <c r="AN3" t="inlineStr"/>
     </row>
@@ -876,10 +876,10 @@
         <v>0.001786449637055907</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5305184715213832</v>
+        <v>0.5232701740216598</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5583256390383116</v>
+        <v>0.5629139573148427</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.446044591924739</v>
+        <v>4.449533919724023</v>
       </c>
       <c r="P4" t="n">
-        <v>4.431275326359563</v>
+        <v>4.468232409487467</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9373349392029749</v>
+        <v>0.9506522977372028</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01637558418473189</v>
+        <v>0.01453173726654724</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -907,38 +907,38 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0.9252218389691323</v>
+        <v>0.9634769067417481</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0240782539589011</v>
+        <v>0.01682756886500787</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.8109986128343527</v>
+        <v>0.8881326429492018</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.005410538681520366</v>
+        <v>0.004162552262481068</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>0.4196026523983681</v>
+        <v>0.3953107692851815</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02479534225471426</v>
+        <v>0.02530891427614309</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0.981111033715438</v>
+        <v>0.9742154488976996</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.005700814913816499</v>
+        <v>0.00666058895579237</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>0.8120865605025451</v>
+        <v>0.7724473162864484</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.002196735462064656</v>
+        <v>0.002417351591745542</v>
       </c>
       <c r="AN4" t="inlineStr"/>
     </row>
@@ -980,10 +980,10 @@
         <v>0.03029424940398749</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4066877904640895</v>
+        <v>0.4069734038792392</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5405471563127944</v>
+        <v>0.5405343569984278</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -992,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.338269228295625</v>
+        <v>4.328675728015952</v>
       </c>
       <c r="P5" t="n">
-        <v>4.406771049779584</v>
+        <v>4.405143033925619</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9953647537120632</v>
+        <v>0.9953678993801566</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004029713286530362</v>
+        <v>0.004028345690172988</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1011,38 +1011,38 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0.9904770347140393</v>
+        <v>0.990483689694984</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.006989622696175108</v>
+        <v>0.006987179973030806</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.9990484607641259</v>
+        <v>0.9989863611164577</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0001900940255023106</v>
+        <v>0.0001961989813094021</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0.9982521227026747</v>
+        <v>0.9982509438660022</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.001943433793635109</v>
+        <v>0.001944089046974934</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>0.9793895781976413</v>
+        <v>0.9794091029029719</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.004773279675559104</v>
+        <v>0.004771018223504815</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>0.9843586252634147</v>
+        <v>0.9843504167260139</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0005831235738626227</v>
+        <v>0.00058327656437382</v>
       </c>
       <c r="AN5" t="inlineStr"/>
     </row>
@@ -1084,10 +1084,10 @@
         <v>0.01850467691463906</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4654721783172479</v>
+        <v>0.4592879234335376</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5550656209349576</v>
+        <v>0.5472917331264102</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1096,16 +1096,16 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.423356086505447</v>
+        <v>4.385019187083561</v>
       </c>
       <c r="P6" t="n">
-        <v>4.478379873202567</v>
+        <v>4.422800524664928</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9787999715256915</v>
+        <v>0.9788443631625323</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008801943971214239</v>
+        <v>0.008792723760540879</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1115,38 +1115,38 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>0.9765205827608662</v>
+        <v>0.9774437513737219</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.008838669399886709</v>
+        <v>0.008663166666407275</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>0.6693563966009922</v>
+        <v>0.7014166865362259</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.00153578998363964</v>
+        <v>0.001459434252392132</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>0.9941031566352456</v>
+        <v>0.9943083932971585</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.003149584660279576</v>
+        <v>0.003094289415119421</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0.7441165992507954</v>
+        <v>0.7414976022624304</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0164337243994759</v>
+        <v>0.01651761085917213</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>0.664188400033743</v>
+        <v>0.6555228832738873</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.00136552454802236</v>
+        <v>0.001383030805378332</v>
       </c>
       <c r="AN6" t="inlineStr"/>
     </row>
@@ -1188,10 +1188,10 @@
         <v>0.01739226579276497</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3885161499124838</v>
+        <v>0.3951965360399166</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5246539770844061</v>
+        <v>0.5363504762467854</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1200,16 +1200,16 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.322490428799298</v>
+        <v>4.421262405329895</v>
       </c>
       <c r="P7" t="n">
-        <v>4.307136249181392</v>
+        <v>4.403178102079354</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9884376205197111</v>
+        <v>0.9889147946947516</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006533328348466836</v>
+        <v>0.006397094205014504</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1219,38 +1219,38 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0.9919973802304445</v>
+        <v>0.9936297453898858</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00678730752298688</v>
+        <v>0.00605563695977519</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>0.6895980702536357</v>
+        <v>0.7254342038383648</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.002403638547522631</v>
+        <v>0.00226063356283661</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>0.9157372137547973</v>
+        <v>0.9148038736101707</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01157212836402355</v>
+        <v>0.01163604144036334</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>0.9999785954894981</v>
+        <v>0.9997999877120718</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0001218305416097206</v>
+        <v>0.0003724190291040825</v>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>0.4494050185176517</v>
+        <v>0.4489140084527502</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.003917343100127407</v>
+        <v>0.003919089416676367</v>
       </c>
       <c r="AN7" t="inlineStr"/>
     </row>
@@ -1292,10 +1292,10 @@
         <v>0.02806021357785015</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2616922581078026</v>
+        <v>0.268136507449542</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4950874267613353</v>
+        <v>0.5105187857826707</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1304,16 +1304,16 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.395443563473687</v>
+        <v>4.51057323281028</v>
       </c>
       <c r="P8" t="n">
-        <v>4.301777706144647</v>
+        <v>4.426334150274576</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9972528081254872</v>
+        <v>0.9975099783380402</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0028236598010953</v>
+        <v>0.002688248654129973</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1323,38 +1323,38 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.9973239184972615</v>
+        <v>0.9976797010488034</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.00345187691499799</v>
+        <v>0.003214234847810291</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0.9989182822778693</v>
+        <v>0.9990352008491494</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0002158808252773738</v>
+        <v>0.0002038804358955573</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>0.9918185667333458</v>
+        <v>0.9922035497969649</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.004478919178271348</v>
+        <v>0.00437227011269687</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>0.9971066782766667</v>
+        <v>0.9976364609288585</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.002277615125034232</v>
+        <v>0.002058559229929922</v>
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>0.9990394853572281</v>
+        <v>0.9991695496174474</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0001132116783639595</v>
+        <v>0.0001052679289410292</v>
       </c>
       <c r="AN8" t="inlineStr"/>
     </row>
@@ -1396,10 +1396,10 @@
         <v>0.03857825619785213</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3418105817087478</v>
+        <v>0.3433990727769944</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5277795257201897</v>
+        <v>0.5299311480446058</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1408,16 +1408,16 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.324191261447337</v>
+        <v>4.328025721001465</v>
       </c>
       <c r="P9" t="n">
-        <v>4.388996960522283</v>
+        <v>4.403087255273483</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9948669654247698</v>
+        <v>0.9948676406085433</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003874795273714183</v>
+        <v>0.003874540425934272</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1427,38 +1427,38 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>0.9978942651944641</v>
+        <v>0.9979411002973234</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00331219775419792</v>
+        <v>0.003275156189782787</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>0.9851566876164843</v>
+        <v>0.9848790867840327</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0006977393336266369</v>
+        <v>0.0007042336985623501</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>0.999618964008298</v>
+        <v>0.9996126815556319</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0007898616410896421</v>
+        <v>0.0007963465678934915</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0.9597628539093975</v>
+        <v>0.9596121762703047</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.007568595419988397</v>
+        <v>0.007582753387835984</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>0.9761329050172814</v>
+        <v>0.9760244387394468</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0009288597687569269</v>
+        <v>0.0009309680218611799</v>
       </c>
       <c r="AN9" t="inlineStr"/>
     </row>
@@ -1500,10 +1500,10 @@
         <v>0.033842442806071</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4075526360986579</v>
+        <v>0.4233368867748208</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5147117481381498</v>
+        <v>0.5368853434172393</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1512,16 +1512,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.165105484036478</v>
+        <v>4.304645472857671</v>
       </c>
       <c r="P10" t="n">
-        <v>4.16403148361174</v>
+        <v>4.33060537101248</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9892747809356115</v>
+        <v>0.9895904479407066</v>
       </c>
       <c r="R10" t="n">
-        <v>0.006578598682034129</v>
+        <v>0.006481064277497743</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1531,38 +1531,38 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>0.9939424629305277</v>
+        <v>0.9945301041090884</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.006884289527405164</v>
+        <v>0.006541850526688699</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.9757179241056461</v>
+        <v>0.9714908552012521</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.001302467473257725</v>
+        <v>0.001411289385638165</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>0.9142334588820622</v>
+        <v>0.9149649237569403</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01197478790995848</v>
+        <v>0.01192361473454799</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>0.9839425892840368</v>
+        <v>0.984540880661173</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.002004874046377433</v>
+        <v>0.00196716917621053</v>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>0.8395639532932484</v>
+        <v>0.8441116167086151</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.002454457336457441</v>
+        <v>0.002419420677825814</v>
       </c>
       <c r="AN10" t="inlineStr"/>
     </row>
@@ -1604,10 +1604,10 @@
         <v>0.02959337905881725</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1963834722000099</v>
+        <v>0.2019906136872595</v>
       </c>
       <c r="L11" t="n">
-        <v>0.480692308902165</v>
+        <v>0.488964981036407</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.094730808965064</v>
+        <v>4.107405143193574</v>
       </c>
       <c r="P11" t="n">
-        <v>4.249326335027039</v>
+        <v>4.301992946457993</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9961540057127866</v>
+        <v>0.9961012423631244</v>
       </c>
       <c r="R11" t="n">
-        <v>0.004613663009162127</v>
+        <v>0.004645202717819015</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
@@ -1635,38 +1635,38 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>0.9944303866516178</v>
+        <v>0.9943218360160239</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.009330889858988346</v>
+        <v>0.009421379655970605</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>0.9828214655028721</v>
+        <v>0.9842165642901131</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0009231871618710268</v>
+        <v>0.0008849066800338916</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>0.9742468776157773</v>
+        <v>0.9747907639518012</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.002844682533187925</v>
+        <v>0.00281448347248342</v>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>0.9736344054731347</v>
+        <v>0.9744648824350942</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.001824617583900501</v>
+        <v>0.001795651291816801</v>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>0.9844540743009256</v>
+        <v>0.9851343996153678</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0005282042502167871</v>
+        <v>0.000516517243422968</v>
       </c>
       <c r="AN11" t="inlineStr"/>
     </row>
@@ -1708,10 +1708,10 @@
         <v>0.0207241649964606</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1717706053199348</v>
+        <v>0.1800254501765517</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4194858451308572</v>
+        <v>0.4443168908743156</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1720,16 +1720,16 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.059116436759205</v>
+        <v>4.004770333347373</v>
       </c>
       <c r="P12" t="n">
-        <v>4.075522114855528</v>
+        <v>4.237473647481432</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9420473424037137</v>
+        <v>0.9410773032914407</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02619986097058493</v>
+        <v>0.02641822385660735</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -1739,38 +1739,38 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>0.6737650947665299</v>
+        <v>0.6683672584493268</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.05645990142382507</v>
+        <v>0.05692507389575106</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>0.9107327487385337</v>
+        <v>0.9027272373207247</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0007016445512507272</v>
+        <v>0.0007324309726465548</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>0.9976140570362998</v>
+        <v>0.9970237826874856</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.001847028409162773</v>
+        <v>0.002062889027689814</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>0.3769504101286306</v>
+        <v>0.380087920686467</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.003429384615403997</v>
+        <v>0.003420738987025546</v>
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>0.9677909090357812</v>
+        <v>0.9527713059643164</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0003630488585611482</v>
+        <v>0.0004396213848865292</v>
       </c>
       <c r="AN12" t="inlineStr"/>
     </row>
@@ -1812,10 +1812,10 @@
         <v>0.05578662037324268</v>
       </c>
       <c r="K13" t="n">
-        <v>0.266420268217613</v>
+        <v>0.2835460062602018</v>
       </c>
       <c r="L13" t="n">
-        <v>0.448172640326343</v>
+        <v>0.4773095883176129</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.316000860305166</v>
+        <v>4.337432442552224</v>
       </c>
       <c r="P13" t="n">
-        <v>4.286953390358095</v>
+        <v>4.486751702679427</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9974679524310623</v>
+        <v>0.997430907495605</v>
       </c>
       <c r="R13" t="n">
-        <v>0.002879576735302887</v>
+        <v>0.002900564965026711</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
@@ -1843,38 +1843,38 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>0.7855788489466251</v>
+        <v>0.7892126951811221</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.00365085490224296</v>
+        <v>0.003619786756878538</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>0.9217651376648219</v>
+        <v>0.9226657016107024</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0002142057872175332</v>
+        <v>0.0002129693540070737</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>0.5725358180136946</v>
+        <v>0.5703327598775618</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.004675324049110632</v>
+        <v>0.004687356371582459</v>
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>0.9985575274304497</v>
+        <v>0.9980023906434857</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.001534396708790731</v>
+        <v>0.001805673225688144</v>
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>0.9624143205485319</v>
+        <v>0.9642173223016289</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.001967779716289186</v>
+        <v>0.001920002062108499</v>
       </c>
       <c r="AN13" t="inlineStr"/>
     </row>
@@ -1916,10 +1916,10 @@
         <v>0.008819171744597891</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3496678499507883</v>
+        <v>0.3546715346376434</v>
       </c>
       <c r="L14" t="n">
-        <v>0.504321828548789</v>
+        <v>0.5125020839216102</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1928,16 +1928,16 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.329492817556477</v>
+        <v>4.399848195776872</v>
       </c>
       <c r="P14" t="n">
-        <v>4.327954381802639</v>
+        <v>4.399284891722037</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9807738565242767</v>
+        <v>0.9808980916435969</v>
       </c>
       <c r="R14" t="n">
-        <v>0.008257360785732889</v>
+        <v>0.008230638921544527</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
@@ -1947,38 +1947,38 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>0.9574544294347543</v>
+        <v>0.9586695052028485</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01025558879290598</v>
+        <v>0.01010808127544982</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>-0.03075427838247347</v>
+        <v>-0.01755876794622058</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.004979023311897616</v>
+        <v>0.004947050423578544</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>0.9945276981482659</v>
+        <v>0.9947811780839491</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.003197083100958669</v>
+        <v>0.003122159897654537</v>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>0.6121422760697572</v>
+        <v>0.6090519836469908</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01407312236564008</v>
+        <v>0.01412907558811348</v>
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>0.312901959053258</v>
+        <v>0.3093965431773571</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.001636504697971622</v>
+        <v>0.001640673922064961</v>
       </c>
       <c r="AN14" t="inlineStr"/>
     </row>
@@ -2020,10 +2020,10 @@
         <v>0.02024626170970604</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4100970253309362</v>
+        <v>0.4107507024762867</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5317445425360625</v>
+        <v>0.5344814196982085</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2032,16 +2032,16 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.259694900513283</v>
+        <v>4.081381386375272</v>
       </c>
       <c r="P15" t="n">
-        <v>4.337698803534247</v>
+        <v>4.337686579085906</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9801372438295334</v>
+        <v>0.9802340964444202</v>
       </c>
       <c r="R15" t="n">
-        <v>0.007448063786402129</v>
+        <v>0.007429882876421959</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
@@ -2051,38 +2051,38 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>0.9522883377363741</v>
+        <v>0.9527527489513464</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01075566997519105</v>
+        <v>0.01070319571484254</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>-1.615747786499282</v>
+        <v>-1.593308484446893</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.004232118518114543</v>
+        <v>0.00421392671622727</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
-        <v>0.9249217354456707</v>
+        <v>0.9252657222484987</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.01003322765896843</v>
+        <v>0.01001021660364923</v>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>0.8034733381829117</v>
+        <v>0.7996522487895394</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.004961463224548253</v>
+        <v>0.005009464162135962</v>
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>0.9999984199616706</v>
+        <v>0.9999999915323877</v>
       </c>
       <c r="AM15" t="n">
-        <v>4.651500966013994e-06</v>
+        <v>3.405177741922873e-07</v>
       </c>
       <c r="AN15" t="inlineStr"/>
     </row>
@@ -2124,10 +2124,10 @@
         <v>0.01569855494294647</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5751444245764759</v>
+        <v>0.5547407510209782</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5874316999305738</v>
+        <v>0.5733753977865961</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.551455588325581</v>
+        <v>4.399547914881412</v>
       </c>
       <c r="P16" t="n">
-        <v>4.642881917668832</v>
+        <v>4.53828267416197</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.975122638547116</v>
+        <v>0.9757558264078261</v>
       </c>
       <c r="R16" t="n">
-        <v>0.009593223199481242</v>
+        <v>0.009470351170750822</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
@@ -2155,31 +2155,31 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>0.9948607139476633</v>
+        <v>0.9946929737023286</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.005284643225081933</v>
+        <v>0.005370193034839947</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>0.957976977481104</v>
+        <v>0.9590837394407519</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.004225098766462982</v>
+        <v>0.004169089230149025</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="n">
-        <v>0.9105516800513709</v>
+        <v>0.909418027163619</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.003591081248007135</v>
+        <v>0.003613765977076533</v>
       </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
-        <v>0.8343470396335655</v>
+        <v>0.8395852168630731</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01844238572074455</v>
+        <v>0.01814845648655414</v>
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
@@ -2226,10 +2226,10 @@
         <v>0.07189096045701066</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2566081945578824</v>
+        <v>0.2331461754905137</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4358028635737645</v>
+        <v>0.4062482878535555</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2238,16 +2238,16 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.075120312358837</v>
+        <v>3.94020970433473</v>
       </c>
       <c r="P17" t="n">
-        <v>4.201159834944092</v>
+        <v>4.112155750684704</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9945086657990576</v>
+        <v>0.9947024167975608</v>
       </c>
       <c r="R17" t="n">
-        <v>0.003439822090143288</v>
+        <v>0.003378593456150539</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
@@ -2257,38 +2257,38 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>0.9868448114228787</v>
+        <v>0.9868785875878128</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.005770067011625659</v>
+        <v>0.005762654879482022</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>0.632695719345076</v>
+        <v>0.5890808723036661</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.001874388220621993</v>
+        <v>0.001982552652961361</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="n">
-        <v>0.9963768425093209</v>
+        <v>0.9963180462165</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.00162786853292715</v>
+        <v>0.001641023833260421</v>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>0.2633000771404709</v>
+        <v>0.3562145935779377</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.004417017897887211</v>
+        <v>0.004129090585578979</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>0.9979171501029633</v>
+        <v>0.9979327370821336</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0004414436183491745</v>
+        <v>0.0004397887477965621</v>
       </c>
       <c r="AN17" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>0.03009288922194302</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4170637401884277</v>
+        <v>0.4237696658272739</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5169164423657864</v>
+        <v>0.5304037895712913</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2342,16 +2342,16 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.246963527162229</v>
+        <v>4.353516083339685</v>
       </c>
       <c r="P18" t="n">
-        <v>4.249617520877014</v>
+        <v>4.363447800770301</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9859410832761872</v>
+        <v>0.9861562549579391</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006132174603827293</v>
+        <v>0.00608506720647654</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -2361,38 +2361,38 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>0.9324510197127935</v>
+        <v>0.9334778426930815</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.01334694670553846</v>
+        <v>0.01324511368013147</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>0.863396766412165</v>
+        <v>0.8537801254765851</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.001017978606723329</v>
+        <v>0.001053201247225721</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.9969328844974605</v>
+        <v>0.9967858202098074</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.001662250460597004</v>
+        <v>0.001701635273024805</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
-        <v>0.9789543028543592</v>
+        <v>0.9803187579769195</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.002440571290846839</v>
+        <v>0.002360130900288685</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.9914780010892725</v>
+        <v>0.9906989875670851</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.0003479874070004691</v>
+        <v>0.000363544771682573</v>
       </c>
       <c r="AN18" t="inlineStr"/>
     </row>
@@ -2434,10 +2434,10 @@
         <v>0.01254934055241822</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5813650193172442</v>
+        <v>0.4773272763108123</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5870200880901194</v>
+        <v>0.5574072554906462</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.597747250805167</v>
+        <v>3.822055423832857</v>
       </c>
       <c r="P19" t="n">
-        <v>4.660679894479138</v>
+        <v>4.419352489123138</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9866564686605589</v>
+        <v>0.9870541876666454</v>
       </c>
       <c r="R19" t="n">
-        <v>0.008138784310071452</v>
+        <v>0.008016573942401751</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
@@ -2465,38 +2465,38 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>0.6677637461958341</v>
+        <v>0.6848950318813257</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.008582418866351964</v>
+        <v>0.008358220443262567</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>-0.03155737580705376</v>
+        <v>0.03396216730781076</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.003025894311737358</v>
+        <v>0.002928222868760106</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="n">
-        <v>0.7281409644947996</v>
+        <v>0.730598622594996</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.01471639114316045</v>
+        <v>0.01464972061570835</v>
       </c>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
-        <v>0.761077578284524</v>
+        <v>0.7876204041426068</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.005639246537884978</v>
+        <v>0.005316784068055204</v>
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>0.9986159852179549</v>
+        <v>0.9987782087607665</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.000108767883442419</v>
+        <v>0.0001021948043493886</v>
       </c>
       <c r="AN19" t="inlineStr"/>
     </row>
@@ -2538,10 +2538,10 @@
         <v>0.005481236733903614</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4153745673784932</v>
+        <v>0.4199137651576323</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5426458353657829</v>
+        <v>0.5466925142383374</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2550,16 +2550,16 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.545581196261954</v>
+        <v>4.56912263600572</v>
       </c>
       <c r="P20" t="n">
-        <v>4.513236741473515</v>
+        <v>4.539899296940812</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.977254974263289</v>
+        <v>0.9773210307689926</v>
       </c>
       <c r="R20" t="n">
-        <v>0.00885427327955159</v>
+        <v>0.008841406562354765</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -2569,38 +2569,38 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>0.9185386151600993</v>
+        <v>0.9181453483247343</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.008314657315285096</v>
+        <v>0.008334703267227508</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>0.6550315670708148</v>
+        <v>0.6458088236668431</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.004007729478166941</v>
+        <v>0.004060949510058019</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="n">
-        <v>0.9797052908786645</v>
+        <v>0.9799087280024977</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.003801423759000695</v>
+        <v>0.003782322757568091</v>
       </c>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>0.7835639576083588</v>
+        <v>0.7848662162158422</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.01708430980205455</v>
+        <v>0.01703283557393487</v>
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>0.4736454722269201</v>
+        <v>0.474297474934772</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.0006862147594172274</v>
+        <v>0.0006857896158134105</v>
       </c>
       <c r="AN20" t="inlineStr"/>
     </row>
@@ -2642,10 +2642,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5351911822574889</v>
+        <v>0.5119505968393867</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5529481507233011</v>
+        <v>0.5214040378706312</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.25389152450637</v>
+        <v>4.080584583903153</v>
       </c>
       <c r="P21" t="n">
-        <v>4.386184553673481</v>
+        <v>4.151092398028675</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.9812066993839685</v>
+        <v>0.9807245874358685</v>
       </c>
       <c r="R21" t="n">
-        <v>0.008921589401371274</v>
+        <v>0.009035299282911835</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -2673,38 +2673,38 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>0.9305211289508095</v>
+        <v>0.9293877291295994</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.01035414305198907</v>
+        <v>0.01043825431261878</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>0.9962220958117336</v>
+        <v>0.9960348199549983</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.00202890601960426</v>
+        <v>0.00207858561234625</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="n">
-        <v>0.5085856355751177</v>
+        <v>0.5037533632643423</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.01535439601547208</v>
+        <v>0.01542970426672279</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
-        <v>0.8248039860214601</v>
+        <v>0.8043675129155022</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.007132796745293699</v>
+        <v>0.0075373420832216</v>
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>0.9861889728701395</v>
+        <v>0.9830011533144901</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.0001215847286627412</v>
+        <v>0.0001348887621392687</v>
       </c>
       <c r="AN21" t="inlineStr"/>
     </row>
@@ -2746,10 +2746,10 @@
         <v>0.02704531936448205</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3707840411234966</v>
+        <v>0.3688714801677829</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4925270552350977</v>
+        <v>0.4915905589122538</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2758,16 +2758,16 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.357078932018656</v>
+        <v>4.178478767273362</v>
       </c>
       <c r="P22" t="n">
-        <v>4.395358467068268</v>
+        <v>4.349919916238273</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9829707164827922</v>
+        <v>0.9830007146267988</v>
       </c>
       <c r="R22" t="n">
-        <v>0.006596660322171436</v>
+        <v>0.006590847547054678</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
@@ -2777,38 +2777,38 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>0.9107952980184559</v>
+        <v>0.9114904021866279</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.008805276319446928</v>
+        <v>0.008770902827479245</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>0.9247294038469767</v>
+        <v>0.9250372431819808</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.001520661200595993</v>
+        <v>0.001517548438356098</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="n">
-        <v>0.3712710954929309</v>
+        <v>0.3721034400398802</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.01094430017396473</v>
+        <v>0.01093705345332912</v>
       </c>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>0.9275747195345729</v>
+        <v>0.92563504737467</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.003853466970249362</v>
+        <v>0.003904727227574165</v>
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
-        <v>0.8261551808553537</v>
+        <v>0.8266467802751225</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.00176278798869765</v>
+        <v>0.001760293812977091</v>
       </c>
       <c r="AN22" t="inlineStr"/>
     </row>
@@ -2850,10 +2850,10 @@
         <v>0.0237900385797033</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3404821858300435</v>
+        <v>0.3463056376458854</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4858189023189348</v>
+        <v>0.4947493563760101</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2862,16 +2862,16 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.105159995358824</v>
+        <v>3.869820336646796</v>
       </c>
       <c r="P23" t="n">
-        <v>4.200444334594142</v>
+        <v>4.218788295000432</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9829506101330284</v>
+        <v>0.9830728547251535</v>
       </c>
       <c r="R23" t="n">
-        <v>0.009775589921948505</v>
+        <v>0.009740481252516593</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2881,38 +2881,38 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>0.9038569867748475</v>
+        <v>0.9045420264382695</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.02173762389625539</v>
+        <v>0.02166004282918055</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>-1.105565670259599</v>
+        <v>-1.107072089054323</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.001385700381284274</v>
+        <v>0.001386195989637312</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="n">
-        <v>0.9892532949466076</v>
+        <v>0.9895066042716104</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.001746056640316297</v>
+        <v>0.001725355880916715</v>
       </c>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="n">
-        <v>0.926165620319787</v>
+        <v>0.9241904912760229</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.0004411610641314155</v>
+        <v>0.0004470228277812744</v>
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
-        <v>0.994333223015689</v>
+        <v>0.9940474982743336</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.0003507086156098391</v>
+        <v>0.0003594414349269529</v>
       </c>
       <c r="AN23" t="inlineStr"/>
     </row>
@@ -2954,10 +2954,10 @@
         <v>0.01655830938827357</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5248228924400306</v>
+        <v>0.5381273422429782</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5346619123675868</v>
+        <v>0.5469554563350643</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2966,16 +2966,16 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.176595398310353</v>
+        <v>4.275774819085798</v>
       </c>
       <c r="P24" t="n">
-        <v>4.249943635766656</v>
+        <v>4.341554147160157</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9926767711312096</v>
+        <v>0.9926953288581162</v>
       </c>
       <c r="R24" t="n">
-        <v>0.005082038447477863</v>
+        <v>0.005075595189499516</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2985,31 +2985,31 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>0.9990711816414876</v>
+        <v>0.9989979145197011</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.002445614290197801</v>
+        <v>0.002540241183442363</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>0.9612024084671005</v>
+        <v>0.9608443827013903</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.003109934748062506</v>
+        <v>0.003124251098636244</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="n">
-        <v>0.8432798990979502</v>
+        <v>0.8446192709595116</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.009755977409476171</v>
+        <v>0.009714199361370081</v>
       </c>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
-        <v>0.9762159677482655</v>
+        <v>0.9769001235953902</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.001041959106340037</v>
+        <v>0.001026863601820317</v>
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         <v>0.05553965571423582</v>
       </c>
       <c r="K25" t="n">
-        <v>0.546176191779207</v>
+        <v>0.5494012369207484</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5474373258942006</v>
+        <v>0.5531651098141975</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3068,65 +3068,65 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.335750152080124</v>
+        <v>4.359776070804065</v>
       </c>
       <c r="P25" t="n">
-        <v>4.345145644667552</v>
+        <v>4.387811859846882</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.9827387291373857</v>
+        <v>0.9827869502360601</v>
       </c>
       <c r="R25" t="n">
-        <v>0.02178914927046165</v>
+        <v>0.02175869289332351</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>-0.3178696900896567</v>
+        <v>-0.3143661111299618</v>
       </c>
       <c r="U25" t="n">
-        <v>0.04226582086109543</v>
+        <v>0.04220960126964817</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>0.2715419016375845</v>
+        <v>0.2705704395949385</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001082974965634676</v>
+        <v>0.001083696845556093</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>0.9025866658831153</v>
+        <v>0.9037293283445984</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.01075964932178874</v>
+        <v>0.01069635760359922</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>0.516909168050367</v>
+        <v>0.5155857894256859</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.003406138054026074</v>
+        <v>0.003410800249187533</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="n">
-        <v>0.9999935732209662</v>
+        <v>0.9999642980004979</v>
       </c>
       <c r="AG25" t="n">
-        <v>4.152746277530777e-05</v>
+        <v>9.787797672631068e-05</v>
       </c>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="n">
-        <v>0.99834042675764</v>
+        <v>0.9912692940008837</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.0002544449168657389</v>
+        <v>0.000583606673247077</v>
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
-        <v>-0.06041086027544185</v>
+        <v>-0.06019105087399779</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.003409952638309039</v>
+        <v>0.003409599200541214</v>
       </c>
       <c r="AN25" t="inlineStr"/>
     </row>
@@ -3168,10 +3168,10 @@
         <v>0.05246774739927379</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5471977775578866</v>
+        <v>0.540731726273736</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5532293772499586</v>
+        <v>0.5490181805573094</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3180,65 +3180,65 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.343361074649197</v>
+        <v>4.295183238249074</v>
       </c>
       <c r="P26" t="n">
-        <v>4.388289853205311</v>
+        <v>4.35691974105193</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.979314812173351</v>
+        <v>0.9795222297738044</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02210635105936981</v>
+        <v>0.02199523776444483</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>0.2427630145943427</v>
+        <v>0.2503683661072617</v>
       </c>
       <c r="U26" t="n">
-        <v>0.04273358774231388</v>
+        <v>0.04251844761102798</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>-0.6665875550631879</v>
+        <v>-0.6471722246888199</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0009049905024329322</v>
+        <v>0.0008997036024602547</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>0.9504715364084975</v>
+        <v>0.9509637374357274</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01201517225632442</v>
+        <v>0.01195532135634414</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>-0.4571320571760833</v>
+        <v>-0.4457842790344297</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.004138979097333071</v>
+        <v>0.004122830932079933</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="n">
-        <v>0.9169771163994712</v>
+        <v>0.9173165762320066</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.003856845859956554</v>
+        <v>0.003848952943997378</v>
       </c>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="n">
-        <v>0.9916811813196229</v>
+        <v>0.9927408269512144</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.000775873208618261</v>
+        <v>0.0007247754950350273</v>
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>0.5370226430074407</v>
+        <v>0.5346525047973455</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.000942865176822287</v>
+        <v>0.0009452755193291395</v>
       </c>
       <c r="AN26" t="inlineStr"/>
     </row>
@@ -3280,10 +3280,10 @@
         <v>0.07321928484019485</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5184276146984496</v>
+        <v>0.5300735357727636</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5227981113404304</v>
+        <v>0.5351292280259271</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3292,65 +3292,65 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.128901529664978</v>
+        <v>4.215743336119488</v>
       </c>
       <c r="P27" t="n">
-        <v>4.161495752880196</v>
+        <v>4.253428618571796</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9962385935324101</v>
+        <v>0.9962122267991117</v>
       </c>
       <c r="R27" t="n">
-        <v>0.009954129110999511</v>
+        <v>0.009988956446203911</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>0.9038462785322294</v>
+        <v>0.9032455827205915</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0162781251649524</v>
+        <v>0.01632889271337542</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
-        <v>0.3568215206527713</v>
+        <v>0.3403901858307666</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0008987475938432298</v>
+        <v>0.0009101553846429754</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>0.896409747478216</v>
+        <v>0.8956302952875048</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.01364799694266148</v>
+        <v>0.01369924705925465</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>0.8036552957432164</v>
+        <v>0.7957531353606853</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.001620347645801288</v>
+        <v>0.00165263256275092</v>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="n">
-        <v>0.8796028119280882</v>
+        <v>0.8785610062006513</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.009693025851397544</v>
+        <v>0.009734872753268337</v>
       </c>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
-        <v>0.7165622915505249</v>
+        <v>0.701592386452264</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.002868232465646778</v>
+        <v>0.0029430014967645</v>
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="n">
-        <v>0.4329737498948468</v>
+        <v>0.4340804153614276</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.00490305564950791</v>
+        <v>0.00489826866437603</v>
       </c>
       <c r="AN27" t="inlineStr"/>
     </row>
@@ -3392,10 +3392,10 @@
         <v>0.02087465183044777</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4418134987247647</v>
+        <v>0.4452115703335381</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5159779027854803</v>
+        <v>0.5394700346189368</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.152089315711887</v>
+        <v>4.128552560111538</v>
       </c>
       <c r="P28" t="n">
-        <v>4.160243196873861</v>
+        <v>4.338880960548818</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9510208806427194</v>
+        <v>0.9504127269419997</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02304672083790665</v>
+        <v>0.02318936028512819</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
@@ -3425,38 +3425,38 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>0.6685155099640713</v>
+        <v>0.6641377878335885</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.04717717891790594</v>
+        <v>0.04748767786512259</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>0.9380600948045472</v>
+        <v>0.9450048563428035</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.002976612568935795</v>
+        <v>0.002804782658138229</v>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="n">
-        <v>0.5191842163919258</v>
+        <v>0.5150812060064947</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.01159137122837552</v>
+        <v>0.01164072327467621</v>
       </c>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="n">
-        <v>0.3880662286910495</v>
+        <v>0.3813307433411852</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01699860208343219</v>
+        <v>0.01709189690352015</v>
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
-        <v>0.9905742761499218</v>
+        <v>0.9905616779881961</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.0003361096783147619</v>
+        <v>0.0003363342207591197</v>
       </c>
       <c r="AN28" t="inlineStr"/>
     </row>
@@ -3498,10 +3498,10 @@
         <v>0.03864752444133265</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5137115865110338</v>
+        <v>0.5450393411938402</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5154247351720747</v>
+        <v>0.5378951225118166</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3510,16 +3510,16 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.093722495858296</v>
+        <v>4.327280143443206</v>
       </c>
       <c r="P29" t="n">
-        <v>4.106500720371598</v>
+        <v>4.274042576065238</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9365634869260727</v>
+        <v>0.9370092198966595</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01625315658438449</v>
+        <v>0.01619595499649923</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
@@ -3531,38 +3531,38 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>0.7217448756772677</v>
+        <v>0.7199198589712297</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.03437425002626893</v>
+        <v>0.03448679252226174</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>0.9306142453337927</v>
+        <v>0.9343812983619562</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.009123769463589835</v>
+        <v>0.008872642059008218</v>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="n">
-        <v>0.5427167746793323</v>
+        <v>0.6184579859230938</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.009557872598296295</v>
+        <v>0.008730513457351945</v>
       </c>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="n">
-        <v>0.9578486310945015</v>
+        <v>0.9545880790724479</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.005334488199129581</v>
+        <v>0.005536965959767819</v>
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>0.9375347331216408</v>
+        <v>0.9388067148510899</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.001491590586131032</v>
+        <v>0.001476325829841406</v>
       </c>
       <c r="AN29" t="inlineStr"/>
     </row>
@@ -3604,10 +3604,10 @@
         <v>0.0191674492264043</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4917148241362141</v>
+        <v>0.5180684702589732</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5155063900765706</v>
+        <v>0.5445554295267135</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3616,16 +3616,16 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.182807504896132</v>
+        <v>4.577350772514278</v>
       </c>
       <c r="P30" t="n">
-        <v>4.1143270705468</v>
+        <v>4.340420680421795</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9735983471239049</v>
+        <v>0.9741213341857776</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01339311034997847</v>
+        <v>0.01325979561442754</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
@@ -3637,38 +3637,38 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>0.8707567853237899</v>
+        <v>0.8721219140354467</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.02448769040814206</v>
+        <v>0.02435802173845336</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>0.9833298395648508</v>
+        <v>0.9548937407706659</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0005818382689238558</v>
+        <v>0.0009570856361806922</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="n">
-        <v>-0.06574814470136081</v>
+        <v>-0.004976003296010445</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.01396110433398448</v>
+        <v>0.01355721008320211</v>
       </c>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
-        <v>0.8774213538368757</v>
+        <v>0.8766879227666049</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.007327935181665131</v>
+        <v>0.007349825290750353</v>
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>0.5014765600333357</v>
+        <v>0.5069525364481759</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.001898908992062694</v>
+        <v>0.001888451014660394</v>
       </c>
       <c r="AN30" t="inlineStr"/>
     </row>
@@ -3710,10 +3710,10 @@
         <v>0.02030227596285282</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5492159660579294</v>
+        <v>0.5411091241769229</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5548683045678015</v>
+        <v>0.5556445995349577</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.35839592105136</v>
+        <v>4.297995521688784</v>
       </c>
       <c r="P31" t="n">
-        <v>4.400497349139041</v>
+        <v>4.406273731714898</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9845130816922074</v>
+        <v>0.9845846215736355</v>
       </c>
       <c r="R31" t="n">
-        <v>0.008127165808253836</v>
+        <v>0.008108372867425035</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -3743,38 +3743,38 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>0.9389312232340536</v>
+        <v>0.9403393012386818</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.01319917546374068</v>
+        <v>0.01304611971851409</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0.8918662357371373</v>
+        <v>0.8908991023708824</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.0080057491002262</v>
+        <v>0.008041470559999596</v>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="n">
-        <v>-0.02547675039257369</v>
+        <v>-0.04007470500952648</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.009207840512719495</v>
+        <v>0.00927314704035594</v>
       </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
-        <v>0.9733931947205273</v>
+        <v>0.9703497265043083</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.002559564919299102</v>
+        <v>0.002701992476453797</v>
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
-        <v>0.05857907364202219</v>
+        <v>0.05262509718589548</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.004078133638813569</v>
+        <v>0.004091009304045872</v>
       </c>
       <c r="AN31" t="inlineStr"/>
     </row>
@@ -3816,10 +3816,10 @@
         <v>0.02773752553385222</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5246702789488129</v>
+        <v>0.5785259936431176</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5154133601425148</v>
+        <v>0.5570048359248688</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3828,16 +3828,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.175457408489923</v>
+        <v>4.576621334530718</v>
       </c>
       <c r="P32" t="n">
-        <v>4.106415121301283</v>
+        <v>4.416392399057208</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9802556012802348</v>
+        <v>0.9813117562949464</v>
       </c>
       <c r="R32" t="n">
-        <v>0.01353056408015836</v>
+        <v>0.01316370649800837</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -3849,38 +3849,38 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>0.8420104094751262</v>
+        <v>0.8830149249119658</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.01133625921117785</v>
+        <v>0.009754853694145426</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>0.2197806636491788</v>
+        <v>0.2196324728205126</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.01753338943787072</v>
+        <v>0.01753505445950276</v>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="n">
-        <v>-0.3406033005926725</v>
+        <v>-0.2312443221242326</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.01472455336441108</v>
+        <v>0.01411120524233461</v>
       </c>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
-        <v>0.3365535540866608</v>
+        <v>0.3378479862451139</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01687695183224104</v>
+        <v>0.01686047971490034</v>
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
-        <v>0.08750968120625413</v>
+        <v>0.0827074752067728</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.004855447425927944</v>
+        <v>0.004868207156664338</v>
       </c>
       <c r="AN32" t="inlineStr"/>
     </row>
@@ -3920,10 +3920,10 @@
         <v>0.02495281852103528</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4068426477840261</v>
+        <v>0.3932497006496025</v>
       </c>
       <c r="L33" t="n">
-        <v>0.5163910330019399</v>
+        <v>0.5367600548392822</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3932,16 +3932,16 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.166252496298712</v>
+        <v>4.368367739242999</v>
       </c>
       <c r="P33" t="n">
-        <v>4.153979214333269</v>
+        <v>4.330556365681336</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.9667634505646282</v>
+        <v>0.9666686912297314</v>
       </c>
       <c r="R33" t="n">
-        <v>0.005783741400478788</v>
+        <v>0.005791980423681998</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
@@ -3951,38 +3951,38 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>0.9191075912178182</v>
+        <v>0.9182092969256205</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.01149296101430093</v>
+        <v>0.01155659836799151</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>0.5192175920991666</v>
+        <v>0.5438624804908768</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.004449747225039836</v>
+        <v>0.004334200072395147</v>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="n">
-        <v>0.932027002936532</v>
+        <v>0.9307269936887617</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.003109824082740399</v>
+        <v>0.003139421517657733</v>
       </c>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>0.7764009743946804</v>
+        <v>0.7830871901422091</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.002243712332089454</v>
+        <v>0.002209911193717272</v>
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>0.3200550944733873</v>
+        <v>0.3296852055332312</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.000815272249195542</v>
+        <v>0.0008094782797049903</v>
       </c>
       <c r="AN33" t="inlineStr"/>
     </row>
@@ -4024,10 +4024,10 @@
         <v>0.008784365836720525</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5179999681685502</v>
+        <v>0.536901696262555</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5226926153685167</v>
+        <v>0.5432389027487502</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.125711815458049</v>
+        <v>4.266640352725299</v>
       </c>
       <c r="P34" t="n">
-        <v>4.160709122843012</v>
+        <v>4.313865019699602</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.9437303344346608</v>
+        <v>0.9392370431768626</v>
       </c>
       <c r="R34" t="n">
-        <v>0.01654204816445072</v>
+        <v>0.01718982928280536</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
@@ -4057,38 +4057,38 @@
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>0.9103728914185104</v>
+        <v>0.9025777770358581</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.03583861983970351</v>
+        <v>0.03736462267539677</v>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>0.9956350035562451</v>
+        <v>0.9954666026972713</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.001562847182316779</v>
+        <v>0.001592709087179328</v>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="n">
-        <v>0.6868423332197944</v>
+        <v>0.7077091980568507</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.004308087539485898</v>
+        <v>0.004162081399060013</v>
       </c>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
-        <v>0.4910170618572209</v>
+        <v>0.5015557242603633</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.007919376951724129</v>
+        <v>0.00783696143241468</v>
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="n">
-        <v>0.2782269776724356</v>
+        <v>0.2670092201505117</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.0008258918345748553</v>
+        <v>0.0008322850727627393</v>
       </c>
       <c r="AN34" t="inlineStr"/>
     </row>
@@ -4130,10 +4130,10 @@
         <v>0.033117285160876</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5047782193068076</v>
+        <v>0.5172477546113869</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5047792694042009</v>
+        <v>0.5370322289733235</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4142,16 +4142,16 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.027064102812506</v>
+        <v>4.120101088769337</v>
       </c>
       <c r="P35" t="n">
-        <v>4.027071892554085</v>
+        <v>4.267610979150944</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9964299958071222</v>
+        <v>0.9963030324501649</v>
       </c>
       <c r="R35" t="n">
-        <v>0.005952348429042161</v>
+        <v>0.006057268172059271</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>0.9797012867392142</v>
+        <v>0.9774878171816286</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.007774611517268954</v>
+        <v>0.008187536450259427</v>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4173,24 +4173,24 @@
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="n">
-        <v>0.6407959292110588</v>
+        <v>0.6458277866106918</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.008950646875872586</v>
+        <v>0.008887733861668164</v>
       </c>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
-        <v>0.7002774476226137</v>
+        <v>0.699717325088644</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.002212388954170106</v>
+        <v>0.002214455249279027</v>
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="n">
-        <v>0.5553646995502781</v>
+        <v>0.5660210730834871</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.002264087368568243</v>
+        <v>0.002236791650735604</v>
       </c>
       <c r="AN35" t="inlineStr"/>
     </row>
@@ -4232,10 +4232,10 @@
         <v>0.02290841461070009</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5291426829145613</v>
+        <v>0.5508842687946176</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5286557860396734</v>
+        <v>0.5490979189898959</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.208803672383319</v>
+        <v>4.370823363997192</v>
       </c>
       <c r="P36" t="n">
-        <v>4.205173662037383</v>
+        <v>4.357516428485859</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9839701669244788</v>
+        <v>0.9839315696536894</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01147266173959638</v>
+        <v>0.01148646560125316</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
@@ -4265,38 +4265,38 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>0.817723976418594</v>
+        <v>0.8166610429078107</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.01855906841856205</v>
+        <v>0.01861310289764294</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>0.3705482319500039</v>
+        <v>0.3723614624476508</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.008138674206086631</v>
+        <v>0.008126943414296529</v>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="n">
-        <v>0.06420798879367828</v>
+        <v>0.06702911052602845</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.01349658276513005</v>
+        <v>0.01347622341055103</v>
       </c>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="n">
-        <v>0.7347136685789963</v>
+        <v>0.7326810460920691</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.006033980829770504</v>
+        <v>0.00605705288442605</v>
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="n">
-        <v>0.14635170221074</v>
+        <v>0.1524810339639457</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.004085770458337526</v>
+        <v>0.004071075789554511</v>
       </c>
       <c r="AN36" t="inlineStr"/>
     </row>
@@ -4338,10 +4338,10 @@
         <v>0.007462828179086988</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5448562437145308</v>
+        <v>0.5416253914309452</v>
       </c>
       <c r="L37" t="n">
-        <v>0.5498883332052865</v>
+        <v>0.5505442072965488</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4350,61 +4350,61 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.325915956550759</v>
+        <v>4.301842560539425</v>
       </c>
       <c r="P37" t="n">
-        <v>4.363403740894099</v>
+        <v>4.368288281711853</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.990296608537576</v>
+        <v>0.990418338661169</v>
       </c>
       <c r="R37" t="n">
-        <v>0.006563727542686192</v>
+        <v>0.006522426256053311</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
-        <v>-1.524683709658958</v>
+        <v>-1.532500131799742</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0006797541525909888</v>
+        <v>0.0006808055990136449</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
-        <v>0.9745784974441917</v>
+        <v>0.9759297449476745</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.007569902348256348</v>
+        <v>0.007365971176233688</v>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>-0.7418751389149945</v>
+        <v>-0.7305958191896744</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.008356455871203709</v>
+        <v>0.008329356277167882</v>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="n">
-        <v>0.9059626047732871</v>
+        <v>0.9057722359341037</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.009979341087240204</v>
+        <v>0.009989437044715525</v>
       </c>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
-        <v>0.9659062198024937</v>
+        <v>0.9607746650322766</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.001656590247050169</v>
+        <v>0.001776891264080643</v>
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="n">
-        <v>0.9998821209654625</v>
+        <v>0.9999955954615968</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.068744836987045e-05</v>
+        <v>2.065884061737462e-06</v>
       </c>
       <c r="AN37" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>0.003185097564105027</v>
       </c>
       <c r="K38" t="n">
-        <v>0.540912009343728</v>
+        <v>0.5410877791334675</v>
       </c>
       <c r="L38" t="n">
-        <v>0.5469205628049896</v>
+        <v>0.5459534785704414</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4458,61 +4458,61 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.296526671931293</v>
+        <v>4.297836464385832</v>
       </c>
       <c r="P38" t="n">
-        <v>4.341294306558273</v>
+        <v>4.334089179456488</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9428325660011811</v>
+        <v>0.9430380972433829</v>
       </c>
       <c r="R38" t="n">
-        <v>0.01341604592867179</v>
+        <v>0.0133919071904237</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
-        <v>0.2594209483904801</v>
+        <v>0.2639470867320597</v>
       </c>
       <c r="X38" t="n">
-        <v>0.001127983700122156</v>
+        <v>0.001124531513097592</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>0.7451969187800127</v>
+        <v>0.7469339915377098</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.02434632169428359</v>
+        <v>0.02426319150403365</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>-0.545267829990691</v>
+        <v>-0.5464580451682217</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.01804255156000626</v>
+        <v>0.01804949870042787</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="n">
-        <v>0.991168406693346</v>
+        <v>0.9907604013767453</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.002181442096618998</v>
+        <v>0.002231262732024745</v>
       </c>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
-        <v>-2.304964116336112</v>
+        <v>-2.316352245161167</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.006005350560149638</v>
+        <v>0.006015688175171676</v>
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="n">
-        <v>0.9999879117301999</v>
+        <v>0.9999993534681905</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.393476724578854e-06</v>
+        <v>3.222645951117273e-07</v>
       </c>
       <c r="AN38" t="inlineStr"/>
     </row>
@@ -4554,10 +4554,10 @@
         <v>0.03277409385829239</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5277031214589124</v>
+        <v>0.5532307663355256</v>
       </c>
       <c r="L39" t="n">
-        <v>0.5262642480452384</v>
+        <v>0.5491049323283788</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.198070974628081</v>
+        <v>4.388301465052076</v>
       </c>
       <c r="P39" t="n">
-        <v>4.187342706575164</v>
+        <v>4.357568293928008</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9820155687657246</v>
+        <v>0.9819945676145284</v>
       </c>
       <c r="R39" t="n">
-        <v>0.008976421545433658</v>
+        <v>0.008981661082384249</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
@@ -4585,38 +4585,38 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>0.8615733922404776</v>
+        <v>0.8614104763354866</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.01245262617987344</v>
+        <v>0.0124599518462974</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>0.2501341581817347</v>
+        <v>0.2315287535118379</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.001288321907383524</v>
+        <v>0.001304206671885018</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="n">
-        <v>-0.05102372831820112</v>
+        <v>-0.05242748113915696</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.01468426495895124</v>
+        <v>0.0146940678776024</v>
       </c>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>0.7811804882406734</v>
+        <v>0.781611202634598</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.005076142584020242</v>
+        <v>0.005071144298890516</v>
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="n">
-        <v>-0.1176510596055118</v>
+        <v>-0.1198831906614264</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.002181326609182442</v>
+        <v>0.002183503754813192</v>
       </c>
       <c r="AN39" t="inlineStr"/>
     </row>
@@ -4658,10 +4658,10 @@
         <v>0.003165060709665684</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2903270778508912</v>
+        <v>0.2863667851232302</v>
       </c>
       <c r="L40" t="n">
-        <v>0.5387599182150005</v>
+        <v>0.5256098943551707</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4670,16 +4670,16 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>4.568405641987668</v>
+        <v>4.296817286241648</v>
       </c>
       <c r="P40" t="n">
-        <v>4.620008740478608</v>
+        <v>4.505131646370524</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.993919736336724</v>
+        <v>0.9940283693395067</v>
       </c>
       <c r="R40" t="n">
-        <v>0.004683831582571979</v>
+        <v>0.004641801174720207</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
@@ -4689,38 +4689,38 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>0.9882978992494589</v>
+        <v>0.9875289690252108</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.006528202521258065</v>
+        <v>0.006739270391131856</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>0.8450246630743629</v>
+        <v>0.8553981492924094</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.0008955992662064113</v>
+        <v>0.000865106071817611</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="n">
-        <v>0.9794754300164332</v>
+        <v>0.9801740764481187</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.0035984902905137</v>
+        <v>0.003536714601192772</v>
       </c>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
-        <v>0.9789991496375281</v>
+        <v>0.9810170861862123</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.006507963847683754</v>
+        <v>0.006187399095203475</v>
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="n">
-        <v>0.9999983517515396</v>
+        <v>0.999999992126543</v>
       </c>
       <c r="AM40" t="n">
-        <v>7.8060812470376e-07</v>
+        <v>5.395161618500646e-08</v>
       </c>
       <c r="AN40" t="inlineStr"/>
     </row>
@@ -4762,10 +4762,10 @@
         <v>0.01422966781757511</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5262631340488253</v>
+        <v>0.5140482499878871</v>
       </c>
       <c r="L41" t="n">
-        <v>0.5790478064554327</v>
+        <v>0.5640757300050252</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4774,16 +4774,16 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4.586833780976132</v>
+        <v>4.40576475719459</v>
       </c>
       <c r="P41" t="n">
-        <v>4.614769198979042</v>
+        <v>4.493386417444865</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.9944793884758271</v>
+        <v>0.9944727431335436</v>
       </c>
       <c r="R41" t="n">
-        <v>0.005758489774894905</v>
+        <v>0.005761954574627198</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
@@ -4793,38 +4793,38 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>0.8780583777663737</v>
+        <v>0.8783828200649977</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.01016911611188049</v>
+        <v>0.01015557894211137</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>0.7454115425051362</v>
+        <v>0.7420484408028993</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.001258321805170328</v>
+        <v>0.001266605723691094</v>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="n">
-        <v>0.9833840055855889</v>
+        <v>0.9831984807204074</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.003456241095700448</v>
+        <v>0.0034754827582404</v>
       </c>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="n">
-        <v>0.9549463169325469</v>
+        <v>0.9545695098592104</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.006843146084046806</v>
+        <v>0.006871702870929159</v>
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>0.8089633836899086</v>
+        <v>0.8156581769174286</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.001425649092995011</v>
+        <v>0.001400445694209945</v>
       </c>
       <c r="AN41" t="inlineStr"/>
     </row>
@@ -4866,10 +4866,10 @@
         <v>0.01067227249555984</v>
       </c>
       <c r="K42" t="n">
-        <v>0.2810853425074218</v>
+        <v>0.3386526589655819</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5469095230126961</v>
+        <v>0.5329537165975325</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -4878,16 +4878,16 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>4.524889107463629</v>
+        <v>4.440464077287422</v>
       </c>
       <c r="P42" t="n">
-        <v>4.609347422586908</v>
+        <v>4.468409147149607</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.9729698292483695</v>
+        <v>0.9718770256853601</v>
       </c>
       <c r="R42" t="n">
-        <v>0.0108873889346811</v>
+        <v>0.01110529163991968</v>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
@@ -4897,31 +4897,31 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>0.9097627823137071</v>
+        <v>0.9054343665896841</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.01648485239192508</v>
+        <v>0.01687558678137446</v>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>0.9997813318086378</v>
+        <v>0.9996966553002804</v>
       </c>
       <c r="AD42" t="n">
-        <v>7.903568201671705e-05</v>
+        <v>9.308905131191456e-05</v>
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="n">
-        <v>0.718872654401269</v>
+        <v>0.7120679758439483</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.01547457119834159</v>
+        <v>0.01566073218317996</v>
       </c>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
-        <v>0.9974551575080723</v>
+        <v>0.9954341101501322</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.001560044359392336</v>
+        <v>0.002089629105712255</v>
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
@@ -4968,10 +4968,10 @@
         <v>0.0240059836138475</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2594834876018522</v>
+        <v>0.260825416693064</v>
       </c>
       <c r="L43" t="n">
-        <v>0.4892820864730077</v>
+        <v>0.4993475355383537</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -4980,16 +4980,16 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>4.103051778684014</v>
+        <v>3.977480086284531</v>
       </c>
       <c r="P43" t="n">
-        <v>4.234750006418406</v>
+        <v>4.301903453506331</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.96705395574965</v>
+        <v>0.9679398970104771</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01109054210110046</v>
+        <v>0.01094040987057284</v>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
@@ -4999,38 +4999,38 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>0.9483829465159948</v>
+        <v>0.9502196689188239</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.01953892772458244</v>
+        <v>0.01918814589791783</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>0.6201971648777247</v>
+        <v>0.6176573760793274</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.002910465399416724</v>
+        <v>0.002920180507010408</v>
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="n">
-        <v>0.7820570468622405</v>
+        <v>0.7849284998005326</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.01479452802704665</v>
+        <v>0.01469674407288626</v>
       </c>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="n">
-        <v>0.8162053210566632</v>
+        <v>0.8198087942877239</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.002403259224441941</v>
+        <v>0.002379583487650323</v>
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>0.9932628002949776</v>
+        <v>0.994064484900142</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.0003261910035801619</v>
+        <v>0.0003061691831618108</v>
       </c>
       <c r="AN43" t="inlineStr"/>
     </row>
@@ -5072,10 +5072,10 @@
         <v>0.02192364384915694</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5457327389361865</v>
+        <v>0.5286870787682787</v>
       </c>
       <c r="L44" t="n">
-        <v>0.5768348026250045</v>
+        <v>0.5600074997541628</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5084,16 +5084,16 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.33244628845221</v>
+        <v>4.205406969984286</v>
       </c>
       <c r="P44" t="n">
-        <v>4.564016717324882</v>
+        <v>4.438748696822004</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.9535533506493198</v>
+        <v>0.95302310452405</v>
       </c>
       <c r="R44" t="n">
-        <v>0.007340553793944856</v>
+        <v>0.007382335648650627</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
@@ -5103,38 +5103,38 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>0.9564774780883339</v>
+        <v>0.9556761552670739</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.009355203020702363</v>
+        <v>0.009440932723754175</v>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>0.8092811316243541</v>
+        <v>0.8126900677434666</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.004843377820810989</v>
+        <v>0.004799897038070332</v>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="n">
-        <v>0.9019754780492765</v>
+        <v>0.8998961627984626</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.01095041690744184</v>
+        <v>0.01106594864011849</v>
       </c>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="n">
-        <v>0.9218653904937562</v>
+        <v>0.9233222961529891</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.006072489103649121</v>
+        <v>0.006015608589755103</v>
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>0.6313700271707015</v>
+        <v>0.6252075221395293</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.001285987315094204</v>
+        <v>0.00129669189296649</v>
       </c>
       <c r="AN44" t="inlineStr"/>
     </row>
@@ -5176,10 +5176,10 @@
         <v>0.02487778863857871</v>
       </c>
       <c r="K45" t="n">
-        <v>0.534591615256344</v>
+        <v>0.5400703130547023</v>
       </c>
       <c r="L45" t="n">
-        <v>0.5477541400153174</v>
+        <v>0.5560424067601982</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5188,16 +5188,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.249422615389083</v>
+        <v>4.290254436529441</v>
       </c>
       <c r="P45" t="n">
-        <v>4.347504656731103</v>
+        <v>4.409240661505166</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.9689141855888582</v>
+        <v>0.9689003003205184</v>
       </c>
       <c r="R45" t="n">
-        <v>0.008610754754599804</v>
+        <v>0.0086126776460247</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
@@ -5207,38 +5207,38 @@
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>0.9762036707707286</v>
+        <v>0.9761786969789389</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.01319421015637796</v>
+        <v>0.01320113187623589</v>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>0.9228004106100011</v>
+        <v>0.9228403531276196</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.00728698792543135</v>
+        <v>0.007285102563709765</v>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="n">
-        <v>0.8734375046375369</v>
+        <v>0.8734203387177651</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.008454148991649896</v>
+        <v>0.008454722298625272</v>
       </c>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="n">
-        <v>0.9225919625245063</v>
+        <v>0.9225908945229462</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.008466910283201587</v>
+        <v>0.008466968692137505</v>
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="n">
-        <v>0.9804512895666484</v>
+        <v>0.9804677110250209</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.0006139280303638275</v>
+        <v>0.0006136701179116748</v>
       </c>
       <c r="AN45" t="inlineStr"/>
     </row>
@@ -5280,10 +5280,10 @@
         <v>0.04354702384994095</v>
       </c>
       <c r="K46" t="n">
-        <v>0.5306468072560714</v>
+        <v>0.4692195827002179</v>
       </c>
       <c r="L46" t="n">
-        <v>0.5746731523761059</v>
+        <v>0.56319358864237</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5292,16 +5292,16 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4.220017038479095</v>
+        <v>3.761450846446995</v>
       </c>
       <c r="P46" t="n">
-        <v>4.547935087036819</v>
+        <v>4.462444238329396</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9677847421026257</v>
+        <v>0.9695306941104365</v>
       </c>
       <c r="R46" t="n">
-        <v>0.008557699023027636</v>
+        <v>0.008322570492744614</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
@@ -5311,38 +5311,38 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>0.9824825443662556</v>
+        <v>0.9840113589995604</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.01020584497525098</v>
+        <v>0.009750328092818736</v>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>0.9204160001375665</v>
+        <v>0.9224336542903625</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.01047117642148282</v>
+        <v>0.01033758898922709</v>
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="n">
-        <v>0.9836807424446214</v>
+        <v>0.9848925210034284</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.002091118985687701</v>
+        <v>0.002011984109332633</v>
       </c>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>0.8658714761208417</v>
+        <v>0.8728316232390262</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.01212794854304989</v>
+        <v>0.01180908740359581</v>
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="n">
-        <v>0.9878502006923368</v>
+        <v>0.9880876414415648</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.0009520194639804986</v>
+        <v>0.0009426710156491396</v>
       </c>
       <c r="AN46" t="inlineStr"/>
     </row>
@@ -5384,10 +5384,10 @@
         <v>0.01548193654302897</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5362846783319638</v>
+        <v>0.5376530400040005</v>
       </c>
       <c r="L47" t="n">
-        <v>0.5492302964256942</v>
+        <v>0.55386159540626</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5396,16 +5396,16 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.262041686410713</v>
+        <v>4.272240003116125</v>
       </c>
       <c r="P47" t="n">
-        <v>4.358499538739855</v>
+        <v>4.392994941751244</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9442435661395094</v>
+        <v>0.9451092518699958</v>
       </c>
       <c r="R47" t="n">
-        <v>0.008873757836498755</v>
+        <v>0.008804600464171093</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
@@ -5415,38 +5415,38 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>0.9388010457126807</v>
+        <v>0.940644718982248</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.01363056122682955</v>
+        <v>0.01342367472314932</v>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>0.8034696057270717</v>
+        <v>0.8033244109864681</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.006926755960562583</v>
+        <v>0.00692931419805967</v>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="n">
-        <v>0.8472217428334066</v>
+        <v>0.847695687677937</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.0116543004856974</v>
+        <v>0.01163620960645925</v>
       </c>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
-        <v>0.9010697874179765</v>
+        <v>0.9016049470413948</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.004877825252754163</v>
+        <v>0.004864614147289625</v>
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
-        <v>0.9096346914701681</v>
+        <v>0.9099581517169765</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.0005743206432334187</v>
+        <v>0.0005732918389398196</v>
       </c>
       <c r="AN47" t="inlineStr"/>
     </row>
@@ -5488,10 +5488,10 @@
         <v>0.04054047652094685</v>
       </c>
       <c r="K48" t="n">
-        <v>0.5133086615075061</v>
+        <v>0.4047097120777118</v>
       </c>
       <c r="L48" t="n">
-        <v>0.5304241650804626</v>
+        <v>0.5459567870506425</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5500,16 +5500,16 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4.090716553477905</v>
+        <v>3.278188650913639</v>
       </c>
       <c r="P48" t="n">
-        <v>4.218355529141682</v>
+        <v>4.334035035067895</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9636543047177719</v>
+        <v>0.9639931396374642</v>
       </c>
       <c r="R48" t="n">
-        <v>0.009830026639216628</v>
+        <v>0.009784098841558167</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
@@ -5519,38 +5519,38 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>0.9508658427437623</v>
+        <v>0.9507073691867312</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.01620828195268155</v>
+        <v>0.01623439938749992</v>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>0.8763418849191106</v>
+        <v>0.885564897739694</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.005940221760702119</v>
+        <v>0.005714404488955672</v>
       </c>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="n">
-        <v>0.9507766138532817</v>
+        <v>0.9510188166467399</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.01286607049429841</v>
+        <v>0.01283437782524244</v>
       </c>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="n">
-        <v>0.7132509990905755</v>
+        <v>0.7409315243339216</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.004425150112169619</v>
+        <v>0.004206145926056573</v>
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="n">
-        <v>0.9994202483595795</v>
+        <v>0.9996682151621836</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.0001864315829211262</v>
+        <v>0.0001410349541343809</v>
       </c>
       <c r="AN48" t="inlineStr"/>
     </row>
@@ -5592,10 +5592,10 @@
         <v>0.02297528417150188</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3582154952860752</v>
+        <v>0.3632462737432927</v>
       </c>
       <c r="L49" t="n">
-        <v>0.5401662209124551</v>
+        <v>0.5436737909142402</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -5604,16 +5604,16 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4.312452942874997</v>
+        <v>4.068731139454012</v>
       </c>
       <c r="P49" t="n">
-        <v>4.404972903041084</v>
+        <v>4.41054613424981</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.9424119859353426</v>
+        <v>0.9422527860902778</v>
       </c>
       <c r="R49" t="n">
-        <v>0.0113747360821295</v>
+        <v>0.01139044774077632</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
@@ -5623,38 +5623,38 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>0.9684787185265602</v>
+        <v>0.9671176949013629</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.01197580593373487</v>
+        <v>0.0122316189889993</v>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>0.8129645761805001</v>
+        <v>0.8232446508781506</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.004147360694102419</v>
+        <v>0.004031773780192899</v>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="n">
-        <v>0.4595994964304544</v>
+        <v>0.4612537299587078</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.0135716598047161</v>
+        <v>0.01355087160968498</v>
       </c>
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="n">
-        <v>0.3776425794156939</v>
+        <v>0.3836149605572192</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.01733325224270698</v>
+        <v>0.01724988347376059</v>
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="n">
-        <v>0.8747853066914096</v>
+        <v>0.8756694195663643</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.001292668958695836</v>
+        <v>0.001288097251607165</v>
       </c>
       <c r="AN49" t="inlineStr"/>
     </row>
@@ -5696,10 +5696,10 @@
         <v>0.02365077480082941</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5532153165827609</v>
+        <v>0.5409958952894118</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5851082596758951</v>
+        <v>0.5605201676033635</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -5708,16 +5708,16 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.388186391172322</v>
+        <v>4.297151770118208</v>
       </c>
       <c r="P50" t="n">
-        <v>4.625587228345159</v>
+        <v>4.442562212890054</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.9579546499562428</v>
+        <v>0.9608045769180966</v>
       </c>
       <c r="R50" t="n">
-        <v>0.0109594947982313</v>
+        <v>0.01058154850218405</v>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
@@ -5727,31 +5727,31 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>0.9775691242814226</v>
+        <v>0.9819033004737431</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.01259988117814589</v>
+        <v>0.01131730506638015</v>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>0.9379724386735047</v>
+        <v>0.9374170034323297</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.005306798584481242</v>
+        <v>0.005330505898001532</v>
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="n">
-        <v>0.94867769317901</v>
+        <v>0.9482343494354788</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.00231454428559842</v>
+        <v>0.002324519793881028</v>
       </c>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="n">
-        <v>0.8024407405620921</v>
+        <v>0.8050630900901391</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.01783797926667442</v>
+        <v>0.01771919545651057</v>
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
@@ -5798,10 +5798,10 @@
         <v>0.05173441476315732</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5293227205179547</v>
+        <v>0.4812086802605804</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5583707580630578</v>
+        <v>0.5582457840330085</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -5810,16 +5810,16 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>4.210145903626906</v>
+        <v>3.851059526098111</v>
       </c>
       <c r="P51" t="n">
-        <v>4.42657732043377</v>
+        <v>4.425622904874372</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.9282979959973066</v>
+        <v>0.9284299964927997</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01075423064377406</v>
+        <v>0.01074432703134815</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -5829,38 +5829,38 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>0.9299460486816002</v>
+        <v>0.9295092822420135</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.01564785368538375</v>
+        <v>0.01569655784531013</v>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>0.7955981168623248</v>
+        <v>0.7965003248261033</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.01443591286388576</v>
+        <v>0.01440401834558218</v>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="n">
-        <v>-0.8408767479385451</v>
+        <v>-0.8078403432370145</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.003403678605510174</v>
+        <v>0.003372999102247724</v>
       </c>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="n">
-        <v>0.8902798997025974</v>
+        <v>0.8916714400390217</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.01063498913798302</v>
+        <v>0.01056733408254436</v>
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="n">
-        <v>0.9952095412905826</v>
+        <v>0.9956322801226107</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.0005731112544184649</v>
+        <v>0.0005472399253436916</v>
       </c>
       <c r="AN51" t="inlineStr"/>
     </row>
@@ -5902,10 +5902,10 @@
         <v>0.004631983561397277</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5458032169079876</v>
+        <v>0.5429836066241071</v>
       </c>
       <c r="L52" t="n">
-        <v>0.5562802672787837</v>
+        <v>0.5519809004860716</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -5914,16 +5914,16 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.33297137534801</v>
+        <v>4.311963123218198</v>
       </c>
       <c r="P52" t="n">
-        <v>4.411009900256763</v>
+        <v>4.378988121467831</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.9654227421943514</v>
+        <v>0.9652852496903884</v>
       </c>
       <c r="R52" t="n">
-        <v>0.008979425245246357</v>
+        <v>0.008997260360846616</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
@@ -5933,38 +5933,38 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>0.9775886454272612</v>
+        <v>0.9775778295623077</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.006855349610060666</v>
+        <v>0.006857003628598683</v>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>0.9195096840870256</v>
+        <v>0.9189528216211351</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.00200698872328012</v>
+        <v>0.002013919310586962</v>
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="n">
-        <v>0.7877828467702369</v>
+        <v>0.7873706895020927</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.01654210160623573</v>
+        <v>0.01655815742488062</v>
       </c>
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="n">
-        <v>0.7146591608453062</v>
+        <v>0.7108994128057953</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.008806593314211067</v>
+        <v>0.008864422778274969</v>
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="n">
-        <v>0.0001582846317169651</v>
+        <v>0.001044304216321068</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.0009640307621501654</v>
+        <v>0.0009636035248012068</v>
       </c>
       <c r="AN52" t="inlineStr"/>
     </row>
@@ -6006,10 +6006,10 @@
         <v>0.00319007047444387</v>
       </c>
       <c r="K53" t="n">
-        <v>0.4922746809080481</v>
+        <v>0.4961096498617923</v>
       </c>
       <c r="L53" t="n">
-        <v>0.5476792874672232</v>
+        <v>0.5564428925727184</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6018,16 +6018,16 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4.395968424017083</v>
+        <v>4.490422673838463</v>
       </c>
       <c r="P53" t="n">
-        <v>4.363627185494851</v>
+        <v>4.432275172228135</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.9857421372694104</v>
+        <v>0.9857806244172354</v>
       </c>
       <c r="R53" t="n">
-        <v>0.005133814889606065</v>
+        <v>0.005126881192193562</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -6037,38 +6037,38 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="n">
-        <v>0.9785046022839575</v>
+        <v>0.9788109294893552</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.008497028704247643</v>
+        <v>0.008436266604643637</v>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>0.7291594877434919</v>
+        <v>0.7228101524293111</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.005342401311773184</v>
+        <v>0.005404659709356356</v>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="n">
-        <v>0.9851235604552461</v>
+        <v>0.9850331455528376</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.003011254136632222</v>
+        <v>0.003020391061388467</v>
       </c>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="n">
-        <v>0.9818831239541677</v>
+        <v>0.9819223089037094</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.003919717285696808</v>
+        <v>0.003915476017345877</v>
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="n">
-        <v>0.8730174919320054</v>
+        <v>0.8730747425828687</v>
       </c>
       <c r="AM53" t="n">
-        <v>0.0001578147500505981</v>
+        <v>0.0001577791702849639</v>
       </c>
       <c r="AN53" t="inlineStr"/>
     </row>
@@ -6110,10 +6110,10 @@
         <v>0.02695043454293275</v>
       </c>
       <c r="K54" t="n">
-        <v>0.3323169060274417</v>
+        <v>0.3258000977721075</v>
       </c>
       <c r="L54" t="n">
-        <v>0.5412028534638927</v>
+        <v>0.527541511323768</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -6122,16 +6122,16 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>4.248018727268365</v>
+        <v>4.139890418693176</v>
       </c>
       <c r="P54" t="n">
-        <v>4.472839858339956</v>
+        <v>4.360447263399376</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.945525134503722</v>
+        <v>0.9441125306217791</v>
       </c>
       <c r="R54" t="n">
-        <v>0.008475189103775347</v>
+        <v>0.008584372139672728</v>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
@@ -6141,38 +6141,38 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>0.9400335518339341</v>
+        <v>0.9373580417392703</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.01261667838507558</v>
+        <v>0.0128950649015272</v>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>0.4062756922784018</v>
+        <v>0.4217348810428259</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.004443593461145251</v>
+        <v>0.004385361528281823</v>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="n">
-        <v>0.8240753931633302</v>
+        <v>0.8209224712522627</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.01243884061087673</v>
+        <v>0.01254981010968369</v>
       </c>
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="n">
-        <v>0.850534326846389</v>
+        <v>0.8511419103976374</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.004953909535544923</v>
+        <v>0.004943830368299336</v>
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="n">
-        <v>0.8903137612939338</v>
+        <v>0.8843393427070396</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.0009757458553520836</v>
+        <v>0.001001967122203119</v>
       </c>
       <c r="AN54" t="inlineStr"/>
     </row>
@@ -6214,10 +6214,10 @@
         <v>0.00266683139341308</v>
       </c>
       <c r="K55" t="n">
-        <v>0.3199361685503805</v>
+        <v>0.3243733482653745</v>
       </c>
       <c r="L55" t="n">
-        <v>0.513747128190716</v>
+        <v>0.5195633213139152</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6226,16 +6226,16 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>4.345610810250299</v>
+        <v>4.37343702145688</v>
       </c>
       <c r="P55" t="n">
-        <v>4.368230524749379</v>
+        <v>4.410183567146585</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.9009745037673984</v>
+        <v>0.9016826123858003</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01268968260566848</v>
+        <v>0.01264423070047798</v>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
@@ -6245,38 +6245,38 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>0.8417831275406037</v>
+        <v>0.8434473460713175</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.01920047591428336</v>
+        <v>0.01909922798992492</v>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>0.1344788012608691</v>
+        <v>0.1345516419215065</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.004073433961358093</v>
+        <v>0.004073262551423722</v>
       </c>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="n">
-        <v>0.6250557250259022</v>
+        <v>0.6267996862692629</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.01961419767932818</v>
+        <v>0.01956852920097032</v>
       </c>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="n">
-        <v>0.8284280311228004</v>
+        <v>0.8288765285861632</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.00591613143284092</v>
+        <v>0.005908393845408905</v>
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="n">
-        <v>0.9105387510380626</v>
+        <v>0.9091333760619739</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.0004143933591336233</v>
+        <v>0.000417635593421625</v>
       </c>
       <c r="AN55" t="inlineStr"/>
     </row>
@@ -6318,10 +6318,10 @@
         <v>0.03893815066809572</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5336789504017783</v>
+        <v>0.5097180810386136</v>
       </c>
       <c r="L56" t="n">
-        <v>0.5483711655041982</v>
+        <v>0.5518535577083454</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -6330,16 +6330,16 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>4.242619804626787</v>
+        <v>4.063927352245716</v>
       </c>
       <c r="P56" t="n">
-        <v>4.352100318077322</v>
+        <v>4.378024103527062</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8242670219004026</v>
+        <v>0.8290942444541722</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01229988857148968</v>
+        <v>0.01212977896087996</v>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
@@ -6349,38 +6349,38 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0.7196027677003406</v>
+        <v>0.7283256784225867</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.01848776660585475</v>
+        <v>0.01819792556061479</v>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>-0.2139204721596895</v>
+        <v>-0.1642604336165421</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.009656550822694223</v>
+        <v>0.009456969361349826</v>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="n">
-        <v>0.6232084159368971</v>
+        <v>0.6280877513406949</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.01622894053033722</v>
+        <v>0.01612351822136859</v>
       </c>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="n">
-        <v>0.7348469815186315</v>
+        <v>0.7483831336531044</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.007486526698408037</v>
+        <v>0.00729292864910951</v>
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="n">
-        <v>0.9126349647852501</v>
+        <v>0.915257761023231</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.001401147297138398</v>
+        <v>0.001379955025367335</v>
       </c>
       <c r="AN56" t="inlineStr"/>
     </row>
@@ -6422,10 +6422,10 @@
         <v>0.02444228773888892</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5416026416533484</v>
+        <v>0.5362984060044483</v>
       </c>
       <c r="L57" t="n">
-        <v>0.5546963790150543</v>
+        <v>0.554455161301568</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -6434,16 +6434,16 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4.301673038976071</v>
+        <v>4.26214400069415</v>
       </c>
       <c r="P57" t="n">
-        <v>4.399214048441006</v>
+        <v>4.397413072186263</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.9059462298041834</v>
+        <v>0.9075211627563269</v>
       </c>
       <c r="R57" t="n">
-        <v>0.009325716035934436</v>
+        <v>0.009247306723752669</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
@@ -6453,38 +6453,38 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
-        <v>0.8140214676226617</v>
+        <v>0.817918593012726</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.01632283342963049</v>
+        <v>0.01615090791475431</v>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>0.6143887314377203</v>
+        <v>0.6169303172194858</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.008952304261603374</v>
+        <v>0.008922752914418243</v>
       </c>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="n">
-        <v>0.7454058531746608</v>
+        <v>0.7460658066096132</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.007746089106169566</v>
+        <v>0.007736042969368808</v>
       </c>
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="n">
-        <v>0.9215997188427121</v>
+        <v>0.9245547766948449</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.005152726803217192</v>
+        <v>0.00505468598589359</v>
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="n">
-        <v>0.6569838767558028</v>
+        <v>0.6597688663710393</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.001309108552155662</v>
+        <v>0.001303783315303731</v>
       </c>
       <c r="AN57" t="inlineStr"/>
     </row>
@@ -6526,10 +6526,10 @@
         <v>0.02625641629885448</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2467965400229047</v>
+        <v>0.2359136518339272</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5500374731379446</v>
+        <v>0.5314496607071902</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -6538,16 +6538,16 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>4.317748846014766</v>
+        <v>4.091754229257946</v>
       </c>
       <c r="P58" t="n">
-        <v>4.740193105772273</v>
+        <v>4.427388979875565</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.9770448898225341</v>
+        <v>0.9753643174695377</v>
       </c>
       <c r="R58" t="n">
-        <v>0.006371034319295661</v>
+        <v>0.006600130964115387</v>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
@@ -6557,38 +6557,38 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>0.9920398980513737</v>
+        <v>0.9908778247480367</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.005176753381400173</v>
+        <v>0.005541755571874639</v>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>0.9437600717937621</v>
+        <v>0.954174277554766</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.002182621397159902</v>
+        <v>0.001970201701686497</v>
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="n">
-        <v>0.979331831399143</v>
+        <v>0.97878329253977</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.005523889933775291</v>
+        <v>0.00559671269031568</v>
       </c>
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="n">
-        <v>0.7867920580961186</v>
+        <v>0.7700920248525112</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.01184595062806399</v>
+        <v>0.01230113677889452</v>
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="n">
-        <v>0.9563215443065751</v>
+        <v>0.9541800329657104</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.0007401847539930535</v>
+        <v>0.0007581128957019003</v>
       </c>
       <c r="AN58" t="inlineStr"/>
     </row>
@@ -6630,10 +6630,10 @@
         <v>0.02080322163891103</v>
       </c>
       <c r="K59" t="n">
-        <v>0.5318362786808796</v>
+        <v>0.5293059348727757</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5522015830235472</v>
+        <v>0.5537011020857625</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>4.228884151391346</v>
+        <v>4.210020762317669</v>
       </c>
       <c r="P59" t="n">
-        <v>4.380628629632027</v>
+        <v>4.391793516466226</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.7824327653299111</v>
+        <v>0.7893019037545375</v>
       </c>
       <c r="R59" t="n">
-        <v>0.01996519928968916</v>
+        <v>0.01964749602167767</v>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
@@ -6661,38 +6661,38 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>0.7324247911474242</v>
+        <v>0.7511808006713493</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.03242759479864647</v>
+        <v>0.03127042221855022</v>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
-        <v>0.4673994583749578</v>
+        <v>0.456024180753672</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.02255329314555998</v>
+        <v>0.02279286721567782</v>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="n">
-        <v>0.1419712598525847</v>
+        <v>0.1390582692687956</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.01074618996479988</v>
+        <v>0.01076441605967704</v>
       </c>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="n">
-        <v>-1.018723166284632</v>
+        <v>-1.015799239317717</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.01762406767912647</v>
+        <v>0.01761129966795367</v>
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="n">
-        <v>-0.6676998393311022</v>
+        <v>-0.662332675334125</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.002599541677346572</v>
+        <v>0.00259535524947564</v>
       </c>
       <c r="AN59" t="inlineStr"/>
     </row>
@@ -6734,10 +6734,10 @@
         <v>0.0151609171982884</v>
       </c>
       <c r="K60" t="n">
-        <v>0.525362947003733</v>
+        <v>0.520091897588902</v>
       </c>
       <c r="L60" t="n">
-        <v>0.539655723525681</v>
+        <v>0.5419720878153651</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -6746,16 +6746,16 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.180622353107697</v>
+        <v>4.141314459674549</v>
       </c>
       <c r="P60" t="n">
-        <v>4.287158916417223</v>
+        <v>4.304414026823678</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.8221347114998343</v>
+        <v>0.8246015048840531</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02623119911056224</v>
+        <v>0.02604866526239791</v>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
@@ -6765,38 +6765,38 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>0.3323109987312934</v>
+        <v>0.34159354583436</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.05724703921997685</v>
+        <v>0.0568477079221997</v>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>-1.759004463168659</v>
+        <v>-1.724682159987728</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.008803385065024382</v>
+        <v>0.008748456186128822</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="n">
-        <v>0.6517873767234297</v>
+        <v>0.6533379756932023</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.006507808907720355</v>
+        <v>0.006493303028177932</v>
       </c>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="n">
-        <v>-7.701239102907756</v>
+        <v>-7.498498238228663</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.006563358872323581</v>
+        <v>0.006486444317226213</v>
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="n">
-        <v>0.9398996491455879</v>
+        <v>0.9388936035041684</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.0004761190679149376</v>
+        <v>0.0004800875104764872</v>
       </c>
       <c r="AN60" t="inlineStr"/>
     </row>
@@ -6838,10 +6838,10 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4188133248307595</v>
+        <v>0.4276854726398666</v>
       </c>
       <c r="L61" t="n">
-        <v>0.5238550623315624</v>
+        <v>0.5387062158005479</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -6850,16 +6850,16 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>4.076109010387499</v>
+        <v>3.964762310542818</v>
       </c>
       <c r="P61" t="n">
-        <v>4.199448870580616</v>
+        <v>4.302246317661345</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.9769807906238656</v>
+        <v>0.9764564161278908</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01081708273018071</v>
+        <v>0.0109395948022426</v>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
@@ -6871,38 +6871,38 @@
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
-        <v>0.9585456995148877</v>
+        <v>0.9575418218156996</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.02269139475788429</v>
+        <v>0.02296450419028379</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>0.1058772521141456</v>
+        <v>0.09921825726618483</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.005125811194488109</v>
+        <v>0.005144863072379082</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="n">
-        <v>0.6738813789489807</v>
+        <v>0.6683998390589159</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.005786070528789076</v>
+        <v>0.005834495252819951</v>
       </c>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="n">
-        <v>0.8995885831524089</v>
+        <v>0.8976402994945234</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.002532955577829286</v>
+        <v>0.002557411000898167</v>
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="n">
-        <v>0.3298393824776636</v>
+        <v>0.3339938065814732</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.002230073254069481</v>
+        <v>0.00222315023235074</v>
       </c>
       <c r="AN61" t="inlineStr"/>
     </row>
@@ -6944,10 +6944,10 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1552434129439603</v>
+        <v>0.1560475317581405</v>
       </c>
       <c r="L62" t="n">
-        <v>0.4416266659513342</v>
+        <v>0.4542540445922373</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -6956,16 +6956,16 @@
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>4.099154174190237</v>
+        <v>4.22633178824696</v>
       </c>
       <c r="P62" t="n">
-        <v>4.14398868735137</v>
+        <v>4.265401247070139</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.9901600365266197</v>
+        <v>0.9902226006716003</v>
       </c>
       <c r="R62" t="n">
-        <v>0.006542059804315173</v>
+        <v>0.00652122888087008</v>
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
@@ -6977,38 +6977,38 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>0.986518745393455</v>
+        <v>0.9866299560375427</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.01211062301218399</v>
+        <v>0.01206056760800621</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>-0.3109570120402458</v>
+        <v>-0.3328617033881316</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.003811640735892155</v>
+        <v>0.00384335303761227</v>
       </c>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="n">
-        <v>0.7806474939477505</v>
+        <v>0.7850876997653191</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.006270676114688861</v>
+        <v>0.006206885096906208</v>
       </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="n">
-        <v>0.9501142169931515</v>
+        <v>0.948071503545309</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.003315844261474691</v>
+        <v>0.003383051443696128</v>
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>0.8764456382559918</v>
+        <v>0.8788222670363137</v>
       </c>
       <c r="AM62" t="n">
-        <v>0.001760942741738242</v>
+        <v>0.001743924205480003</v>
       </c>
       <c r="AN62" t="inlineStr"/>
     </row>
@@ -7050,10 +7050,10 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K63" t="n">
-        <v>0.3646171913311278</v>
+        <v>0.3712793451295304</v>
       </c>
       <c r="L63" t="n">
-        <v>0.514685002555867</v>
+        <v>0.52729018172343</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -7062,16 +7062,16 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>4.076109010387499</v>
+        <v>4.032785542367162</v>
       </c>
       <c r="P63" t="n">
-        <v>4.205537025212092</v>
+        <v>4.293305936567684</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9890244494450439</v>
+        <v>0.9889576127993983</v>
       </c>
       <c r="R63" t="n">
-        <v>0.007662446197455941</v>
+        <v>0.007685741379523292</v>
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
@@ -7083,38 +7083,38 @@
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>0.9781558022975246</v>
+        <v>0.9780284592844997</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.0162745053657639</v>
+        <v>0.01632187338921539</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>0.7278532779929342</v>
+        <v>0.7258897890726739</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.0022779600469001</v>
+        <v>0.002286162811083265</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="n">
-        <v>0.9782481100601726</v>
+        <v>0.9780994857142516</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.00164026095085094</v>
+        <v>0.001645855124601485</v>
       </c>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
-        <v>0.7706141905845793</v>
+        <v>0.7678883977110569</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.004271347343786665</v>
+        <v>0.004296650618390212</v>
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="n">
-        <v>0.3948424858284316</v>
+        <v>0.4016283054013692</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.001796495773312589</v>
+        <v>0.001786395044683362</v>
       </c>
       <c r="AN63" t="inlineStr"/>
     </row>
@@ -7156,10 +7156,10 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K64" t="n">
-        <v>0.261923789223986</v>
+        <v>0.2665008022242393</v>
       </c>
       <c r="L64" t="n">
-        <v>0.5063257388123407</v>
+        <v>0.5255162256578281</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -7168,16 +7168,16 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>4.099154174190237</v>
+        <v>3.919470058378178</v>
       </c>
       <c r="P64" t="n">
-        <v>4.162703810072364</v>
+        <v>4.303284276620948</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.9782896373664617</v>
+        <v>0.9782948641580993</v>
       </c>
       <c r="R64" t="n">
-        <v>0.009872205090486494</v>
+        <v>0.00987101664730056</v>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
@@ -7189,38 +7189,38 @@
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>0.9656601593373315</v>
+        <v>0.9657497827782375</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.01957074954735519</v>
+        <v>0.01954519404366117</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>0.3179779672134455</v>
+        <v>0.2942650832185683</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.004459955446021431</v>
+        <v>0.004536825970330232</v>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="n">
-        <v>0.4939858053130187</v>
+        <v>0.4937598639763084</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.008656035911114092</v>
+        <v>0.008657968206765608</v>
       </c>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
-        <v>0.9739516791237199</v>
+        <v>0.9731351093991819</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.002329286707008766</v>
+        <v>0.00236551452914697</v>
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="n">
-        <v>0.8417827815290835</v>
+        <v>0.8422841838162359</v>
       </c>
       <c r="AM64" t="n">
-        <v>0.002248386104351653</v>
+        <v>0.002244820624800383</v>
       </c>
       <c r="AN64" t="inlineStr"/>
     </row>
@@ -7262,10 +7262,10 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K65" t="n">
-        <v>0.363558395025915</v>
+        <v>0.3705977767793169</v>
       </c>
       <c r="L65" t="n">
-        <v>0.5204902037318956</v>
+        <v>0.5335660846006467</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -7274,16 +7274,16 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>4.076109010387499</v>
+        <v>3.919437140445244</v>
       </c>
       <c r="P65" t="n">
-        <v>4.223168896346237</v>
+        <v>4.310184148305897</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.9779796447449592</v>
+        <v>0.9777822818323934</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01068870145541154</v>
+        <v>0.01073649467768937</v>
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
@@ -7295,38 +7295,38 @@
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="n">
-        <v>0.9631457179307704</v>
+        <v>0.9627713869596259</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.02194721311647242</v>
+        <v>0.02205839104534131</v>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>0.6683714427362812</v>
+        <v>0.6674842826994962</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.003899502140451382</v>
+        <v>0.003904714556281373</v>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="n">
-        <v>0.672456233328645</v>
+        <v>0.6715960039120876</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.008055449871464476</v>
+        <v>0.008066020964317635</v>
       </c>
       <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="n">
-        <v>0.9096939914982891</v>
+        <v>0.9093875573381727</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.002592751959604288</v>
+        <v>0.002597147209296385</v>
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="n">
-        <v>0.5801425782373126</v>
+        <v>0.581132593361839</v>
       </c>
       <c r="AM65" t="n">
-        <v>0.001851613531366265</v>
+        <v>0.001849429209737506</v>
       </c>
       <c r="AN65" t="inlineStr"/>
     </row>
@@ -7368,10 +7368,10 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K66" t="n">
-        <v>0.3066348386477217</v>
+        <v>0.3123846531483918</v>
       </c>
       <c r="L66" t="n">
-        <v>0.5109539117916543</v>
+        <v>0.5296498294463413</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -7380,16 +7380,16 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>4.099154174190237</v>
+        <v>4.0372004394865</v>
       </c>
       <c r="P66" t="n">
-        <v>4.170740050374269</v>
+        <v>4.306941228393627</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.9786997259509119</v>
+        <v>0.9784700039257482</v>
       </c>
       <c r="R66" t="n">
-        <v>0.009871567947535121</v>
+        <v>0.009924657288851042</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -7401,38 +7401,38 @@
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>0.9651621473486919</v>
+        <v>0.9647740911636622</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.01964746458441907</v>
+        <v>0.01975658735355412</v>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>0.5513546751070978</v>
+        <v>0.5424297723972302</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.004129012710340382</v>
+        <v>0.004169879700126315</v>
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="n">
-        <v>0.6931426458413376</v>
+        <v>0.6911480349487376</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.008463402129030658</v>
+        <v>0.008490864156873577</v>
       </c>
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="n">
-        <v>0.9532625968764245</v>
+        <v>0.9524169399192033</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.003006739736452711</v>
+        <v>0.003033819456986722</v>
       </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="n">
-        <v>0.8573045300742362</v>
+        <v>0.8578496290053969</v>
       </c>
       <c r="AM66" t="n">
-        <v>0.002091051982679832</v>
+        <v>0.002087054235492194</v>
       </c>
       <c r="AN66" t="inlineStr"/>
     </row>
@@ -7474,10 +7474,10 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.5363853847768683</v>
+        <v>0.5593936798993145</v>
       </c>
       <c r="L67" t="n">
-        <v>0.5389185047934655</v>
+        <v>0.5512003213762259</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -7486,61 +7486,61 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>4.262792264471607</v>
+        <v>4.434199252443003</v>
       </c>
       <c r="P67" t="n">
-        <v>4.281670570195018</v>
+        <v>4.373177070109338</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.8938769961570038</v>
+        <v>0.9015940609169077</v>
       </c>
       <c r="R67" t="n">
-        <v>0.02356224336245918</v>
+        <v>0.02268937459238491</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
-        <v>0.7930484511241501</v>
+        <v>0.7840874861795611</v>
       </c>
       <c r="X67" t="n">
-        <v>0.0007907628043781875</v>
+        <v>0.0008077013323736372</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>0.710599339075296</v>
+        <v>0.7336078490036118</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.0554317985089654</v>
+        <v>0.05318264375510302</v>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
-        <v>0.7511313546796123</v>
+        <v>0.7404141677709583</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.002733044770765369</v>
+        <v>0.002791271922402073</v>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="n">
-        <v>0.6473741654653834</v>
+        <v>0.6497432520747137</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.01302489109972103</v>
+        <v>0.01298106405333017</v>
       </c>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
-        <v>0.8122930623439362</v>
+        <v>0.805658359473467</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.008972511648131107</v>
+        <v>0.009129706177855584</v>
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="n">
-        <v>0.6852643873059676</v>
+        <v>0.664722169751524</v>
       </c>
       <c r="AM67" t="n">
-        <v>0.0001497229198302242</v>
+        <v>0.0001545317644025472</v>
       </c>
       <c r="AN67" t="inlineStr"/>
     </row>
@@ -7582,10 +7582,10 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.5363853847768683</v>
+        <v>0.5709446758847706</v>
       </c>
       <c r="L68" t="n">
-        <v>0.529747196855043</v>
+        <v>0.5513570310668608</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -7594,61 +7594,61 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.262792264471607</v>
+        <v>4.520196890876156</v>
       </c>
       <c r="P68" t="n">
-        <v>4.213309963814893</v>
+        <v>4.374341291890712</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.7871066386495369</v>
+        <v>0.7868225624667292</v>
       </c>
       <c r="R68" t="n">
-        <v>0.03077960582545608</v>
+        <v>0.03080013450233389</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>0.5362378985559215</v>
+        <v>0.5373268068139827</v>
       </c>
       <c r="X68" t="n">
-        <v>0.001113685536388511</v>
+        <v>0.001112377307381705</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>0.4232202496007236</v>
+        <v>0.4243587182068744</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.07387614955683269</v>
+        <v>0.0738032038434403</v>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
-        <v>0.5178906677339579</v>
+        <v>0.517967293818874</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.003705594158640165</v>
+        <v>0.003705299664801253</v>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="n">
-        <v>0.7444387170417199</v>
+        <v>0.7400216559757031</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.007433941404912978</v>
+        <v>0.007497909433729451</v>
       </c>
       <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="n">
-        <v>0.6940281635271426</v>
+        <v>0.6598645649093471</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.01247357279563066</v>
+        <v>0.01315152390614106</v>
       </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="n">
-        <v>0.1358609629615259</v>
+        <v>0.07978784700122687</v>
       </c>
       <c r="AM68" t="n">
-        <v>0.0008261730617061148</v>
+        <v>0.0008525565595529457</v>
       </c>
       <c r="AN68" t="inlineStr"/>
     </row>
@@ -7690,10 +7690,10 @@
         <v>0.04611530568392795</v>
       </c>
       <c r="K69" t="n">
-        <v>0.4141431162653932</v>
+        <v>0.4227647615340945</v>
       </c>
       <c r="L69" t="n">
-        <v>0.5230173541933488</v>
+        <v>0.5365480432054363</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -7702,16 +7702,16 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>4.262919614482086</v>
+        <v>4.368894955962674</v>
       </c>
       <c r="P69" t="n">
-        <v>4.265278554251244</v>
+        <v>4.372337639764951</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.9680039604543749</v>
+        <v>0.9678409253969988</v>
       </c>
       <c r="R69" t="n">
-        <v>0.01048370203485141</v>
+        <v>0.01051037782356906</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
@@ -7721,38 +7721,38 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>0.9367524250040786</v>
+        <v>0.9360477862573848</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.01393268002302167</v>
+        <v>0.01401007677178978</v>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
-        <v>0.6588013163642681</v>
+        <v>0.6619752013653453</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.003709446073827349</v>
+        <v>0.003692152831910198</v>
       </c>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="n">
-        <v>0.857697097932728</v>
+        <v>0.8587090683356974</v>
       </c>
       <c r="AG69" t="n">
-        <v>0.01527569759346986</v>
+        <v>0.01522128501753176</v>
       </c>
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
-        <v>0.9002874746427216</v>
+        <v>0.8974250672104145</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.009581048546963908</v>
+        <v>0.009717595190113004</v>
       </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="n">
-        <v>0.5659360306981278</v>
+        <v>0.5714615671432348</v>
       </c>
       <c r="AM69" t="n">
-        <v>0.004064117462965029</v>
+        <v>0.004038166963040459</v>
       </c>
       <c r="AN69" t="inlineStr"/>
     </row>
@@ -7794,10 +7794,10 @@
         <v>0.03389921553245138</v>
       </c>
       <c r="K70" t="n">
-        <v>0.5481989593924306</v>
+        <v>0.5503708566416453</v>
       </c>
       <c r="L70" t="n">
-        <v>0.5511909743090966</v>
+        <v>0.5571388279955621</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -7806,16 +7806,16 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>4.3508196972905</v>
+        <v>4.366998961487805</v>
       </c>
       <c r="P70" t="n">
-        <v>4.373107845075807</v>
+        <v>4.417406803997117</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.9577167159245279</v>
+        <v>0.9577440876459358</v>
       </c>
       <c r="R70" t="n">
-        <v>0.0100910667170145</v>
+        <v>0.01008780000550043</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
@@ -7825,38 +7825,38 @@
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>0.8859224981354885</v>
+        <v>0.8854756377355057</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.01508131466268258</v>
+        <v>0.01511082379202798</v>
       </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
-        <v>0.9254726862436822</v>
+        <v>0.9253918248346422</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.003166708927624993</v>
+        <v>0.003168426386055833</v>
       </c>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="n">
-        <v>0.9428528437063111</v>
+        <v>0.9431770989989549</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.01085497252243279</v>
+        <v>0.01082413293580442</v>
       </c>
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="n">
-        <v>0.8099224002261393</v>
+        <v>0.8105629049318468</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.01221107077450313</v>
+        <v>0.0121904795837367</v>
       </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="n">
-        <v>0.7677324838809731</v>
+        <v>0.7706955991884092</v>
       </c>
       <c r="AM70" t="n">
-        <v>0.002175629133457512</v>
+        <v>0.002161706969927251</v>
       </c>
       <c r="AN70" t="inlineStr"/>
     </row>
@@ -7898,10 +7898,10 @@
         <v>0.02861063360823382</v>
       </c>
       <c r="K71" t="n">
-        <v>0.5103518668467035</v>
+        <v>0.5091634325943013</v>
       </c>
       <c r="L71" t="n">
-        <v>0.5598474514508065</v>
+        <v>0.5591645399916279</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>4.438072623193317</v>
+        <v>4.443210889445625</v>
       </c>
       <c r="P71" t="n">
-        <v>4.455612740725383</v>
+        <v>4.45157851663676</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.9608864461406768</v>
+        <v>0.960905064904266</v>
       </c>
       <c r="R71" t="n">
-        <v>0.01079863435247132</v>
+        <v>0.01079606387328092</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
@@ -7929,38 +7929,38 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>0.9409038442643789</v>
+        <v>0.9409314163791648</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.01446802603151689</v>
+        <v>0.01446465051063864</v>
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
-        <v>0.7620720296692828</v>
+        <v>0.7624778062601361</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.004320794335866249</v>
+        <v>0.00431710829305459</v>
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="n">
-        <v>0.9056170711000586</v>
+        <v>0.9056837309667829</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.009798311037594045</v>
+        <v>0.009794850298019122</v>
       </c>
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="n">
-        <v>0.846287338726757</v>
+        <v>0.8463330626188879</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.01606913398702664</v>
+        <v>0.01606674381958397</v>
       </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="n">
-        <v>0.9452564122584486</v>
+        <v>0.9454807641177289</v>
       </c>
       <c r="AM71" t="n">
-        <v>0.0009140635469770537</v>
+        <v>0.000912188602309321</v>
       </c>
       <c r="AN71" t="inlineStr"/>
     </row>
@@ -8002,10 +8002,10 @@
         <v>0.03450948851818413</v>
       </c>
       <c r="K72" t="n">
-        <v>0.5584922532709602</v>
+        <v>0.5525686244778018</v>
       </c>
       <c r="L72" t="n">
-        <v>0.5758544370589833</v>
+        <v>0.5679527318392125</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -8014,16 +8014,16 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>4.547889869855799</v>
+        <v>4.490464158932846</v>
       </c>
       <c r="P72" t="n">
-        <v>4.559734659249446</v>
+        <v>4.500406950239454</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.9587044561216487</v>
+        <v>0.9585881834994068</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01160463323929139</v>
+        <v>0.01162095888323122</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -8033,38 +8033,38 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>0.857322332362483</v>
+        <v>0.8574052485563871</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.0157759249580855</v>
+        <v>0.01577134025406268</v>
       </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
-        <v>0.8497356490914018</v>
+        <v>0.8481187305244917</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.004269831750542723</v>
+        <v>0.004292743029630342</v>
       </c>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="n">
-        <v>0.951007252030083</v>
+        <v>0.9509468533867654</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.00693642816121291</v>
+        <v>0.006940702485738673</v>
       </c>
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
-        <v>0.8658016004997049</v>
+        <v>0.8651300588873552</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.01887031113247611</v>
+        <v>0.01891746663331906</v>
       </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="n">
-        <v>0.9026634138394147</v>
+        <v>0.9025142005278294</v>
       </c>
       <c r="AM72" t="n">
-        <v>0.001422537788294693</v>
+        <v>0.001423627719109316</v>
       </c>
       <c r="AN72" t="inlineStr"/>
     </row>
@@ -8106,10 +8106,10 @@
         <v>0.01985208116188355</v>
       </c>
       <c r="K73" t="n">
-        <v>0.5344803546979763</v>
+        <v>0.5594245360474558</v>
       </c>
       <c r="L73" t="n">
-        <v>0.5301017122050052</v>
+        <v>0.5542545413407491</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -8118,16 +8118,16 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.248593316158351</v>
+        <v>4.434429024992574</v>
       </c>
       <c r="P73" t="n">
-        <v>4.215952598021142</v>
+        <v>4.395925804706224</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9946573317614431</v>
+        <v>0.9946561269747206</v>
       </c>
       <c r="R73" t="n">
-        <v>0.004861062880573913</v>
+        <v>0.004861610941357829</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -8137,38 +8137,38 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>0.9546124838040193</v>
+        <v>0.9546484981116624</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.007314768265226086</v>
+        <v>0.007311865610315094</v>
       </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
-        <v>0.3242157811451821</v>
+        <v>0.303953838942979</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.001643312081606894</v>
+        <v>0.001667765734048136</v>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="n">
-        <v>0.9722422360809647</v>
+        <v>0.9721215045196219</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.005589925513544799</v>
+        <v>0.00560206893016771</v>
       </c>
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="n">
-        <v>0.8215678012476042</v>
+        <v>0.8216023361476901</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.005164772802440515</v>
+        <v>0.005164272966801963</v>
       </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="n">
-        <v>0.2274662213165166</v>
+        <v>0.2548646921498328</v>
       </c>
       <c r="AM73" t="n">
-        <v>0.002005294722764113</v>
+        <v>0.001969414101880343</v>
       </c>
       <c r="AN73" t="inlineStr"/>
     </row>
@@ -8210,10 +8210,10 @@
         <v>0.03595872786204279</v>
       </c>
       <c r="K74" t="n">
-        <v>0.5564885816617009</v>
+        <v>0.5539023206624197</v>
       </c>
       <c r="L74" t="n">
-        <v>0.5628321442795107</v>
+        <v>0.5600553689522942</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8222,16 +8222,16 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>4.431244325415121</v>
+        <v>4.39330331686405</v>
       </c>
       <c r="P74" t="n">
-        <v>4.460175575014954</v>
+        <v>4.439125468698231</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.9677299291542107</v>
+        <v>0.9676665625001474</v>
       </c>
       <c r="R74" t="n">
-        <v>0.008509721304889634</v>
+        <v>0.008518072202447611</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -8241,38 +8241,38 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>0.7920990008157948</v>
+        <v>0.790650401322366</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.01089359463548393</v>
+        <v>0.01093148060661289</v>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>0.8335712809166836</v>
+        <v>0.8362110962657245</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.001355693697341721</v>
+        <v>0.001344899028102427</v>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="n">
-        <v>0.8820436350179452</v>
+        <v>0.8820519222157659</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.01352372524309968</v>
+        <v>0.01352325017015671</v>
       </c>
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
-        <v>0.8656657308425511</v>
+        <v>0.8658459154178477</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.007410689221595908</v>
+        <v>0.007405717519435522</v>
       </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="n">
-        <v>0.7302059371769747</v>
+        <v>0.730221247810467</v>
       </c>
       <c r="AM74" t="n">
-        <v>0.001938817877284227</v>
+        <v>0.001938762863191675</v>
       </c>
       <c r="AN74" t="inlineStr"/>
     </row>
@@ -8314,10 +8314,10 @@
         <v>0.05396179716059933</v>
       </c>
       <c r="K75" t="n">
-        <v>0.5349426521273756</v>
+        <v>0.5371232694513625</v>
       </c>
       <c r="L75" t="n">
-        <v>0.5413772776291564</v>
+        <v>0.5502296926302926</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -8326,16 +8326,16 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>4.252039103170227</v>
+        <v>4.268291721388134</v>
       </c>
       <c r="P75" t="n">
-        <v>4.299992914838684</v>
+        <v>4.365943769511382</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.9676287084065744</v>
+        <v>0.9676649476119463</v>
       </c>
       <c r="R75" t="n">
-        <v>0.007105495843128927</v>
+        <v>0.007101517478086479</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -8345,38 +8345,38 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>0.8878174341871221</v>
+        <v>0.8871496550952456</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.01196835557650719</v>
+        <v>0.01200392420158328</v>
       </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
-        <v>0.8404662438353948</v>
+        <v>0.8451492726607359</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.002410055786531198</v>
+        <v>0.002374419361649531</v>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="n">
-        <v>0.9218240777938458</v>
+        <v>0.9222494765015478</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.007338187549231866</v>
+        <v>0.007318194732568614</v>
       </c>
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
-        <v>0.8636514196420016</v>
+        <v>0.8654124041024618</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.007004236752120719</v>
+        <v>0.006958858806779673</v>
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="n">
-        <v>0.9872474183398596</v>
+        <v>0.9882558302454952</v>
       </c>
       <c r="AM75" t="n">
-        <v>0.0006943506291843446</v>
+        <v>0.0006663324087990279</v>
       </c>
       <c r="AN75" t="inlineStr"/>
     </row>
@@ -8418,10 +8418,10 @@
         <v>0.03136066852465918</v>
       </c>
       <c r="K76" t="n">
-        <v>0.5259650027132444</v>
+        <v>0.543770931818184</v>
       </c>
       <c r="L76" t="n">
-        <v>0.5298880753788606</v>
+        <v>0.5537060846224899</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -8430,16 +8430,16 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>4.249893838573551</v>
+        <v>4.439776253946184</v>
       </c>
       <c r="P76" t="n">
-        <v>4.215857230931703</v>
+        <v>4.395647657598982</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.992705438661879</v>
+        <v>0.9927073085664859</v>
       </c>
       <c r="R76" t="n">
-        <v>0.005359321791017452</v>
+        <v>0.005358634836562376</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -8449,38 +8449,38 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>0.9144597113868075</v>
+        <v>0.9143295704973174</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.008321203624639704</v>
+        <v>0.008327531153341478</v>
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
-        <v>0.9201866785437895</v>
+        <v>0.9189787060359157</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.0007789028547092183</v>
+        <v>0.0007847750562913786</v>
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="n">
-        <v>0.9596490039943465</v>
+        <v>0.9597230179488534</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.008479840325159993</v>
+        <v>0.00847205966732008</v>
       </c>
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
-        <v>0.9883892910938183</v>
+        <v>0.9883601661096005</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.000905622857667056</v>
+        <v>0.0009067580050309622</v>
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="n">
-        <v>0.6813272950079535</v>
+        <v>0.6879495991187494</v>
       </c>
       <c r="AM76" t="n">
-        <v>0.001017195250698156</v>
+        <v>0.001006570649746</v>
       </c>
       <c r="AN76" t="inlineStr"/>
     </row>
@@ -8522,10 +8522,10 @@
         <v>0.02805201336700053</v>
       </c>
       <c r="K77" t="n">
-        <v>0.5107448989191544</v>
+        <v>0.4954473192373093</v>
       </c>
       <c r="L77" t="n">
-        <v>0.5733277688533781</v>
+        <v>0.5482686032782675</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -8534,16 +8534,16 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4.469822402045478</v>
+        <v>4.299272883877356</v>
       </c>
       <c r="P77" t="n">
-        <v>4.564221517389679</v>
+        <v>4.371525967068971</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.9771707196558915</v>
+        <v>0.9767796259190831</v>
       </c>
       <c r="R77" t="n">
-        <v>0.009060541560354237</v>
+        <v>0.009137821119754757</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -8553,38 +8553,38 @@
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>0.8283378591663131</v>
+        <v>0.8215885909469113</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.007548619914390963</v>
+        <v>0.007695584440325635</v>
       </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
-        <v>-3.740917650513611</v>
+        <v>-3.620114111636158</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.002129297848354373</v>
+        <v>0.00210199442831366</v>
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="n">
-        <v>0.9103370477295625</v>
+        <v>0.9072882482877223</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.01298062096364481</v>
+        <v>0.0131994654869828</v>
       </c>
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
-        <v>0.1932789150771066</v>
+        <v>0.1970902304960034</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.01341302947282749</v>
+        <v>0.01338130735097165</v>
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="n">
-        <v>0.8937692136070039</v>
+        <v>0.8883987431838454</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.0007386573324834917</v>
+        <v>0.0007570984514043576</v>
       </c>
       <c r="AN77" t="inlineStr"/>
     </row>
@@ -8626,10 +8626,10 @@
         <v>0.01052672116974796</v>
       </c>
       <c r="K78" t="n">
-        <v>0.4915367798062172</v>
+        <v>0.4805966135072757</v>
       </c>
       <c r="L78" t="n">
-        <v>0.5773511869453958</v>
+        <v>0.5547396320628748</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -8638,16 +8638,16 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>4.592870244659815</v>
+        <v>4.450858392300603</v>
       </c>
       <c r="P78" t="n">
-        <v>4.62658162052657</v>
+        <v>4.449312526961258</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.9827572809495235</v>
+        <v>0.9825247110262895</v>
       </c>
       <c r="R78" t="n">
-        <v>0.009535309364245398</v>
+        <v>0.009599400135841075</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -8657,38 +8657,38 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="n">
-        <v>0.3580014629203405</v>
+        <v>0.3531126832467799</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.00971326621655003</v>
+        <v>0.009750179042274446</v>
       </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
-        <v>0.159869505639033</v>
+        <v>0.1737835108794157</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.001072112313315747</v>
+        <v>0.001063197235471501</v>
       </c>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="n">
-        <v>0.8858676781376549</v>
+        <v>0.8835301692370344</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.01389311042032773</v>
+        <v>0.01403465959329246</v>
       </c>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
-        <v>-0.469249646625624</v>
+        <v>-0.4823378456373797</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.01276984859842668</v>
+        <v>0.01282659993310616</v>
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="n">
-        <v>-0.3881665501416753</v>
+        <v>-0.4003650099827274</v>
       </c>
       <c r="AM78" t="n">
-        <v>0.001739571089445828</v>
+        <v>0.001747197578538527</v>
       </c>
       <c r="AN78" t="inlineStr"/>
     </row>
@@ -8730,10 +8730,10 @@
         <v>3.234988232153624e-17</v>
       </c>
       <c r="K79" t="n">
-        <v>0.5515163866565659</v>
+        <v>0.5610550899029443</v>
       </c>
       <c r="L79" t="n">
-        <v>0.5597358919004219</v>
+        <v>0.5628967104249973</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -8742,58 +8742,58 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.375531902801428</v>
+        <v>4.446570697558703</v>
       </c>
       <c r="P79" t="n">
-        <v>4.436745638812805</v>
+        <v>4.460283018455883</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.9810915793406919</v>
+        <v>0.982243384299494</v>
       </c>
       <c r="R79" t="n">
-        <v>0.02022731371680062</v>
+        <v>0.01960156198295226</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
-        <v>0.917683960597017</v>
+        <v>0.9236410073665533</v>
       </c>
       <c r="U79" t="n">
-        <v>0.04456378051768834</v>
+        <v>0.04292100560411066</v>
       </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="n">
-        <v>0.6982275188905437</v>
+        <v>0.6981942464365025</v>
       </c>
       <c r="X79" t="n">
-        <v>0.001546068265304778</v>
+        <v>0.001546153495189306</v>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>0.9863612624336334</v>
+        <v>0.9839019855367579</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.009126954050928308</v>
+        <v>0.009915735517281758</v>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
-        <v>0.8740663970732334</v>
+        <v>0.874554951078451</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.00268213465456372</v>
+        <v>0.002676926985810397</v>
       </c>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="n">
-        <v>0.9897139566822728</v>
+        <v>0.988746861923252</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.003254008125341544</v>
+        <v>0.003403543318451284</v>
       </c>
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
-        <v>0.8978384099379954</v>
+        <v>0.895514667962212</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.008541232315438943</v>
+        <v>0.008637824505324111</v>
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         <v>7.592549229303372e-17</v>
       </c>
       <c r="K80" t="n">
-        <v>0.5606867247544488</v>
+        <v>0.5606777633938705</v>
       </c>
       <c r="L80" t="n">
-        <v>0.562908825353038</v>
+        <v>0.5620907024490294</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -8850,58 +8850,58 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.443827784785064</v>
+        <v>4.54003655508906</v>
       </c>
       <c r="P80" t="n">
-        <v>4.460373221667973</v>
+        <v>4.456206201223724</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.9950738576752266</v>
+        <v>0.9956428303795127</v>
       </c>
       <c r="R80" t="n">
-        <v>0.009700938164374411</v>
+        <v>0.009123521339572144</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="n">
-        <v>0.9836933130028076</v>
+        <v>0.9860021967035142</v>
       </c>
       <c r="U80" t="n">
-        <v>0.0202780996934044</v>
+        <v>0.01878773082974619</v>
       </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="n">
-        <v>0.9830116545067298</v>
+        <v>0.9828196059631479</v>
       </c>
       <c r="X80" t="n">
-        <v>0.0003486490581334399</v>
+        <v>0.0003506142104155993</v>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>0.9871536329367077</v>
+        <v>0.9869570965409913</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.007276969947927941</v>
+        <v>0.00733242378844812</v>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>0.984768046494358</v>
+        <v>0.9847105974336611</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.001026881559214551</v>
+        <v>0.001028816237539852</v>
       </c>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="n">
-        <v>0.9894722307648089</v>
+        <v>0.9892340751087918</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.005442304089175806</v>
+        <v>0.005503516828303766</v>
       </c>
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
-        <v>0.9870288496878931</v>
+        <v>0.9864324608827842</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.003731253531068583</v>
+        <v>0.003816067557802077</v>
       </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
@@ -8946,10 +8946,10 @@
         <v>9.901399624920571e-18</v>
       </c>
       <c r="K81" t="n">
-        <v>0.40758718491556</v>
+        <v>0.4048865563859553</v>
       </c>
       <c r="L81" t="n">
-        <v>0.5545990570078008</v>
+        <v>0.5485342861325764</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -8958,54 +8958,54 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>4.554087837697824</v>
+        <v>4.610890896156159</v>
       </c>
       <c r="P81" t="n">
-        <v>4.552486445287244</v>
+        <v>4.50798211336803</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.9936880128588121</v>
+        <v>0.9935903263366648</v>
       </c>
       <c r="R81" t="n">
-        <v>0.01079690865154443</v>
+        <v>0.01088013624163685</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="n">
-        <v>0.9811113799817824</v>
+        <v>0.9808214000644143</v>
       </c>
       <c r="U81" t="n">
-        <v>0.0205962227895499</v>
+        <v>0.02075371822057495</v>
       </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>0.9845487607130791</v>
+        <v>0.984272054509954</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.008192335544711748</v>
+        <v>0.008265365640124717</v>
       </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
-        <v>0.9598748118813727</v>
+        <v>0.9586624166745832</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.001216364057016891</v>
+        <v>0.001234603714788191</v>
       </c>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="n">
-        <v>0.9730430659575827</v>
+        <v>0.9727833946089174</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.005267421681227811</v>
+        <v>0.005292730945256697</v>
       </c>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
-        <v>0.9735147259383083</v>
+        <v>0.9730921609198954</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.007894438205976526</v>
+        <v>0.007957165754681318</v>
       </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
@@ -9050,10 +9050,10 @@
         <v>1.336850539002381e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2997988150084465</v>
+        <v>0.2917254962962554</v>
       </c>
       <c r="L82" t="n">
-        <v>0.5118295548648562</v>
+        <v>0.5166499751550074</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -9062,54 +9062,54 @@
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>4.554008665274212</v>
+        <v>4.60546490597388</v>
       </c>
       <c r="P82" t="n">
-        <v>4.544555992215201</v>
+        <v>4.601134779146905</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.9788127290369275</v>
+        <v>0.9806319072772055</v>
       </c>
       <c r="R82" t="n">
-        <v>0.01963552751675858</v>
+        <v>0.01877364021631047</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="n">
-        <v>0.943567057975677</v>
+        <v>0.9507780796374334</v>
       </c>
       <c r="U82" t="n">
-        <v>0.03708875805619967</v>
+        <v>0.03463819251382697</v>
       </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>0.9403397861054531</v>
+        <v>0.9385329377813838</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.01635479304580003</v>
+        <v>0.01660060355951193</v>
       </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
-        <v>-0.4512819632076477</v>
+        <v>-0.4500396261437978</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.003535738704930115</v>
+        <v>0.003534225036395271</v>
       </c>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="n">
-        <v>0.7950852229962224</v>
+        <v>0.7940999877192783</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.01628569944508209</v>
+        <v>0.01632480351941912</v>
       </c>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
-        <v>0.9974966203758107</v>
+        <v>0.9971798253213455</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.002643675467897485</v>
+        <v>0.002805968484642784</v>
       </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
@@ -9152,10 +9152,10 @@
         <v>0.002282733977536599</v>
       </c>
       <c r="K83" t="n">
-        <v>0.4674705519403926</v>
+        <v>0.5433397409012656</v>
       </c>
       <c r="L83" t="n">
-        <v>0.5637303949630073</v>
+        <v>0.5678007693909581</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -9164,54 +9164,54 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4.516876761044007</v>
+        <v>4.643199327406445</v>
       </c>
       <c r="P83" t="n">
-        <v>4.484674883652117</v>
+        <v>4.506586517990205</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.976671358583673</v>
+        <v>0.9773604326208327</v>
       </c>
       <c r="R83" t="n">
-        <v>0.01828636991596875</v>
+        <v>0.01801427710008432</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="n">
-        <v>0.9257838627496888</v>
+        <v>0.9288854542269736</v>
       </c>
       <c r="U83" t="n">
-        <v>0.03530673521000107</v>
+        <v>0.0345611040369481</v>
       </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>0.955743407128399</v>
+        <v>0.955749412226038</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.01014436978949946</v>
+        <v>0.01014368153048852</v>
       </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
-        <v>0.666563259157845</v>
+        <v>0.6714075996782407</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.006453837124905376</v>
+        <v>0.006406783260828276</v>
       </c>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="n">
-        <v>0.9250069980987885</v>
+        <v>0.9248154943371998</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.01051240954618392</v>
+        <v>0.01052582334709004</v>
       </c>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
-        <v>0.8774519913834061</v>
+        <v>0.8752597591225428</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.01305067300186046</v>
+        <v>0.01316688577694108</v>
       </c>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
@@ -9254,10 +9254,10 @@
         <v>0.001579598306755124</v>
       </c>
       <c r="K84" t="n">
-        <v>0.3117458209363655</v>
+        <v>0.3162631075751625</v>
       </c>
       <c r="L84" t="n">
-        <v>0.529637211818053</v>
+        <v>0.5351320396311876</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -9266,54 +9266,54 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>4.44868884650036</v>
+        <v>4.586521951223069</v>
       </c>
       <c r="P84" t="n">
-        <v>4.40868238081008</v>
+        <v>4.464050665003252</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.998239493582045</v>
+        <v>0.9983855038885692</v>
       </c>
       <c r="R84" t="n">
-        <v>0.004927306190447385</v>
+        <v>0.004718557440247502</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="n">
-        <v>0.998645630468854</v>
+        <v>0.999198213570286</v>
       </c>
       <c r="U84" t="n">
-        <v>0.004922115004490007</v>
+        <v>0.003787150114489743</v>
       </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>0.9904574363923625</v>
+        <v>0.9902632093078262</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.006664446953739852</v>
+        <v>0.00673192859624555</v>
       </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
-        <v>0.9629647243800461</v>
+        <v>0.9644759828324329</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.00174232948357663</v>
+        <v>0.001706410563302213</v>
       </c>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="n">
-        <v>0.9710657838691495</v>
+        <v>0.9715663539084161</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.00701048344133933</v>
+        <v>0.006949577205247874</v>
       </c>
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
-        <v>0.9994534474605852</v>
+        <v>0.9995623387168208</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.0007530418612761321</v>
+        <v>0.0006738639534036706</v>
       </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -9356,10 +9356,10 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.502344907933708</v>
+        <v>0.4976135263187853</v>
       </c>
       <c r="L85" t="n">
-        <v>0.5569070718026026</v>
+        <v>0.5644886621821832</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -9368,54 +9368,54 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>4.429178952661008</v>
+        <v>4.548143428306743</v>
       </c>
       <c r="P85" t="n">
-        <v>4.428985127463545</v>
+        <v>4.489765718580981</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.9918898298147617</v>
+        <v>0.9938663389452655</v>
       </c>
       <c r="R85" t="n">
-        <v>0.01125488992159682</v>
+        <v>0.009787824069591307</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="n">
-        <v>0.9718988881590083</v>
+        <v>0.9810790972934864</v>
       </c>
       <c r="U85" t="n">
-        <v>0.02152107844242206</v>
+        <v>0.01765928863517425</v>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="n">
-        <v>0.9871093154611723</v>
+        <v>0.9883479579565141</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.008749467816058237</v>
+        <v>0.008318493263601066</v>
       </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
-        <v>0.7530880744307676</v>
+        <v>0.7560744652676666</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.007764946457410194</v>
+        <v>0.007717845228511201</v>
       </c>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="n">
-        <v>0.9700650437746479</v>
+        <v>0.9688679758640638</v>
       </c>
       <c r="AG85" t="n">
-        <v>0.005588148782308686</v>
+        <v>0.005698785702661338</v>
       </c>
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="n">
-        <v>0.9973845111665076</v>
+        <v>0.9927357984343882</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.001459770888708595</v>
+        <v>0.00243277647005917</v>
       </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
@@ -9458,10 +9458,10 @@
         <v>0.001282293415705915</v>
       </c>
       <c r="K86" t="n">
-        <v>0.4868109864264576</v>
+        <v>0.5001855836882525</v>
       </c>
       <c r="L86" t="n">
-        <v>0.5542196708588537</v>
+        <v>0.5639737205055934</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -9470,54 +9470,54 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4.469780948890098</v>
+        <v>4.655189285584574</v>
       </c>
       <c r="P86" t="n">
-        <v>4.411774395081101</v>
+        <v>4.489666769931012</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.9945584432696085</v>
+        <v>0.9959748287961132</v>
       </c>
       <c r="R86" t="n">
-        <v>0.008797971009404845</v>
+        <v>0.007566815146635277</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="n">
-        <v>0.9874355059334551</v>
+        <v>0.9927018621214131</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01558088221204589</v>
+        <v>0.01187478003392466</v>
       </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
-        <v>0.9964691064190591</v>
+        <v>0.996496038256767</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.003456448580391664</v>
+        <v>0.003443241342889964</v>
       </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
-        <v>0.6028925478050606</v>
+        <v>0.6186588172610236</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.009432597118473071</v>
+        <v>0.009243450533327643</v>
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="n">
-        <v>0.9912729880846731</v>
+        <v>0.9904405870625187</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.004776132516173057</v>
+        <v>0.004998724419040988</v>
       </c>
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
-        <v>0.9805670859621561</v>
+        <v>0.978234866820092</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.004530475902775455</v>
+        <v>0.004794634703256448</v>
       </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
@@ -9560,10 +9560,10 @@
         <v>1.327388309752159e-16</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1824219159392768</v>
+        <v>0.1801165461460996</v>
       </c>
       <c r="L87" t="n">
-        <v>0.492645100015865</v>
+        <v>0.5035595819689067</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -9572,54 +9572,54 @@
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>4.595558295125066</v>
+        <v>4.683999502138008</v>
       </c>
       <c r="P87" t="n">
-        <v>4.531934298034223</v>
+        <v>4.634575928036571</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9816880595436358</v>
+        <v>0.9840376906873116</v>
       </c>
       <c r="R87" t="n">
-        <v>0.01517035133696684</v>
+        <v>0.01416368685130138</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="n">
-        <v>0.9570253119215857</v>
+        <v>0.966041525995557</v>
       </c>
       <c r="U87" t="n">
-        <v>0.02687983208482459</v>
+        <v>0.02389429756705195</v>
       </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="n">
-        <v>0.9497391012847465</v>
+        <v>0.948935077828046</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.01253010826993595</v>
+        <v>0.01262993268470194</v>
       </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
-        <v>0.8834463513185151</v>
+        <v>0.8831468287147135</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.00400174819312061</v>
+        <v>0.004006886792308986</v>
       </c>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="n">
-        <v>0.8100166470916303</v>
+        <v>0.8090116094486198</v>
       </c>
       <c r="AG87" t="n">
-        <v>0.01540020773057147</v>
+        <v>0.01544088859105175</v>
       </c>
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="n">
-        <v>0.9928931972126003</v>
+        <v>0.9928407063740644</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.004241276402744552</v>
+        <v>0.00425691061898865</v>
       </c>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
@@ -9662,10 +9662,10 @@
         <v>1.912261794240524e-16</v>
       </c>
       <c r="K88" t="n">
-        <v>0.1719570752124408</v>
+        <v>0.1739893793974186</v>
       </c>
       <c r="L88" t="n">
-        <v>0.5385048594000243</v>
+        <v>0.5289535724632448</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -9674,54 +9674,54 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>4.602089508487431</v>
+        <v>4.663409450690607</v>
       </c>
       <c r="P88" t="n">
-        <v>4.606443005982453</v>
+        <v>4.538878988034735</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.9934025017701104</v>
+        <v>0.9926910668379216</v>
       </c>
       <c r="R88" t="n">
-        <v>0.009523121087223758</v>
+        <v>0.01002343689410575</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="n">
-        <v>0.9826452753466763</v>
+        <v>0.9794723805860036</v>
       </c>
       <c r="U88" t="n">
-        <v>0.01660367340255245</v>
+        <v>0.01805779057204282</v>
       </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="n">
-        <v>0.9828778930405275</v>
+        <v>0.9829718696440537</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.007403586502244249</v>
+        <v>0.007383240839219295</v>
       </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
-        <v>0.06845498223291624</v>
+        <v>0.06882594369813955</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.006020541761351087</v>
+        <v>0.006019342886717594</v>
       </c>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="n">
-        <v>0.9854501440793633</v>
+        <v>0.9852304917887408</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.003595328423703318</v>
+        <v>0.003622365251437063</v>
       </c>
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
-        <v>0.9644366247952311</v>
+        <v>0.965103940150055</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.008589575256107066</v>
+        <v>0.008508605726805693</v>
       </c>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
@@ -9764,10 +9764,10 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.2700881523524867</v>
+        <v>0.2744023045987236</v>
       </c>
       <c r="L89" t="n">
-        <v>0.5502165457719604</v>
+        <v>0.5396384876006752</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -9776,54 +9776,54 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>4.568276553466714</v>
+        <v>4.565818894645068</v>
       </c>
       <c r="P89" t="n">
-        <v>4.599963284257567</v>
+        <v>4.509829245498081</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.9977790733211689</v>
+        <v>0.9977408577930305</v>
       </c>
       <c r="R89" t="n">
-        <v>0.005576967002672004</v>
+        <v>0.005624743844317256</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="n">
-        <v>0.9976615359088992</v>
+        <v>0.9976048310363318</v>
       </c>
       <c r="U89" t="n">
-        <v>0.006608575109727023</v>
+        <v>0.006688220080037116</v>
       </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
-        <v>0.9994163980479122</v>
+        <v>0.9993522401326416</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.001841013088824713</v>
+        <v>0.001939570307149694</v>
       </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
-        <v>0.9139057918319314</v>
+        <v>0.911902219092205</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.002843557452913951</v>
+        <v>0.002876454600932586</v>
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="n">
-        <v>0.9951396615991948</v>
+        <v>0.9950895817913649</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.001693810845901503</v>
+        <v>0.001702514800958786</v>
       </c>
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="n">
-        <v>0.9529201607522533</v>
+        <v>0.9524244462078089</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.009873975713997798</v>
+        <v>0.009925822285172442</v>
       </c>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
@@ -9866,10 +9866,10 @@
         <v>0.03004752976171331</v>
       </c>
       <c r="K90" t="n">
-        <v>0.2009697586071757</v>
+        <v>0.2308034783562465</v>
       </c>
       <c r="L90" t="n">
-        <v>0.3927848806328323</v>
+        <v>0.4969469837414318</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -9878,54 +9878,54 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>4.174898420666395</v>
+        <v>4.504155908456531</v>
       </c>
       <c r="P90" t="n">
-        <v>3.529638818086289</v>
+        <v>4.287955954220703</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.9840157560602371</v>
+        <v>0.9851109387161933</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01671805836354857</v>
+        <v>0.01613516631784879</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
-        <v>0.9658169705094377</v>
+        <v>0.9678592635158081</v>
       </c>
       <c r="U90" t="n">
-        <v>0.02994271397320951</v>
+        <v>0.0290344630605909</v>
       </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
-        <v>0.9907457607336531</v>
+        <v>0.9923571513487364</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.01242726111180765</v>
+        <v>0.01129360753018157</v>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>0.820603516827949</v>
+        <v>0.7985577305534821</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.004825627421300963</v>
+        <v>0.005113545539360988</v>
       </c>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="n">
-        <v>0.9955813791539947</v>
+        <v>0.9869662170171315</v>
       </c>
       <c r="AG90" t="n">
-        <v>0.0005063065001342152</v>
+        <v>0.0008695716598774213</v>
       </c>
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="n">
-        <v>0.9866109024284322</v>
+        <v>0.9879562958590633</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.003792768093899103</v>
+        <v>0.003597167614908986</v>
       </c>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>

--- a/tables/Flexible CUE/Local_perf_matrix_protection_False_vo_False_CUE_False.xlsx
+++ b/tables/Flexible CUE/Local_perf_matrix_protection_False_vo_False_CUE_False.xlsx
@@ -653,25 +653,25 @@
         <v>70.85714285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.432164952517398</v>
+        <v>0.4321649524844555</v>
       </c>
       <c r="G2" t="n">
         <v>0.04480286738351254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2627803891781534</v>
+        <v>0.2627803892434106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2428872347095719</v>
+        <v>0.2428872346838566</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01736455621136393</v>
+        <v>0.01736455620476475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4820009970627345</v>
+        <v>0.4819862052836677</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5552417873022963</v>
+        <v>0.5552403078350914</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -680,16 +680,16 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.465606698018054</v>
+        <v>4.465607701141615</v>
       </c>
       <c r="P2" t="n">
-        <v>4.439419994930735</v>
+        <v>4.439419849459852</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9944747925766798</v>
+        <v>0.9944743053020207</v>
       </c>
       <c r="R2" t="n">
-        <v>0.004569174776725734</v>
+        <v>0.00456937625345568</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
@@ -699,38 +699,38 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.9962385148023404</v>
+        <v>0.9962373763757938</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00444766098947113</v>
+        <v>0.004448333988017097</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.9602885112983912</v>
+        <v>0.9602983221059959</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.001311216716686438</v>
+        <v>0.001311054737244471</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>0.9988116672678174</v>
+        <v>0.9988112662258869</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.001454498924824368</v>
+        <v>0.001454744338970607</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>0.9593854736932543</v>
+        <v>0.9593842869115153</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.008575504490409844</v>
+        <v>0.008575629778566098</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>0.9066936900173973</v>
+        <v>0.9066908545371569</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0009192093366300093</v>
+        <v>0.0009192232974435064</v>
       </c>
       <c r="AN2" t="inlineStr"/>
     </row>
@@ -757,25 +757,25 @@
         <v>82.71186440677965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4230480283044928</v>
+        <v>0.4230480283479805</v>
       </c>
       <c r="G3" t="n">
         <v>0.03838147280770231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3417824749441816</v>
+        <v>0.341782474747073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733633998846752</v>
+        <v>0.1733633999809309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02342462405894816</v>
+        <v>0.02342462411631339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4085894186420144</v>
+        <v>0.4085894689594561</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5338988315833292</v>
+        <v>0.5338988735093217</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -784,16 +784,16 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.378970833950168</v>
+        <v>4.378970778573013</v>
       </c>
       <c r="P3" t="n">
-        <v>4.397004243933332</v>
+        <v>4.397004270596634</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9912810293563251</v>
+        <v>0.9912810368166275</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005678091372530199</v>
+        <v>0.005678088942566369</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -803,38 +803,38 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9924031317098851</v>
+        <v>0.9924031314627175</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005600732625962754</v>
+        <v>0.005600732718027821</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>0.3878782706913023</v>
+        <v>0.3878716293310736</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.001915855245598459</v>
+        <v>0.001915865638833751</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>0.9835676470597937</v>
+        <v>0.9835676156849659</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.00621722866551922</v>
+        <v>0.006217234596164716</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0.8813375979691237</v>
+        <v>0.8813379676203343</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.008354232894866861</v>
+        <v>0.008354219888199274</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>0.5077790291095217</v>
+        <v>0.5077797985832715</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.002862578312022976</v>
+        <v>0.002862576079619989</v>
       </c>
       <c r="AN3" t="inlineStr"/>
     </row>
@@ -861,25 +861,25 @@
         <v>38.828125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5026131523004256</v>
+        <v>0.5026131523545405</v>
       </c>
       <c r="G4" t="n">
         <v>0.08176040369199321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1418117772088146</v>
+        <v>0.1418117771640022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2720282171617107</v>
+        <v>0.2720282171735377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001786449637055907</v>
+        <v>0.00178644961592619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5232701740216598</v>
+        <v>0.5232640989042529</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5629139573148427</v>
+        <v>0.5629137526179258</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.449533919724023</v>
+        <v>4.449531792817196</v>
       </c>
       <c r="P4" t="n">
-        <v>4.468232409487467</v>
+        <v>4.468232539789589</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9506522977372028</v>
+        <v>0.9506502652619999</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01453173726654724</v>
+        <v>0.01453203652298386</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -907,38 +907,38 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0.9634769067417481</v>
+        <v>0.9634720510671314</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01682756886500787</v>
+        <v>0.01682868742627642</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.8881326429492018</v>
+        <v>0.8881278024446404</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.004162552262481068</v>
+        <v>0.004162642318399921</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>0.3953107692851815</v>
+        <v>0.3953139638702818</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02530891427614309</v>
+        <v>0.02530884741829886</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0.9742154488976996</v>
+        <v>0.9742119587219065</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.00666058895579237</v>
+        <v>0.006661039726824245</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>0.7724473162864484</v>
+        <v>0.7724542784346344</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.002417351591745542</v>
+        <v>0.002417314612244816</v>
       </c>
       <c r="AN4" t="inlineStr"/>
     </row>
@@ -965,25 +965,25 @@
         <v>67.8082191780822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4142260612899763</v>
+        <v>0.414226061397911</v>
       </c>
       <c r="G5" t="n">
         <v>0.04681738015071348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2912830177383198</v>
+        <v>0.2912830175544637</v>
       </c>
       <c r="I5" t="n">
-        <v>0.217379291417003</v>
+        <v>0.2173792914645093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03029424940398749</v>
+        <v>0.03029424943240262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4069734038792392</v>
+        <v>0.4069735005006315</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5405343569984278</v>
+        <v>0.5405343764180063</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -992,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.328675728015952</v>
+        <v>4.328675634134481</v>
       </c>
       <c r="P5" t="n">
-        <v>4.405143033925619</v>
+        <v>4.405143032125637</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9953678993801566</v>
+        <v>0.9953678997924318</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004028345690172988</v>
+        <v>0.004028345510985809</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1011,38 +1011,38 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0.990483689694984</v>
+        <v>0.9904836906874467</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.006987179973030806</v>
+        <v>0.006987179610684475</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.9989863611164577</v>
+        <v>0.9989863519541978</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0001961989813094021</v>
+        <v>0.0001961998680265724</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0.9982509438660022</v>
+        <v>0.9982509434084936</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.001944089046974934</v>
+        <v>0.001944089299382716</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>0.9794091029029719</v>
+        <v>0.9794091055082044</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.004771018223504815</v>
+        <v>0.004771017922688331</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>0.9843504167260139</v>
+        <v>0.9843504175424571</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.00058327656437382</v>
+        <v>0.0005832765502539746</v>
       </c>
       <c r="AN5" t="inlineStr"/>
     </row>
@@ -1069,25 +1069,25 @@
         <v>77.65625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3890909284533883</v>
+        <v>0.3890909284112034</v>
       </c>
       <c r="G6" t="n">
         <v>0.0408802018459966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3036991224550851</v>
+        <v>0.3036991225960292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2478250703308909</v>
+        <v>0.2478250702399798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01850467691463906</v>
+        <v>0.01850467690679097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4592879234335376</v>
+        <v>0.4592879149818232</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5472917331264102</v>
+        <v>0.5472917506985611</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1096,16 +1096,16 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.385019187083561</v>
+        <v>4.385019195419657</v>
       </c>
       <c r="P6" t="n">
-        <v>4.422800524664928</v>
+        <v>4.422800573410375</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9788443631625323</v>
+        <v>0.9788443691741815</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008792723760540879</v>
+        <v>0.008792722510672497</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1115,38 +1115,38 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>0.9774437513737219</v>
+        <v>0.9774437234181179</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.008663166666407275</v>
+        <v>0.008663172032094093</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>0.7014166865362259</v>
+        <v>0.7014128431812319</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.001459434252392132</v>
+        <v>0.00145944364525774</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>0.9943083932971585</v>
+        <v>0.9943083234250074</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.003094289415119421</v>
+        <v>0.003094308411266494</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0.7414976022624304</v>
+        <v>0.7414979118046522</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01651761085917213</v>
+        <v>0.01651760096034717</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>0.6555228832738873</v>
+        <v>0.6555236710945043</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001383030805378332</v>
+        <v>0.001383029226901241</v>
       </c>
       <c r="AN6" t="inlineStr"/>
     </row>
@@ -1173,25 +1173,25 @@
         <v>66.19718309859155</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4886958146778536</v>
+        <v>0.4886958146760266</v>
       </c>
       <c r="G7" t="n">
         <v>0.04795677136102667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2566075839924613</v>
+        <v>0.2566075840123206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893475641758934</v>
+        <v>0.1893475641544703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01739226579276497</v>
+        <v>0.01739226579615577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3951965360399166</v>
+        <v>0.3952111644541383</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5363504762467854</v>
+        <v>0.5363539733151907</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1200,16 +1200,16 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.421262405329895</v>
+        <v>4.421257329219673</v>
       </c>
       <c r="P7" t="n">
-        <v>4.403178102079354</v>
+        <v>4.40317716128641</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9889147946947516</v>
+        <v>0.9889147678787027</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006397094205014504</v>
+        <v>0.006397101942615954</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1219,38 +1219,38 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0.9936297453898858</v>
+        <v>0.993629181885275</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00605563695977519</v>
+        <v>0.006055904790758963</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>0.7254342038383648</v>
+        <v>0.7253202564494212</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.00226063356283661</v>
+        <v>0.002261102606277342</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>0.9148038736101707</v>
+        <v>0.9148060011516272</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01163604144036334</v>
+        <v>0.01163589615343508</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>0.9997999877120718</v>
+        <v>0.9998003986564609</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0003724190291040825</v>
+        <v>0.0003720362469933054</v>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>0.4489140084527502</v>
+        <v>0.4489330145244766</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.003919089416676367</v>
+        <v>0.003919021834371615</v>
       </c>
       <c r="AN7" t="inlineStr"/>
     </row>
@@ -1277,25 +1277,25 @@
         <v>66.66666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3735503885622976</v>
+        <v>0.3735503886646729</v>
       </c>
       <c r="G8" t="n">
         <v>0.04761904761904761</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3017797553926043</v>
+        <v>0.3017797550644881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2489905948482005</v>
+        <v>0.2489905949934041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02806021357785015</v>
+        <v>0.02806021365838738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.268136507449542</v>
+        <v>0.2681364660808555</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5105187857826707</v>
+        <v>0.5105187609812849</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1304,16 +1304,16 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.51057323281028</v>
+        <v>4.510573300984529</v>
       </c>
       <c r="P8" t="n">
-        <v>4.426334150274576</v>
+        <v>4.426334149748979</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9975099783380402</v>
+        <v>0.9975099796565072</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002688248654129973</v>
+        <v>0.002688247942082091</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1323,38 +1323,38 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.9976797010488034</v>
+        <v>0.9976797013841122</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003214234847810291</v>
+        <v>0.003214234616720709</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0.9990352008491494</v>
+        <v>0.9990351698025722</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0002038804358955573</v>
+        <v>0.000203883716235698</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>0.9922035497969649</v>
+        <v>0.9922035530410555</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.00437227011269687</v>
+        <v>0.004372269196587643</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>0.9976364609288585</v>
+        <v>0.9976364660329947</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.002058559229929922</v>
+        <v>0.002058557008746462</v>
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>0.9991695496174474</v>
+        <v>0.9991695583074941</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0001052679289410292</v>
+        <v>0.0001052673785906278</v>
       </c>
       <c r="AN8" t="inlineStr"/>
     </row>
@@ -1381,25 +1381,25 @@
         <v>69.85074626865672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4184346509008527</v>
+        <v>0.4184346509642805</v>
       </c>
       <c r="G9" t="n">
         <v>0.0454483787817121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2664295170187482</v>
+        <v>0.2664295168783421</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2311091971008347</v>
+        <v>0.2311091971723147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03857825619785213</v>
+        <v>0.03857825620335059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3433990727769944</v>
+        <v>0.3433996615356982</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5299311480446058</v>
+        <v>0.5299313016930907</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1408,16 +1408,16 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.328025721001465</v>
+        <v>4.328025823301873</v>
       </c>
       <c r="P9" t="n">
-        <v>4.403087255273483</v>
+        <v>4.403087288611972</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9948676406085433</v>
+        <v>0.9948676569205339</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003874540425934272</v>
+        <v>0.003874534268907652</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1427,38 +1427,38 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>0.9979411002973234</v>
+        <v>0.9979411068912065</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003275156189782787</v>
+        <v>0.003275150945787482</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>0.9848790867840327</v>
+        <v>0.9848785139506704</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0007042336985623501</v>
+        <v>0.0007042470378604159</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>0.9996126815556319</v>
+        <v>0.9996126853757995</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0007963465678934915</v>
+        <v>0.000796342640208028</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0.9596121762703047</v>
+        <v>0.959612310622733</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.007582753387835984</v>
+        <v>0.007582740777703983</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>0.9760244387394468</v>
+        <v>0.9760245309556149</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0009309680218611799</v>
+        <v>0.0009309662313967786</v>
       </c>
       <c r="AN9" t="inlineStr"/>
     </row>
@@ -1485,25 +1485,25 @@
         <v>52.61363636363636</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5306916825504616</v>
+        <v>0.5306916826579526</v>
       </c>
       <c r="G10" t="n">
         <v>0.0603380301004491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2597511503162143</v>
+        <v>0.2597511501438604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115376694226804</v>
+        <v>0.1153766942703101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.033842442806071</v>
+        <v>0.03384244282742767</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4233368867748208</v>
+        <v>0.4233319440240271</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5368853434172393</v>
+        <v>0.5368846750198718</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1512,16 +1512,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.304645472857671</v>
+        <v>4.304645875259564</v>
       </c>
       <c r="P10" t="n">
-        <v>4.33060537101248</v>
+        <v>4.330605357010606</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9895904479407066</v>
+        <v>0.9895903379811851</v>
       </c>
       <c r="R10" t="n">
-        <v>0.006481064277497743</v>
+        <v>0.0064810985086887</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1531,38 +1531,38 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>0.9945301041090884</v>
+        <v>0.9945298838759494</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.006541850526688699</v>
+        <v>0.006541982223702605</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.9714908552012521</v>
+        <v>0.9714942019623921</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.001411289385638165</v>
+        <v>0.001411206545778655</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>0.9149649237569403</v>
+        <v>0.9149646249564235</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01192361473454799</v>
+        <v>0.01192363567148878</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>0.984540880661173</v>
+        <v>0.9845410312867434</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.00196716917621053</v>
+        <v>0.001967159594947597</v>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>0.8441116167086151</v>
+        <v>0.8441105029191325</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.002419420677825814</v>
+        <v>0.002419429322517659</v>
       </c>
       <c r="AN10" t="inlineStr"/>
     </row>
@@ -1589,25 +1589,25 @@
         <v>61.69014084507042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6976459379986636</v>
+        <v>0.6976459379735106</v>
       </c>
       <c r="G11" t="n">
         <v>0.05146046241936653</v>
       </c>
       <c r="H11" t="n">
-        <v>0.128689928922737</v>
+        <v>0.1286899289623047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09261029160041566</v>
+        <v>0.09261029157801856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02959337905881725</v>
+        <v>0.02959337906679948</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2019906136872595</v>
+        <v>0.2020093881041004</v>
       </c>
       <c r="L11" t="n">
-        <v>0.488964981036407</v>
+        <v>0.4889699963867177</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.107405143193574</v>
+        <v>4.107412849525095</v>
       </c>
       <c r="P11" t="n">
-        <v>4.301992946457993</v>
+        <v>4.301993202211461</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9961012423631244</v>
+        <v>0.9961002070411327</v>
       </c>
       <c r="R11" t="n">
-        <v>0.004645202717819015</v>
+        <v>0.00464581944760565</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
@@ -1635,38 +1635,38 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>0.9943218360160239</v>
+        <v>0.9943201483696682</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.009421379655970605</v>
+        <v>0.009422779647772892</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>0.9842165642901131</v>
+        <v>0.9842282415637192</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0008849066800338916</v>
+        <v>0.0008845792732014403</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>0.9747907639518012</v>
+        <v>0.9747903624401022</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.00281448347248342</v>
+        <v>0.002814505887938757</v>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>0.9744648824350942</v>
+        <v>0.9744600864546497</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.001795651291816801</v>
+        <v>0.001795819910900227</v>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>0.9851343996153678</v>
+        <v>0.9851336737753822</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.000516517243422968</v>
+        <v>0.0005165298529691546</v>
       </c>
       <c r="AN11" t="inlineStr"/>
     </row>
@@ -1693,25 +1693,25 @@
         <v>1182.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6580079528637066</v>
+        <v>0.658007952809377</v>
       </c>
       <c r="G12" t="n">
         <v>0.002684653847444545</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3185832282923884</v>
+        <v>0.3185832283714021</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0207241649964606</v>
+        <v>0.02072416497177636</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1800254501765517</v>
+        <v>0.1800254450734587</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4443168908743156</v>
+        <v>0.4443168380251787</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1720,16 +1720,16 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.004770333347373</v>
+        <v>4.004770596798982</v>
       </c>
       <c r="P12" t="n">
-        <v>4.237473647481432</v>
+        <v>4.237473685138769</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9410773032914407</v>
+        <v>0.9410773032563967</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02641822385660735</v>
+        <v>0.02641822386510781</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -1739,38 +1739,38 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>0.6683672584493268</v>
+        <v>0.6683672572421645</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.05692507389575106</v>
+        <v>0.05692507400029989</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>0.9027272373207247</v>
+        <v>0.9027281502155772</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0007324309726465548</v>
+        <v>0.0007324275357438952</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>0.9970237826874856</v>
+        <v>0.9970237943578035</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.002062889027689814</v>
+        <v>0.002062884983400878</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>0.380087920686467</v>
+        <v>0.3800873777703667</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.003420738987025546</v>
+        <v>0.003420740499580258</v>
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>0.9527713059643164</v>
+        <v>0.9527713333606218</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0004396213848865292</v>
+        <v>0.0004396212565413521</v>
       </c>
       <c r="AN12" t="inlineStr"/>
     </row>
@@ -1797,25 +1797,25 @@
         <v>37.30769230769231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3764292995365501</v>
+        <v>0.3764292995885038</v>
       </c>
       <c r="G13" t="n">
         <v>0.08509245622647683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.20530781079537</v>
+        <v>0.2053078106416003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2773838130683605</v>
+        <v>0.2773838131849478</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05578662037324268</v>
+        <v>0.0557866203584713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2835460062602018</v>
+        <v>0.2835459920369253</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4773095883176129</v>
+        <v>0.4773095750817874</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.337432442552224</v>
+        <v>4.337432423540404</v>
       </c>
       <c r="P13" t="n">
-        <v>4.486751702679427</v>
+        <v>4.486751697172535</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.997430907495605</v>
+        <v>0.9974309074020913</v>
       </c>
       <c r="R13" t="n">
-        <v>0.002900564965026711</v>
+        <v>0.002900565019288114</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
@@ -1843,38 +1843,38 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>0.7892126951811221</v>
+        <v>0.7892126883270607</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.003619786756878538</v>
+        <v>0.00361978679632158</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>0.9226657016107024</v>
+        <v>0.9226658691613587</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0002129693540070737</v>
+        <v>0.0002129691232997736</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>0.5703327598775618</v>
+        <v>0.5703327483296623</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.004687356371582459</v>
+        <v>0.004687356418732767</v>
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>0.9980023906434857</v>
+        <v>0.9980023901717711</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.001805673225688144</v>
+        <v>0.001805673443523383</v>
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>0.9642173223016289</v>
+        <v>0.9642173205849192</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.001920002062108499</v>
+        <v>0.001920002103229392</v>
       </c>
       <c r="AN13" t="inlineStr"/>
     </row>
@@ -1901,25 +1901,25 @@
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4685666630154797</v>
+        <v>0.4685666629631464</v>
       </c>
       <c r="G14" t="n">
         <v>0.07215007215007214</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2791093997172449</v>
+        <v>0.2791093997308827</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1713546933726054</v>
+        <v>0.1713546934252931</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008819171744597891</v>
+        <v>0.008819171730605837</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3546715346376434</v>
+        <v>0.3546629830233172</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5125020839216102</v>
+        <v>0.5124977300184471</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1928,16 +1928,16 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.399848195776872</v>
+        <v>4.399847587477812</v>
       </c>
       <c r="P14" t="n">
-        <v>4.399284891722037</v>
+        <v>4.399284580198001</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9808980916435969</v>
+        <v>0.9808984193725632</v>
       </c>
       <c r="R14" t="n">
-        <v>0.008230638921544527</v>
+        <v>0.008230568313953796</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
@@ -1947,38 +1947,38 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>0.9586695052028485</v>
+        <v>0.9586716175308446</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01010808127544982</v>
+        <v>0.01010782296656785</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>-0.01755876794622058</v>
+        <v>-0.01736609965096325</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.004947050423578544</v>
+        <v>0.004946582055105045</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>0.9947811780839491</v>
+        <v>0.9947816674082327</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.003122159897654537</v>
+        <v>0.003122013524013514</v>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>0.6090519836469908</v>
+        <v>0.6090423900193036</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01412907558811348</v>
+        <v>0.01412924898964926</v>
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>0.3093965431773571</v>
+        <v>0.3093815735309196</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.001640673922064961</v>
+        <v>0.001640691697519511</v>
       </c>
       <c r="AN14" t="inlineStr"/>
     </row>
@@ -2005,25 +2005,25 @@
         <v>37.66666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4676168791864762</v>
+        <v>0.467616879374457</v>
       </c>
       <c r="G15" t="n">
         <v>0.08428150021070376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2808036479653256</v>
+        <v>0.280803647842334</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1470517109277883</v>
+        <v>0.1470517108760386</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02024626170970604</v>
+        <v>0.02024626169646662</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4107507024762867</v>
+        <v>0.4107503650737578</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5344814196982085</v>
+        <v>0.5344814045997159</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2032,16 +2032,16 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.081381386375272</v>
+        <v>4.081379451844411</v>
       </c>
       <c r="P15" t="n">
-        <v>4.337686579085906</v>
+        <v>4.337686575872048</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9802340964444202</v>
+        <v>0.9802340990115765</v>
       </c>
       <c r="R15" t="n">
-        <v>0.007429882876421959</v>
+        <v>0.007429882391808041</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
@@ -2051,38 +2051,38 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>0.9527527489513464</v>
+        <v>0.9527527597767624</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01070319571484254</v>
+        <v>0.01070319452210794</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>-1.593308484446893</v>
+        <v>-1.593309622403957</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.00421392671622727</v>
+        <v>0.004213927640773497</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
-        <v>0.9252657222484987</v>
+        <v>0.9252657218522673</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.01001021660364923</v>
+        <v>0.01001021659688614</v>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>0.7996522487895394</v>
+        <v>0.7996523774375637</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.005009464162135962</v>
+        <v>0.005009462591647056</v>
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>0.9999999915323877</v>
+        <v>0.9999999910519988</v>
       </c>
       <c r="AM15" t="n">
-        <v>3.405177741922873e-07</v>
+        <v>3.50043746883249e-07</v>
       </c>
       <c r="AN15" t="inlineStr"/>
     </row>
@@ -2109,25 +2109,25 @@
         <v>21.39130434782609</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3751087963773801</v>
+        <v>0.3751087964018581</v>
       </c>
       <c r="G16" t="n">
         <v>0.1484062459672215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06809149804835848</v>
+        <v>0.06809149804106746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3926949046640935</v>
+        <v>0.3926949046425352</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01569855494294647</v>
+        <v>0.01569855494731771</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5547407510209782</v>
+        <v>0.5547407800811401</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5733753977865961</v>
+        <v>0.5733754846439694</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.399547914881412</v>
+        <v>4.399548131317051</v>
       </c>
       <c r="P16" t="n">
-        <v>4.53828267416197</v>
+        <v>4.538283320590577</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9757558264078261</v>
+        <v>0.9757558261462026</v>
       </c>
       <c r="R16" t="n">
-        <v>0.009470351170750822</v>
+        <v>0.009470351221831196</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
@@ -2155,31 +2155,31 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>0.9946929737023286</v>
+        <v>0.9946929732411659</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.005370193034839947</v>
+        <v>0.005370193267869897</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>0.9590837394407519</v>
+        <v>0.9590837381243648</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.004169089230149025</v>
+        <v>0.004169089297214486</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="n">
-        <v>0.909418027163619</v>
+        <v>0.9094180286826921</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.003613765977076533</v>
+        <v>0.00361376594888901</v>
       </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
-        <v>0.8395852168630731</v>
+        <v>0.8395852161931516</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01814845648655414</v>
+        <v>0.01814845652331161</v>
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
@@ -2211,25 +2211,25 @@
         <v>51.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4780640258980272</v>
+        <v>0.478064025668827</v>
       </c>
       <c r="G17" t="n">
         <v>0.06194347657762291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2550441184335309</v>
+        <v>0.2550441188812936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1330574186338084</v>
+        <v>0.1330574185135598</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07189096045701066</v>
+        <v>0.07189096035869673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2331461754905137</v>
+        <v>0.2331500314999871</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4062482878535555</v>
+        <v>0.40625305577035</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2238,16 +2238,16 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.94020970433473</v>
+        <v>3.94021163738553</v>
       </c>
       <c r="P17" t="n">
-        <v>4.112155750684704</v>
+        <v>4.112159201074586</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9947024167975608</v>
+        <v>0.9947024176483411</v>
       </c>
       <c r="R17" t="n">
-        <v>0.003378593456150539</v>
+        <v>0.003378593184440084</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
@@ -2257,38 +2257,38 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>0.9868785875878128</v>
+        <v>0.98687864343465</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.005762654879482022</v>
+        <v>0.005762642612497132</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>0.5890808723036661</v>
+        <v>0.5890882853203534</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.001982552652961361</v>
+        <v>0.001982534770169843</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="n">
-        <v>0.9963180462165</v>
+        <v>0.9963180714514224</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.001641023833260421</v>
+        <v>0.00164101821326164</v>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>0.3562145935779377</v>
+        <v>0.3562060706911575</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.004129090585578979</v>
+        <v>0.004129117879941756</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>0.9979327370821336</v>
+        <v>0.9979327782243751</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0004397887477965621</v>
+        <v>0.000439784370701868</v>
       </c>
       <c r="AN17" t="inlineStr"/>
     </row>
@@ -2315,25 +2315,25 @@
         <v>31.46666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4515185462382498</v>
+        <v>0.451518546451847</v>
       </c>
       <c r="G18" t="n">
         <v>0.1008878127522195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2508910324934933</v>
+        <v>0.2508910318037907</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1666097192940944</v>
+        <v>0.1666097196951048</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03009288922194302</v>
+        <v>0.03009288929703804</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4237696658272739</v>
+        <v>0.4237696014838367</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5304037895712913</v>
+        <v>0.530403780099769</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2342,16 +2342,16 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.353516083339685</v>
+        <v>4.35351611582689</v>
       </c>
       <c r="P18" t="n">
-        <v>4.363447800770301</v>
+        <v>4.363447805655611</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9861562549579391</v>
+        <v>0.9861562551465345</v>
       </c>
       <c r="R18" t="n">
-        <v>0.00608506720647654</v>
+        <v>0.006085067164409911</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -2361,38 +2361,38 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>0.9334778426930815</v>
+        <v>0.9334778448262336</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.01324511368013147</v>
+        <v>0.01324511348540639</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>0.8537801254765851</v>
+        <v>0.8537800924792769</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.001053201247225721</v>
+        <v>0.001053201366063206</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.9967858202098074</v>
+        <v>0.9967858221334852</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.001701635273024805</v>
+        <v>0.001701634753776619</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
-        <v>0.9803187579769195</v>
+        <v>0.980318743219598</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.002360130900288685</v>
+        <v>0.002360131798676628</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.9906989875670851</v>
+        <v>0.9906989964766874</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.000363544771682573</v>
+        <v>0.0003635445993847857</v>
       </c>
       <c r="AN18" t="inlineStr"/>
     </row>
@@ -2419,25 +2419,25 @@
         <v>77.71428571428571</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2928786705374068</v>
+        <v>0.2928786705098768</v>
       </c>
       <c r="G19" t="n">
         <v>0.04084967320261438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2980196009674419</v>
+        <v>0.2980196010147655</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3557027147401188</v>
+        <v>0.3557027147337084</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01254934055241822</v>
+        <v>0.01254934053903507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4773272763108123</v>
+        <v>0.4773250445593811</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5574072554906462</v>
+        <v>0.5574072453265833</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.822055423832857</v>
+        <v>3.822038745202903</v>
       </c>
       <c r="P19" t="n">
-        <v>4.419352489123138</v>
+        <v>4.419352411426281</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9870541876666454</v>
+        <v>0.9870541906196574</v>
       </c>
       <c r="R19" t="n">
-        <v>0.008016573942401751</v>
+        <v>0.008016573028294841</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
@@ -2465,38 +2465,38 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>0.6848950318813257</v>
+        <v>0.6848951140536594</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.008358220443262567</v>
+        <v>0.008358219339019222</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>0.03396216730781076</v>
+        <v>0.03396202677281024</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.002928222868760106</v>
+        <v>0.002928223081752689</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="n">
-        <v>0.730598622594996</v>
+        <v>0.7305986738477065</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.01464972061570835</v>
+        <v>0.01464971923913307</v>
       </c>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
-        <v>0.7876204041426068</v>
+        <v>0.7876205222782522</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.005316784068055204</v>
+        <v>0.005316782589128178</v>
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>0.9987782087607665</v>
+        <v>0.9987782098396963</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.0001021948043493886</v>
+        <v>0.0001021947590405902</v>
       </c>
       <c r="AN19" t="inlineStr"/>
     </row>
@@ -2523,25 +2523,25 @@
         <v>55.77777777777778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3719943274037391</v>
+        <v>0.3719943273800574</v>
       </c>
       <c r="G20" t="n">
         <v>0.05691519635742743</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2459185029100323</v>
+        <v>0.2459185030013721</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3196907365948976</v>
+        <v>0.3196907365258876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.005481236733903614</v>
+        <v>0.005481236735255395</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4199137651576323</v>
+        <v>0.4199058580112651</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5466925142383374</v>
+        <v>0.5466893605565266</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2550,16 +2550,16 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.56912263600572</v>
+        <v>4.569123216151214</v>
       </c>
       <c r="P20" t="n">
-        <v>4.539899296940812</v>
+        <v>4.539901291242793</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9773210307689926</v>
+        <v>0.9773213166151525</v>
       </c>
       <c r="R20" t="n">
-        <v>0.008841406562354765</v>
+        <v>0.008841350844083058</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -2569,38 +2569,38 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>0.9181453483247343</v>
+        <v>0.918149079705689</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.008334703267227508</v>
+        <v>0.008334513289233444</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>0.6458088236668431</v>
+        <v>0.6458489495528938</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.004060949510058019</v>
+        <v>0.00406071947353604</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="n">
-        <v>0.9799087280024977</v>
+        <v>0.9799091295294856</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.003782322757568091</v>
+        <v>0.003782284967497278</v>
       </c>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>0.7848662162158422</v>
+        <v>0.7848659310253382</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.01703283557393487</v>
+        <v>0.0170328468711922</v>
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>0.474297474934772</v>
+        <v>0.4742864996929486</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.0006857896158134105</v>
+        <v>0.0006857967751743497</v>
       </c>
       <c r="AN20" t="inlineStr"/>
     </row>
@@ -2627,25 +2627,25 @@
         <v>17.60714285714286</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3926349948370401</v>
+        <v>0.3926349942752794</v>
       </c>
       <c r="G21" t="n">
         <v>0.1803020058598151</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3377870452012128</v>
+        <v>0.3377870456849771</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08927595410193191</v>
+        <v>0.08927595417992841</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.04831636563563e-18</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5119505968393867</v>
+        <v>0.5119505969026676</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5214040378706312</v>
+        <v>0.5214040378862334</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.080584583903153</v>
+        <v>4.080584584375281</v>
       </c>
       <c r="P21" t="n">
-        <v>4.151092398028675</v>
+        <v>4.15109239814509</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.9807245874358685</v>
+        <v>0.9807245874807303</v>
       </c>
       <c r="R21" t="n">
-        <v>0.009035299282911835</v>
+        <v>0.009035299271082077</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -2673,38 +2673,38 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>0.9293877291295994</v>
+        <v>0.9293877282785208</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.01043825431261878</v>
+        <v>0.01043825434415492</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>0.9960348199549983</v>
+        <v>0.9960348202929616</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.00207858561234625</v>
+        <v>0.002078585523764444</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="n">
-        <v>0.5037533632643423</v>
+        <v>0.5037533681207083</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.01542970426672279</v>
+        <v>0.015429704227928</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
-        <v>0.8043675129155022</v>
+        <v>0.8043675127348946</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.0075373420832216</v>
+        <v>0.007537342072434253</v>
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>0.9830011533144901</v>
+        <v>0.9830011525208797</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.0001348887621392687</v>
+        <v>0.0001348887652203537</v>
       </c>
       <c r="AN21" t="inlineStr"/>
     </row>
@@ -2731,25 +2731,25 @@
         <v>29.3125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4135808655857899</v>
+        <v>0.4135808655594087</v>
       </c>
       <c r="G22" t="n">
         <v>0.1083020272785731</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2033297621759581</v>
+        <v>0.203329762176548</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2477420255951969</v>
+        <v>0.247742025507402</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02704531936448205</v>
+        <v>0.02704531947806826</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3688714801677829</v>
+        <v>0.3688612018985629</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4915905589122538</v>
+        <v>0.4915808442177514</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2758,16 +2758,16 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.178478767273362</v>
+        <v>4.178475283245922</v>
       </c>
       <c r="P22" t="n">
-        <v>4.349919916238273</v>
+        <v>4.349916354228388</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9830007146267988</v>
+        <v>0.9830007861870178</v>
       </c>
       <c r="R22" t="n">
-        <v>0.006590847547054678</v>
+        <v>0.006590833675097332</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
@@ -2777,38 +2777,38 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>0.9114904021866279</v>
+        <v>0.9114914448124353</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.008770902827479245</v>
+        <v>0.008770851160486103</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>0.9250372431819808</v>
+        <v>0.925038294274361</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.001517548438356098</v>
+        <v>0.001517537799144979</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="n">
-        <v>0.3721034400398802</v>
+        <v>0.3721055215826546</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.01093705345332912</v>
+        <v>0.01093703534013991</v>
       </c>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>0.92563504737467</v>
+        <v>0.9256330268256607</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.003904727227574165</v>
+        <v>0.003904780259997677</v>
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
-        <v>0.8266467802751225</v>
+        <v>0.8266464248405426</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.001760293812977091</v>
+        <v>0.001760295629266259</v>
       </c>
       <c r="AN22" t="inlineStr"/>
     </row>
@@ -2835,25 +2835,25 @@
         <v>39.58333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6238519511711706</v>
+        <v>0.6238519513177977</v>
       </c>
       <c r="G23" t="n">
         <v>0.08020050125313281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2028318968739128</v>
+        <v>0.2028318965921395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06932561212208042</v>
+        <v>0.06932561224073039</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0237900385797033</v>
+        <v>0.02379003859619956</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3463056376458854</v>
+        <v>0.3463059500009534</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4947493563760101</v>
+        <v>0.494749451036993</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2862,16 +2862,16 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.869820336646796</v>
+        <v>3.869821613027207</v>
       </c>
       <c r="P23" t="n">
-        <v>4.218788295000432</v>
+        <v>4.218788367947586</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9830728547251535</v>
+        <v>0.9830728531222082</v>
       </c>
       <c r="R23" t="n">
-        <v>0.009740481252516593</v>
+        <v>0.009740481713516203</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2881,38 +2881,38 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>0.9045420264382695</v>
+        <v>0.9045420179012066</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.02166004282918055</v>
+        <v>0.02166004381702326</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>-1.107072089054323</v>
+        <v>-1.107074690230538</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.001386195989637312</v>
+        <v>0.001386196845265115</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="n">
-        <v>0.9895066042716104</v>
+        <v>0.9895065973340709</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.001725355880916715</v>
+        <v>0.00172535644279989</v>
       </c>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="n">
-        <v>0.9241904912760229</v>
+        <v>0.9241913173517975</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.0004470228277812744</v>
+        <v>0.0004470203976598611</v>
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
-        <v>0.9940474982743336</v>
+        <v>0.9940474996223176</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.0003594414349269529</v>
+        <v>0.0003594413956296579</v>
       </c>
       <c r="AN23" t="inlineStr"/>
     </row>
@@ -2939,25 +2939,25 @@
         <v>18.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5366376492551596</v>
+        <v>0.5366376495537714</v>
       </c>
       <c r="G24" t="n">
         <v>0.1688618709895305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1622397270835717</v>
+        <v>0.1622397269217724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1157024432834648</v>
+        <v>0.1157024431484001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01655830938827357</v>
+        <v>0.01655830938652574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5381273422429782</v>
+        <v>0.5381273409542512</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5469554563350643</v>
+        <v>0.5469554552120094</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2966,16 +2966,16 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.275774819085798</v>
+        <v>4.275774809481438</v>
       </c>
       <c r="P24" t="n">
-        <v>4.341554147160157</v>
+        <v>4.341554138793168</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9926953288581162</v>
+        <v>0.9926953287131751</v>
       </c>
       <c r="R24" t="n">
-        <v>0.005075595189499516</v>
+        <v>0.005075595246891651</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2985,31 +2985,31 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>0.9989979145197011</v>
+        <v>0.9989979145292962</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.002540241183442363</v>
+        <v>0.002540241171715482</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>0.9608443827013903</v>
+        <v>0.9608443828761388</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.003124251098636244</v>
+        <v>0.003124251091664596</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="n">
-        <v>0.8446192709595116</v>
+        <v>0.8446192682941442</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.009714199361370081</v>
+        <v>0.009714199503360223</v>
       </c>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
-        <v>0.9769001235953902</v>
+        <v>0.9769001262985881</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.001026863601820317</v>
+        <v>0.001026863538079088</v>
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
@@ -3041,25 +3041,25 @@
         <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3559522748638808</v>
+        <v>0.3559522750970078</v>
       </c>
       <c r="G25" t="n">
         <v>0.04668534080298786</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2688668009066632</v>
+        <v>0.2688668010518658</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2729559277122325</v>
+        <v>0.2729559273787527</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05553965571423582</v>
+        <v>0.05553965566938588</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5494012369207484</v>
+        <v>0.5494012367047949</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5531651098141975</v>
+        <v>0.5531651096136052</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3068,65 +3068,65 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.359776070804065</v>
+        <v>4.359776069195355</v>
       </c>
       <c r="P25" t="n">
-        <v>4.387811859846882</v>
+        <v>4.387811858352807</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.9827869502360601</v>
+        <v>0.9827869502327035</v>
       </c>
       <c r="R25" t="n">
-        <v>0.02175869289332351</v>
+        <v>0.02175869289595122</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>-0.3143661111299618</v>
+        <v>-0.3143661115098733</v>
       </c>
       <c r="U25" t="n">
-        <v>0.04220960126964817</v>
+        <v>0.04220960127574842</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>0.2705704395949385</v>
+        <v>0.2705704401435304</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001083696845556093</v>
+        <v>0.001083696845148578</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>0.9037293283445984</v>
+        <v>0.9037293282809171</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.01069635760359922</v>
+        <v>0.01069635760155928</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>0.5155857894256859</v>
+        <v>0.5155857898015717</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.003410800249187533</v>
+        <v>0.003410800247864213</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="n">
-        <v>0.9999642980004979</v>
+        <v>0.9999642980079823</v>
       </c>
       <c r="AG25" t="n">
-        <v>9.787797672631068e-05</v>
+        <v>9.787796732242698e-05</v>
       </c>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="n">
-        <v>0.9912692940008837</v>
+        <v>0.9912692925383154</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.000583606673247077</v>
+        <v>0.000583606708414751</v>
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
-        <v>-0.06019105087399779</v>
+        <v>-0.06019105215306464</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.003409599200541214</v>
+        <v>0.003409599174756292</v>
       </c>
       <c r="AN25" t="inlineStr"/>
     </row>
@@ -3153,25 +3153,25 @@
         <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4002539035826087</v>
+        <v>0.4002539033355717</v>
       </c>
       <c r="G26" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1994618786146296</v>
+        <v>0.199461878586617</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2900964126834302</v>
+        <v>0.2900964128573777</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05246774739927379</v>
+        <v>0.0524677475003759</v>
       </c>
       <c r="K26" t="n">
-        <v>0.540731726273736</v>
+        <v>0.5407317262128234</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5490181805573094</v>
+        <v>0.5490181805095745</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3180,65 +3180,65 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.295183238249074</v>
+        <v>4.295183237795165</v>
       </c>
       <c r="P26" t="n">
-        <v>4.35691974105193</v>
+        <v>4.356919740696322</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.9795222297738044</v>
+        <v>0.9795222298130901</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02199523776444483</v>
+        <v>0.02199523774299785</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>0.2503683661072617</v>
+        <v>0.2503683675309779</v>
       </c>
       <c r="U26" t="n">
-        <v>0.04251844761102798</v>
+        <v>0.04251844757065201</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>-0.6471722246888199</v>
+        <v>-0.6471722266848419</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0008997036024602547</v>
+        <v>0.0008997036030053793</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>0.9509637374357274</v>
+        <v>0.9509637376174738</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01195532135634414</v>
+        <v>0.01195532132646673</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>-0.4457842790344297</v>
+        <v>-0.4457842804035308</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.004122830932079933</v>
+        <v>0.004122830934032012</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="n">
-        <v>0.9173165762320066</v>
+        <v>0.9173165746315359</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.003848952943997378</v>
+        <v>0.003848952967535248</v>
       </c>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="n">
-        <v>0.9927408269512144</v>
+        <v>0.992740827486649</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.0007247754950350273</v>
+        <v>0.00072477547289676</v>
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>0.5346525047973455</v>
+        <v>0.5346525293350575</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.0009452755193291395</v>
+        <v>0.0009452754946355403</v>
       </c>
       <c r="AN26" t="inlineStr"/>
     </row>
@@ -3265,25 +3265,25 @@
         <v>67</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4605706049045288</v>
+        <v>0.4605706047574397</v>
       </c>
       <c r="G27" t="n">
         <v>0.04738213693437573</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2439684145997375</v>
+        <v>0.2439684149537734</v>
       </c>
       <c r="I27" t="n">
-        <v>0.174859558721163</v>
+        <v>0.1748595584867289</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07321928484019485</v>
+        <v>0.07321928486768225</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5300735357727636</v>
+        <v>0.5300735357192439</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5351292280259271</v>
+        <v>0.5351292279816955</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3292,65 +3292,65 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.215743336119488</v>
+        <v>4.215743335720499</v>
       </c>
       <c r="P27" t="n">
-        <v>4.253428618571796</v>
+        <v>4.25342861824211</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9962122267991117</v>
+        <v>0.9962122267971669</v>
       </c>
       <c r="R27" t="n">
-        <v>0.009988956446203911</v>
+        <v>0.009988956448777198</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>0.9032455827205915</v>
+        <v>0.903245582707326</v>
       </c>
       <c r="U27" t="n">
-        <v>0.01632889271337542</v>
+        <v>0.0163288927144948</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
-        <v>0.3403901858307666</v>
+        <v>0.3403901857619679</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0009101553846429754</v>
+        <v>0.000910155384690441</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>0.8956302952875048</v>
+        <v>0.8956302950193801</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.01369924705925465</v>
+        <v>0.01369924706318749</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>0.7957531353606853</v>
+        <v>0.7957531354488794</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.00165263256275092</v>
+        <v>0.001652632562394115</v>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="n">
-        <v>0.8785610062006513</v>
+        <v>0.8785610067911905</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.009734872753268337</v>
+        <v>0.009734872761348982</v>
       </c>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
-        <v>0.701592386452264</v>
+        <v>0.7015923817543881</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.0029430014967645</v>
+        <v>0.002943001503519373</v>
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="n">
-        <v>0.4340804153614276</v>
+        <v>0.4340804142054315</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.00489826866437603</v>
+        <v>0.004898268677630655</v>
       </c>
       <c r="AN27" t="inlineStr"/>
     </row>
@@ -3377,25 +3377,25 @@
         <v>274.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7158795401171276</v>
+        <v>0.7158795401305122</v>
       </c>
       <c r="G28" t="n">
         <v>0.01156082729280107</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1423140067580003</v>
+        <v>0.1423140067686963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1093709740016232</v>
+        <v>0.1093709739889803</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02087465183044777</v>
+        <v>0.02087465181901007</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4452115703335381</v>
+        <v>0.4452115833928689</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5394700346189368</v>
+        <v>0.539470030036131</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.128552560111538</v>
+        <v>4.128552781342059</v>
       </c>
       <c r="P28" t="n">
-        <v>4.338880960548818</v>
+        <v>4.338880950305505</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9504127269419997</v>
+        <v>0.9504127283578816</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02318936028512819</v>
+        <v>0.02318935995365786</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
@@ -3425,38 +3425,38 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>0.6641377878335885</v>
+        <v>0.6641377996269926</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.04748767786512259</v>
+        <v>0.04748767703486408</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>0.9450048563428035</v>
+        <v>0.9450048614301081</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.002804782658138229</v>
+        <v>0.002804782538927793</v>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="n">
-        <v>0.5150812060064947</v>
+        <v>0.5150812052342915</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.01164072327467621</v>
+        <v>0.0116407232640153</v>
       </c>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="n">
-        <v>0.3813307433411852</v>
+        <v>0.3813307368725358</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01709189690352015</v>
+        <v>0.01709189698376248</v>
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
-        <v>0.9905616779881961</v>
+        <v>0.9905616784125569</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.0003363342207591197</v>
+        <v>0.0003363342133287154</v>
       </c>
       <c r="AN28" t="inlineStr"/>
     </row>
@@ -3483,25 +3483,25 @@
         <v>15.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5922072970736373</v>
+        <v>0.5922072966992186</v>
       </c>
       <c r="G29" t="n">
         <v>0.2102386208346473</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01553978349820245</v>
+        <v>0.01553978410683548</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1433667741521803</v>
+        <v>0.1433667739479109</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03864752444133265</v>
+        <v>0.03864752441138786</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5450393411938402</v>
+        <v>0.5450393413035584</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5378951225118166</v>
+        <v>0.5378951225425983</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3510,16 +3510,16 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.327280143443206</v>
+        <v>4.327280144260669</v>
       </c>
       <c r="P29" t="n">
-        <v>4.274042576065238</v>
+        <v>4.274042576294665</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9370092198966595</v>
+        <v>0.9370092203899122</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01619595499649923</v>
+        <v>0.01619595492353491</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
@@ -3531,38 +3531,38 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>0.7199198589712297</v>
+        <v>0.719919860584556</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.03448679252226174</v>
+        <v>0.03448679238595346</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>0.9343812983619562</v>
+        <v>0.9343812992958096</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.008872642059008218</v>
+        <v>0.008872641992009715</v>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="n">
-        <v>0.6184579859230938</v>
+        <v>0.6184579868308682</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.008730513457351945</v>
+        <v>0.008730513374497255</v>
       </c>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="n">
-        <v>0.9545880790724479</v>
+        <v>0.9545880793902278</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.005536965959767819</v>
+        <v>0.005536965929026571</v>
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>0.9388067148510899</v>
+        <v>0.9388067155314166</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.001476325829841406</v>
+        <v>0.001476325819546223</v>
       </c>
       <c r="AN29" t="inlineStr"/>
     </row>
@@ -3589,25 +3589,25 @@
         <v>45.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6915723419858851</v>
+        <v>0.6915723419696138</v>
       </c>
       <c r="G30" t="n">
         <v>0.06992518005733864</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07335276932576335</v>
+        <v>0.07335276911610503</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1459822594046087</v>
+        <v>0.1459822596625786</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0191674492264043</v>
+        <v>0.01916744919436398</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5180684702589732</v>
+        <v>0.5180692828056708</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5445554295267135</v>
+        <v>0.5445554839185889</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3616,16 +3616,16 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.577350772514278</v>
+        <v>4.577351645319421</v>
       </c>
       <c r="P30" t="n">
-        <v>4.340420680421795</v>
+        <v>4.340420751735845</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9741213341857776</v>
+        <v>0.9741213924255319</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01325979561442754</v>
+        <v>0.01325978069367956</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
@@ -3637,38 +3637,38 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>0.8721219140354467</v>
+        <v>0.872122327963907</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.02435802173845336</v>
+        <v>0.02435798231573904</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>0.9548937407706659</v>
+        <v>0.9548911742838412</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0009570856361806922</v>
+        <v>0.0009571128864711719</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="n">
-        <v>-0.004976003296010445</v>
+        <v>-0.004975947405518433</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.01355721008320211</v>
+        <v>0.01355720976533853</v>
       </c>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
-        <v>0.8766879227666049</v>
+        <v>0.8766878660765247</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.007349825290750353</v>
+        <v>0.00734982698997631</v>
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>0.5069525364481759</v>
+        <v>0.5069527325268182</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.001888451014660394</v>
+        <v>0.001888450628084332</v>
       </c>
       <c r="AN30" t="inlineStr"/>
     </row>
@@ -3695,25 +3695,25 @@
         <v>26.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5100618132893889</v>
+        <v>0.510061813306836</v>
       </c>
       <c r="G31" t="n">
         <v>0.1207073450419458</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08244690044211486</v>
+        <v>0.08244690045861332</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2664816652636977</v>
+        <v>0.2664816652601923</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02030227596285282</v>
+        <v>0.02030227593241257</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5411091241769229</v>
+        <v>0.5411091243856065</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5556445995349577</v>
+        <v>0.5556445997103447</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.297995521688784</v>
+        <v>4.297995523243836</v>
       </c>
       <c r="P31" t="n">
-        <v>4.406273731714898</v>
+        <v>4.406273733021131</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9845846215736355</v>
+        <v>0.9845846207792551</v>
       </c>
       <c r="R31" t="n">
-        <v>0.008108372867425035</v>
+        <v>0.008108373078418126</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -3743,38 +3743,38 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>0.9403393012386818</v>
+        <v>0.9403392953662553</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.01304611971851409</v>
+        <v>0.01304612035435265</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0.8908991023708824</v>
+        <v>0.8908991050495451</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.008041470559999596</v>
+        <v>0.008041470466006895</v>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="n">
-        <v>-0.04007470500952648</v>
+        <v>-0.04007469953179266</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.00927314704035594</v>
+        <v>0.009273147068069237</v>
       </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
-        <v>0.9703497265043083</v>
+        <v>0.9703497213672005</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.002701992476453797</v>
+        <v>0.00270199270119878</v>
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
-        <v>0.05262509718589548</v>
+        <v>0.05262510335571136</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.004091009304045872</v>
+        <v>0.004091009294624781</v>
       </c>
       <c r="AN31" t="inlineStr"/>
     </row>
@@ -3801,25 +3801,25 @@
         <v>32.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6207177798737793</v>
+        <v>0.6207177798836309</v>
       </c>
       <c r="G32" t="n">
         <v>0.09738046547862497</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1026556514757471</v>
+        <v>0.102655651448909</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1515085776379964</v>
+        <v>0.1515085776593587</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02773752553385222</v>
+        <v>0.0277375255294765</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5785259936431176</v>
+        <v>0.5785259286975886</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5570048359248688</v>
+        <v>0.5570048517873958</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3828,16 +3828,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.576621334530718</v>
+        <v>4.576620851231514</v>
       </c>
       <c r="P32" t="n">
-        <v>4.416392399057208</v>
+        <v>4.416392517297742</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9813117562949464</v>
+        <v>0.9813117711006507</v>
       </c>
       <c r="R32" t="n">
-        <v>0.01316370649800837</v>
+        <v>0.01316370128386094</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -3849,38 +3849,38 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>0.8830149249119658</v>
+        <v>0.8830160774891798</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.009754853694145426</v>
+        <v>0.009754805639069901</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>0.2196324728205126</v>
+        <v>0.2196327230667259</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.01753505445950276</v>
+        <v>0.01753505169578304</v>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="n">
-        <v>-0.2312443221242326</v>
+        <v>-0.2312454990409245</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.01411120524233461</v>
+        <v>0.01411121202064484</v>
       </c>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
-        <v>0.3378479862451139</v>
+        <v>0.337847701940807</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01686047971490034</v>
+        <v>0.01686048333005009</v>
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
-        <v>0.0827074752067728</v>
+        <v>0.0827074599527291</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.004868207156664338</v>
+        <v>0.004868207214364416</v>
       </c>
       <c r="AN32" t="inlineStr"/>
     </row>
@@ -3905,25 +3905,25 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.6421516036650835</v>
+        <v>0.642151603719554</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002523163010079717</v>
+        <v>0.002523163255140709</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2245698007084695</v>
+        <v>0.2245698005775707</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1058026140953321</v>
+        <v>0.1058026139657058</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02495281852103528</v>
+        <v>0.0249528184820288</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3932497006496025</v>
+        <v>0.3932499985155353</v>
       </c>
       <c r="L33" t="n">
-        <v>0.5367600548392822</v>
+        <v>0.5367600664746894</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3932,16 +3932,16 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.368367739242999</v>
+        <v>4.368367793710408</v>
       </c>
       <c r="P33" t="n">
-        <v>4.330556365681336</v>
+        <v>4.330556407828729</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.9666686912297314</v>
+        <v>0.9666687203117282</v>
       </c>
       <c r="R33" t="n">
-        <v>0.005791980423681998</v>
+        <v>0.005791977896797806</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
@@ -3951,38 +3951,38 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>0.9182092969256205</v>
+        <v>0.9182093792363619</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.01155659836799151</v>
+        <v>0.01155659255446296</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>0.5438624804908768</v>
+        <v>0.5438625819397982</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.004334200072395147</v>
+        <v>0.00433419956640089</v>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="n">
-        <v>0.9307269936887617</v>
+        <v>0.9307269903307352</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.003139421517657733</v>
+        <v>0.003139421589906293</v>
       </c>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>0.7830871901422091</v>
+        <v>0.7830875228698941</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.002209911193717272</v>
+        <v>0.00220990948924859</v>
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>0.3296852055332312</v>
+        <v>0.329685728617171</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.0008094782797049903</v>
+        <v>0.0008094779576199578</v>
       </c>
       <c r="AN33" t="inlineStr"/>
     </row>
@@ -4009,25 +4009,25 @@
         <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7519633395058384</v>
+        <v>0.7519633396250179</v>
       </c>
       <c r="G34" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01478397129559729</v>
+        <v>0.0147839710365304</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1023682012617217</v>
+        <v>0.1023682013871307</v>
       </c>
       <c r="J34" t="n">
-        <v>0.008784365836720525</v>
+        <v>0.008784365851198749</v>
       </c>
       <c r="K34" t="n">
-        <v>0.536901696262555</v>
+        <v>0.5369016959858964</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5432389027487502</v>
+        <v>0.5432389027490659</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.266640352725299</v>
+        <v>4.266640350663374</v>
       </c>
       <c r="P34" t="n">
-        <v>4.313865019699602</v>
+        <v>4.313865019701939</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.9392370431768626</v>
+        <v>0.939237042117992</v>
       </c>
       <c r="R34" t="n">
-        <v>0.01718982928280536</v>
+        <v>0.01718982943601216</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
@@ -4057,38 +4057,38 @@
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>0.9025777770358581</v>
+        <v>0.9025777752172841</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.03736462267539677</v>
+        <v>0.03736462303170694</v>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>0.9954666026972713</v>
+        <v>0.9954666035000507</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.001592709087179328</v>
+        <v>0.001592708948342082</v>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="n">
-        <v>0.7077091980568507</v>
+        <v>0.7077092020821509</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.004162081399060013</v>
+        <v>0.00416208139210575</v>
       </c>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
-        <v>0.5015557242603633</v>
+        <v>0.5015557239555242</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.00783696143241468</v>
+        <v>0.007836961439294451</v>
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="n">
-        <v>0.2670092201505117</v>
+        <v>0.2670092148361114</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.0008322850727627393</v>
+        <v>0.0008322850673228221</v>
       </c>
       <c r="AN34" t="inlineStr"/>
     </row>
@@ -4115,25 +4115,25 @@
         <v>74.09999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.687523750659823</v>
+        <v>0.6875237506860816</v>
       </c>
       <c r="G35" t="n">
         <v>0.042842148105306</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2018749037744333</v>
+        <v>0.201874903841659</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03464191229956181</v>
+        <v>0.03464191218332047</v>
       </c>
       <c r="J35" t="n">
-        <v>0.033117285160876</v>
+        <v>0.03311728518363292</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5172477546113869</v>
+        <v>0.5002346258691004</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5370322289733235</v>
+        <v>0.5375970949564146</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4142,16 +4142,16 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.120101088769337</v>
+        <v>3.993150554641779</v>
       </c>
       <c r="P35" t="n">
-        <v>4.267610979150944</v>
+        <v>4.271817766768105</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9963030324501649</v>
+        <v>0.9962031404854333</v>
       </c>
       <c r="R35" t="n">
-        <v>0.006057268172059271</v>
+        <v>0.006138556343570546</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>0.9774878171816286</v>
+        <v>0.9758018320311664</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.008187536450259427</v>
+        <v>0.008488592519494031</v>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4173,24 +4173,24 @@
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="n">
-        <v>0.6458277866106918</v>
+        <v>0.6494563122337478</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.008887733861668164</v>
+        <v>0.008842088846406426</v>
       </c>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
-        <v>0.699717325088644</v>
+        <v>0.6948344579896206</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.002214455249279027</v>
+        <v>0.002232387158933676</v>
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="n">
-        <v>0.5660210730834871</v>
+        <v>0.5727488610343965</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.002236791650735604</v>
+        <v>0.002219385922148607</v>
       </c>
       <c r="AN35" t="inlineStr"/>
     </row>
@@ -4217,25 +4217,25 @@
         <v>46.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6184344404805445</v>
+        <v>0.6184344404849657</v>
       </c>
       <c r="G36" t="n">
         <v>0.06871435442864013</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1345326977341799</v>
+        <v>0.1345326978111002</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1554100927459354</v>
+        <v>0.1554100926475006</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02290841461070009</v>
+        <v>0.0229084146277933</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5508842687946176</v>
+        <v>0.5508842674969333</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5490979189898959</v>
+        <v>0.5490979182560349</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.370823363997192</v>
+        <v>4.370823354330846</v>
       </c>
       <c r="P36" t="n">
-        <v>4.357516428485859</v>
+        <v>4.357516423019093</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9839315696536894</v>
+        <v>0.9839315684529176</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01148646560125316</v>
+        <v>0.01148646602723091</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
@@ -4265,38 +4265,38 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>0.8166610429078107</v>
+        <v>0.816661020519712</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.01861310289764294</v>
+        <v>0.01861310403019409</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>0.3723614624476508</v>
+        <v>0.3723614460559656</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.008126943414296529</v>
+        <v>0.008126943626044976</v>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="n">
-        <v>0.06702911052602845</v>
+        <v>0.06702911439401316</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.01347622341055103</v>
+        <v>0.01347622343537479</v>
       </c>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="n">
-        <v>0.7326810460920691</v>
+        <v>0.7326810391177341</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.00605705288442605</v>
+        <v>0.006057052976002668</v>
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="n">
-        <v>0.1524810339639457</v>
+        <v>0.1524810380024521</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.004071075789554511</v>
+        <v>0.004071075783492895</v>
       </c>
       <c r="AN36" t="inlineStr"/>
     </row>
@@ -4323,25 +4323,25 @@
         <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4310490712245829</v>
+        <v>0.4310490710111513</v>
       </c>
       <c r="G37" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3585099706610048</v>
+        <v>0.3585099709374001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1452580722152676</v>
+        <v>0.1452580721451264</v>
       </c>
       <c r="J37" t="n">
-        <v>0.007462828179086988</v>
+        <v>0.007462828186264588</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5416253914309452</v>
+        <v>0.5416253932533359</v>
       </c>
       <c r="L37" t="n">
-        <v>0.5505442072965488</v>
+        <v>0.5505442076354963</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4350,61 +4350,61 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.301842560539425</v>
+        <v>4.301842574119091</v>
       </c>
       <c r="P37" t="n">
-        <v>4.368288281711853</v>
+        <v>4.368288284237023</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.990418338661169</v>
+        <v>0.9904183415653044</v>
       </c>
       <c r="R37" t="n">
-        <v>0.006522426256053311</v>
+        <v>0.006522425265922161</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
-        <v>-1.532500131799742</v>
+        <v>-1.53250163877624</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0006808055990136449</v>
+        <v>0.0006808058015719532</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
-        <v>0.9759297449476745</v>
+        <v>0.9759297655506045</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.007365971176233688</v>
+        <v>0.007365968019317885</v>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>-0.7305958191896744</v>
+        <v>-0.7305957996609727</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.008329356277167882</v>
+        <v>0.008329356117522184</v>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="n">
-        <v>0.9057722359341037</v>
+        <v>0.9057722530023082</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.009989437044715525</v>
+        <v>0.009989436156807974</v>
       </c>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
-        <v>0.9607746650322766</v>
+        <v>0.9607746917154589</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.001776891264080643</v>
+        <v>0.001776890655215816</v>
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="n">
-        <v>0.9999955954615968</v>
+        <v>0.9999955949389792</v>
       </c>
       <c r="AM37" t="n">
-        <v>2.065884061737462e-06</v>
+        <v>2.06600661356051e-06</v>
       </c>
       <c r="AN37" t="inlineStr"/>
     </row>
@@ -4431,25 +4431,25 @@
         <v>23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4115513533477569</v>
+        <v>0.4115513534924096</v>
       </c>
       <c r="G38" t="n">
         <v>0.1380262249827467</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3184506857669814</v>
+        <v>0.318450685478181</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1287866383384099</v>
+        <v>0.1287866384976123</v>
       </c>
       <c r="J38" t="n">
-        <v>0.003185097564105027</v>
+        <v>0.003185097549050355</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5410877791334675</v>
+        <v>0.5410877784062029</v>
       </c>
       <c r="L38" t="n">
-        <v>0.5459534785704414</v>
+        <v>0.5459534769004961</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4458,61 +4458,61 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.297836464385832</v>
+        <v>4.297836458966457</v>
       </c>
       <c r="P38" t="n">
-        <v>4.334089179456488</v>
+        <v>4.334089167015388</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9430380972433829</v>
+        <v>0.9430380885096223</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0133919071904237</v>
+        <v>0.01339190820614503</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
-        <v>0.2639470867320597</v>
+        <v>0.2639473950996036</v>
       </c>
       <c r="X38" t="n">
-        <v>0.001124531513097592</v>
+        <v>0.001124531277537722</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>0.7469339915377098</v>
+        <v>0.7469339292169226</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.02426319150403365</v>
+        <v>0.02426319453073373</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>-0.5464580451682217</v>
+        <v>-0.5464580036950251</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.01804949870042787</v>
+        <v>0.01804949804850456</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="n">
-        <v>0.9907604013767453</v>
+        <v>0.9907603512579023</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.002231262732024745</v>
+        <v>0.002231268769398914</v>
       </c>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
-        <v>-2.316352245161167</v>
+        <v>-2.316351388665645</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.006015688175171676</v>
+        <v>0.006015687773131145</v>
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="n">
-        <v>0.9999993534681905</v>
+        <v>0.9999993530653966</v>
       </c>
       <c r="AM38" t="n">
-        <v>3.222645951117273e-07</v>
+        <v>3.223649747371968e-07</v>
       </c>
       <c r="AN38" t="inlineStr"/>
     </row>
@@ -4539,25 +4539,25 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.464866072408512</v>
+        <v>0.4648660724078407</v>
       </c>
       <c r="G39" t="n">
         <v>0.06613756613756613</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3147165341115007</v>
+        <v>0.3147165341147267</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1215057334841287</v>
+        <v>0.1215057334732506</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03277409385829239</v>
+        <v>0.03277409386661587</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5532307663355256</v>
+        <v>0.5532307752309462</v>
       </c>
       <c r="L39" t="n">
-        <v>0.5491049323283788</v>
+        <v>0.5491049349716622</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.388301465052076</v>
+        <v>4.388301531307524</v>
       </c>
       <c r="P39" t="n">
-        <v>4.357568293928008</v>
+        <v>4.357568313617461</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9819945676145284</v>
+        <v>0.9819945679206817</v>
       </c>
       <c r="R39" t="n">
-        <v>0.008981661082384249</v>
+        <v>0.008981661005760262</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
@@ -4585,38 +4585,38 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>0.8614104763354866</v>
+        <v>0.8614104811972901</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.0124599518462974</v>
+        <v>0.01245995162672164</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>0.2315287535118379</v>
+        <v>0.2315286334208446</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.001304206671885018</v>
+        <v>0.001304206773790893</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="n">
-        <v>-0.05242748113915696</v>
+        <v>-0.05242748866655367</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.0146940678776024</v>
+        <v>0.01469406793063627</v>
       </c>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>0.781611202634598</v>
+        <v>0.7816112310192532</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.005071144298890516</v>
+        <v>0.00507114396847763</v>
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="n">
-        <v>-0.1198831906614264</v>
+        <v>-0.1198832156203771</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.002183503754813192</v>
+        <v>0.002183503781482074</v>
       </c>
       <c r="AN39" t="inlineStr"/>
     </row>
@@ -4643,25 +4643,25 @@
         <v>70.70000000000002</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4301189564620539</v>
+        <v>0.4301189564542686</v>
       </c>
       <c r="G40" t="n">
         <v>0.04490244942861631</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1726240369116226</v>
+        <v>0.1726240368983525</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3491894964880415</v>
+        <v>0.3491894964967999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003165060709665684</v>
+        <v>0.00316506072196271</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2863667851232302</v>
+        <v>0.2863664886197732</v>
       </c>
       <c r="L40" t="n">
-        <v>0.5256098943551707</v>
+        <v>0.5256095698570034</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4670,16 +4670,16 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>4.296817286241648</v>
+        <v>4.296820969432684</v>
       </c>
       <c r="P40" t="n">
-        <v>4.505131646370524</v>
+        <v>4.505131552269059</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.9940283693395067</v>
+        <v>0.9940283477841904</v>
       </c>
       <c r="R40" t="n">
-        <v>0.004641801174720207</v>
+        <v>0.004641809552015665</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
@@ -4689,38 +4689,38 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>0.9875289690252108</v>
+        <v>0.9875289694883075</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.006739270391131856</v>
+        <v>0.006739270267178511</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>0.8553981492924094</v>
+        <v>0.8554005802421055</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.000865106071817611</v>
+        <v>0.000865098799994426</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="n">
-        <v>0.9801740764481187</v>
+        <v>0.9801740232648117</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.003536714601192772</v>
+        <v>0.003536719342383558</v>
       </c>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
-        <v>0.9810170861862123</v>
+        <v>0.9810169222196432</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.006187399095203475</v>
+        <v>0.006187425817854655</v>
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="n">
-        <v>0.999999992126543</v>
+        <v>0.9999999932108831</v>
       </c>
       <c r="AM40" t="n">
-        <v>5.395161618500646e-08</v>
+        <v>5.009892056950956e-08</v>
       </c>
       <c r="AN40" t="inlineStr"/>
     </row>
@@ -4747,25 +4747,25 @@
         <v>84.84</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3369254806988865</v>
+        <v>0.3369254807409055</v>
       </c>
       <c r="G41" t="n">
         <v>0.03741870785718027</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2464337952095151</v>
+        <v>0.2464337951089697</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3649923484168429</v>
+        <v>0.3649923484758453</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01422966781757511</v>
+        <v>0.0142296678170992</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5140482499878871</v>
+        <v>0.5140475197579125</v>
       </c>
       <c r="L41" t="n">
-        <v>0.5640757300050252</v>
+        <v>0.5640757464308848</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4774,16 +4774,16 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4.40576475719459</v>
+        <v>4.405764247326679</v>
       </c>
       <c r="P41" t="n">
-        <v>4.493386417444865</v>
+        <v>4.493387035707665</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.9944727431335436</v>
+        <v>0.9944727727958468</v>
       </c>
       <c r="R41" t="n">
-        <v>0.005761954574627198</v>
+        <v>0.005761939114741743</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
@@ -4793,38 +4793,38 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>0.8783828200649977</v>
+        <v>0.8783830019790121</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.01015557894211137</v>
+        <v>0.01015557134600891</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>0.7420484408028993</v>
+        <v>0.7420488214387942</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.001266605723691094</v>
+        <v>0.001266604789182726</v>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="n">
-        <v>0.9831984807204074</v>
+        <v>0.9831985024788151</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.0034754827582404</v>
+        <v>0.003475480508131566</v>
       </c>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="n">
-        <v>0.9545695098592104</v>
+        <v>0.9545702023878974</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.006871702870929159</v>
+        <v>0.006871650496733396</v>
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>0.8156581769174286</v>
+        <v>0.8156580547975442</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.001400445694209945</v>
+        <v>0.001400446158350163</v>
       </c>
       <c r="AN41" t="inlineStr"/>
     </row>
@@ -4851,25 +4851,25 @@
         <v>124.31</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4255446328458828</v>
+        <v>0.4255446328415167</v>
       </c>
       <c r="G42" t="n">
         <v>0.02553779401981477</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2146647956812922</v>
+        <v>0.214664795708344</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3235805049574504</v>
+        <v>0.3235805049438804</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01067227249555984</v>
+        <v>0.01067227248644411</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3386526589655819</v>
+        <v>0.338826929622885</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5329537165975325</v>
+        <v>0.5329852942894827</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -4878,16 +4878,16 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>4.440464077287422</v>
+        <v>4.442217945015177</v>
       </c>
       <c r="P42" t="n">
-        <v>4.468409147149607</v>
+        <v>4.46866731648299</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.9718770256853601</v>
+        <v>0.9718770279658657</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01110529163991968</v>
+        <v>0.01110529119069845</v>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
@@ -4897,31 +4897,31 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>0.9054343665896841</v>
+        <v>0.9054343871808976</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.01687558678137446</v>
+        <v>0.01687558494304432</v>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>0.9996966553002804</v>
+        <v>0.999696513099808</v>
       </c>
       <c r="AD42" t="n">
-        <v>9.308905131191456e-05</v>
+        <v>9.31108676748127e-05</v>
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="n">
-        <v>0.7120679758439483</v>
+        <v>0.712067825699381</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.01566073218317996</v>
+        <v>0.01566073627753675</v>
       </c>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
-        <v>0.9954341101501322</v>
+        <v>0.995434228822871</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.002089629105712255</v>
+        <v>0.002089601949195365</v>
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
@@ -4953,25 +4953,25 @@
         <v>40.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5997176448026437</v>
+        <v>0.5997176446896944</v>
       </c>
       <c r="G43" t="n">
         <v>0.0791671614614258</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2378772798847145</v>
+        <v>0.2378772801295146</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05923193023736853</v>
+        <v>0.05923193014095748</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0240059836138475</v>
+        <v>0.02400598357840774</v>
       </c>
       <c r="K43" t="n">
-        <v>0.260825416693064</v>
+        <v>0.260825778069708</v>
       </c>
       <c r="L43" t="n">
-        <v>0.4993475355383537</v>
+        <v>0.4993476991259018</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -4980,16 +4980,16 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.977480086284531</v>
+        <v>3.977476633209355</v>
       </c>
       <c r="P43" t="n">
-        <v>4.301903453506331</v>
+        <v>4.301903450194346</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.9679398970104771</v>
+        <v>0.967939768714815</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01094040987057284</v>
+        <v>0.01094043176064109</v>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
@@ -4999,38 +4999,38 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>0.9502196689188239</v>
+        <v>0.9502193367590197</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.01918814589791783</v>
+        <v>0.0191882099075009</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>0.6176573760793274</v>
+        <v>0.6176579137588156</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.002920180507010408</v>
+        <v>0.002920178453718917</v>
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="n">
-        <v>0.7849284998005326</v>
+        <v>0.7849285353624574</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.01469674407288626</v>
+        <v>0.01469674288385011</v>
       </c>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="n">
-        <v>0.8198087942877239</v>
+        <v>0.8198092453855583</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.002379583487650323</v>
+        <v>0.002379580507779413</v>
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>0.994064484900142</v>
+        <v>0.9940645143469129</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.0003061691831618108</v>
+        <v>0.0003061684231578218</v>
       </c>
       <c r="AN43" t="inlineStr"/>
     </row>
@@ -5057,25 +5057,25 @@
         <v>25.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3587984910438237</v>
+        <v>0.3587984911488203</v>
       </c>
       <c r="G44" t="n">
         <v>0.1259763164525069</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2964643700107539</v>
+        <v>0.2964643700757857</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1968371786437586</v>
+        <v>0.1968371786061268</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02192364384915694</v>
+        <v>0.02192364371676016</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5286870787682787</v>
+        <v>0.5286870788523484</v>
       </c>
       <c r="L44" t="n">
-        <v>0.5600074997541628</v>
+        <v>0.5600074997451531</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5084,16 +5084,16 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.205406969984286</v>
+        <v>4.205406970611063</v>
       </c>
       <c r="P44" t="n">
-        <v>4.438748696822004</v>
+        <v>4.438748696755018</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.95302310452405</v>
+        <v>0.9530231045110747</v>
       </c>
       <c r="R44" t="n">
-        <v>0.007382335648650627</v>
+        <v>0.007382335651406289</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
@@ -5103,38 +5103,38 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>0.9556761552670739</v>
+        <v>0.955676155014881</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.009440932723754175</v>
+        <v>0.009440932754758139</v>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>0.8126900677434666</v>
+        <v>0.8126900683056585</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.004799897038070332</v>
+        <v>0.004799897030867129</v>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="n">
-        <v>0.8998961627984626</v>
+        <v>0.8998961630219063</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.01106594864011849</v>
+        <v>0.01106594863051115</v>
       </c>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="n">
-        <v>0.9233222961529891</v>
+        <v>0.9233222961764832</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.006015608589755103</v>
+        <v>0.006015608581377027</v>
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>0.6252075221395293</v>
+        <v>0.6252075159771944</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.00129669189296649</v>
+        <v>0.001296691893196228</v>
       </c>
       <c r="AN44" t="inlineStr"/>
     </row>
@@ -5161,25 +5161,25 @@
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4805050132618147</v>
+        <v>0.4805050130472089</v>
       </c>
       <c r="G45" t="n">
         <v>0.1587301587301587</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1510431451475349</v>
+        <v>0.1510431452397918</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1848438942219129</v>
+        <v>0.1848438943574318</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02487778863857871</v>
+        <v>0.02487778862540869</v>
       </c>
       <c r="K45" t="n">
-        <v>0.5400703130547023</v>
+        <v>0.5400682057539531</v>
       </c>
       <c r="L45" t="n">
-        <v>0.5560424067601982</v>
+        <v>0.5560427753777556</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5188,16 +5188,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.290254436529441</v>
+        <v>4.290238732877078</v>
       </c>
       <c r="P45" t="n">
-        <v>4.409240661505166</v>
+        <v>4.409243406450039</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.9689003003205184</v>
+        <v>0.9689000522508463</v>
       </c>
       <c r="R45" t="n">
-        <v>0.0086126776460247</v>
+        <v>0.008612711993460836</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
@@ -5207,38 +5207,38 @@
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>0.9761786969789389</v>
+        <v>0.9761782419009816</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.01320113187623589</v>
+        <v>0.01320125796474662</v>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>0.9228403531276196</v>
+        <v>0.9228405772571957</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.007285102563709765</v>
+        <v>0.007285091982996913</v>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="n">
-        <v>0.8734203387177651</v>
+        <v>0.8734204167665813</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.008454722298625272</v>
+        <v>0.008454719699811132</v>
       </c>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="n">
-        <v>0.9225908945229462</v>
+        <v>0.9225910791922862</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.008466968692137505</v>
+        <v>0.008466958599618869</v>
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="n">
-        <v>0.9804677110250209</v>
+        <v>0.980467803565608</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.0006136701179116748</v>
+        <v>0.0006136686638361343</v>
       </c>
       <c r="AN45" t="inlineStr"/>
     </row>
@@ -5265,25 +5265,25 @@
         <v>13.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4123104193140011</v>
+        <v>0.4123104194730447</v>
       </c>
       <c r="G46" t="n">
         <v>0.2300437083045778</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09500900007204896</v>
+        <v>0.09500899989902098</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2190898484594311</v>
+        <v>0.2190898485295714</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04354702384994095</v>
+        <v>0.04354702379378513</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4692195827002179</v>
+        <v>0.4692227989288898</v>
       </c>
       <c r="L46" t="n">
-        <v>0.56319358864237</v>
+        <v>0.5631935498193604</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5292,16 +5292,16 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.761450846446995</v>
+        <v>3.761474892830758</v>
       </c>
       <c r="P46" t="n">
-        <v>4.462444238329396</v>
+        <v>4.462443951202665</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9695306941104365</v>
+        <v>0.9695306743059184</v>
       </c>
       <c r="R46" t="n">
-        <v>0.008322570492744614</v>
+        <v>0.008322573200325848</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
@@ -5311,38 +5311,38 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>0.9840113589995604</v>
+        <v>0.9840113061080106</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.009750328092818736</v>
+        <v>0.009750344224852572</v>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>0.9224336542903625</v>
+        <v>0.9224336846664369</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.01033758898922709</v>
+        <v>0.0103375869650541</v>
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="n">
-        <v>0.9848925210034284</v>
+        <v>0.9848925307757307</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.002011984109332633</v>
+        <v>0.002011983455999561</v>
       </c>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>0.8728316232390262</v>
+        <v>0.872831664241837</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.01180908740359581</v>
+        <v>0.01180908550323005</v>
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="n">
-        <v>0.9880876414415648</v>
+        <v>0.9880876398478945</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.0009426710156491396</v>
+        <v>0.0009426710778015792</v>
       </c>
       <c r="AN46" t="inlineStr"/>
     </row>
@@ -5369,25 +5369,25 @@
         <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4235443992070436</v>
+        <v>0.4235443991299785</v>
       </c>
       <c r="G47" t="n">
         <v>0.1670843776106934</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2433419961172016</v>
+        <v>0.2433419961113411</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1505472905220324</v>
+        <v>0.1505472906218897</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01548193654302897</v>
+        <v>0.01548193652609739</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5376530400040005</v>
+        <v>0.5376530401280268</v>
       </c>
       <c r="L47" t="n">
-        <v>0.55386159540626</v>
+        <v>0.5538615954093717</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5396,16 +5396,16 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.272240003116125</v>
+        <v>4.272240004040461</v>
       </c>
       <c r="P47" t="n">
-        <v>4.392994941751244</v>
+        <v>4.392994941774486</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9451092518699958</v>
+        <v>0.9451092518371923</v>
       </c>
       <c r="R47" t="n">
-        <v>0.008804600464171093</v>
+        <v>0.008804600465676347</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
@@ -5415,38 +5415,38 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>0.940644718982248</v>
+        <v>0.9406447191409113</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.01342367472314932</v>
+        <v>0.01342367470477476</v>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>0.8033244109864681</v>
+        <v>0.8033244105694615</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.00692931419805967</v>
+        <v>0.006929314205405702</v>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="n">
-        <v>0.847695687677937</v>
+        <v>0.8476956870377512</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.01163620960645925</v>
+        <v>0.01163620962902435</v>
       </c>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
-        <v>0.9016049470413948</v>
+        <v>0.901604947292363</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.004864614147289625</v>
+        <v>0.004864614147542084</v>
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
-        <v>0.9099581517169765</v>
+        <v>0.9099581527661619</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.0005732918389398196</v>
+        <v>0.0005732918358290306</v>
       </c>
       <c r="AN47" t="inlineStr"/>
     </row>
@@ -5473,25 +5473,25 @@
         <v>26.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4466462867107708</v>
+        <v>0.4466462865765082</v>
       </c>
       <c r="G48" t="n">
         <v>0.1197963462114405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3318502634836513</v>
+        <v>0.3318502636697235</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06116662707319055</v>
+        <v>0.06116662702741293</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04054047652094685</v>
+        <v>0.04054047651491494</v>
       </c>
       <c r="K48" t="n">
-        <v>0.4047097120777118</v>
+        <v>0.4047095718033272</v>
       </c>
       <c r="L48" t="n">
-        <v>0.5459567870506425</v>
+        <v>0.545956786370435</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5500,16 +5500,16 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.278188650913639</v>
+        <v>3.27818759776892</v>
       </c>
       <c r="P48" t="n">
-        <v>4.334035035067895</v>
+        <v>4.334035029847181</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9639931396374642</v>
+        <v>0.9639931396920778</v>
       </c>
       <c r="R48" t="n">
-        <v>0.009784098841558167</v>
+        <v>0.009784098834266893</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
@@ -5519,38 +5519,38 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>0.9507073691867312</v>
+        <v>0.9507073692285446</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.01623439938749992</v>
+        <v>0.01623439937648523</v>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>0.885564897739694</v>
+        <v>0.8855648979047368</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.005714404488955672</v>
+        <v>0.005714404484834903</v>
       </c>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="n">
-        <v>0.9510188166467399</v>
+        <v>0.9510188167945697</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.01283437782524244</v>
+        <v>0.01283437781265882</v>
       </c>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="n">
-        <v>0.7409315243339216</v>
+        <v>0.7409315238739723</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.004206145926056573</v>
+        <v>0.004206145927768051</v>
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="n">
-        <v>0.9996682151621836</v>
+        <v>0.9996682151629799</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.0001410349541343809</v>
+        <v>0.0001410349539647752</v>
       </c>
       <c r="AN48" t="inlineStr"/>
     </row>
@@ -5577,25 +5577,25 @@
         <v>27.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4784766675558373</v>
+        <v>0.4784766676196412</v>
       </c>
       <c r="G49" t="n">
         <v>0.1167133520074696</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1617722833471003</v>
+        <v>0.1617722832354314</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2200624129180908</v>
+        <v>0.2200624129775048</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02297528417150188</v>
+        <v>0.0229752841599529</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3632462737432927</v>
+        <v>0.3632548584744412</v>
       </c>
       <c r="L49" t="n">
-        <v>0.5436737909142402</v>
+        <v>0.5436760363759189</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -5604,16 +5604,16 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4.068731139454012</v>
+        <v>4.068683261012442</v>
       </c>
       <c r="P49" t="n">
-        <v>4.41054613424981</v>
+        <v>4.410545496661193</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.9422527860902778</v>
+        <v>0.9422514521966332</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01139044774077632</v>
+        <v>0.01139057929271309</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
@@ -5623,38 +5623,38 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>0.9671176949013629</v>
+        <v>0.9671149343550083</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.0122316189889993</v>
+        <v>0.01223213241492796</v>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>0.8232446508781506</v>
+        <v>0.8232738371402013</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.004031773780192899</v>
+        <v>0.004031440898431044</v>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="n">
-        <v>0.4612537299587078</v>
+        <v>0.4612502805899569</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.01355087160968498</v>
+        <v>0.01355091497287716</v>
       </c>
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="n">
-        <v>0.3836149605572192</v>
+        <v>0.3836068150991564</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.01724988347376059</v>
+        <v>0.0172499974583082</v>
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="n">
-        <v>0.8756694195663643</v>
+        <v>0.8756693785032647</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.001288097251607165</v>
+        <v>0.001288097461476137</v>
       </c>
       <c r="AN49" t="inlineStr"/>
     </row>
@@ -5681,25 +5681,25 @@
         <v>22.6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4707222729765161</v>
+        <v>0.4707222730832482</v>
       </c>
       <c r="G50" t="n">
         <v>0.1404691670178395</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06718571998428063</v>
+        <v>0.06718571980350242</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2979720652205344</v>
+        <v>0.2979720652617544</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02365077480082941</v>
+        <v>0.02365077483365554</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5409958952894118</v>
+        <v>0.540998905599272</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5605201676033635</v>
+        <v>0.5605220283389617</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -5708,16 +5708,16 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.297151770118208</v>
+        <v>4.297174202195596</v>
       </c>
       <c r="P50" t="n">
-        <v>4.442562212890054</v>
+        <v>4.442576016404089</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.9608045769180966</v>
+        <v>0.9608048395334117</v>
       </c>
       <c r="R50" t="n">
-        <v>0.01058154850218405</v>
+        <v>0.01058151305540473</v>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
@@ -5727,31 +5727,31 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>0.9819033004737431</v>
+        <v>0.9819038754006788</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.01131730506638015</v>
+        <v>0.01131712529372419</v>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>0.9374170034323297</v>
+        <v>0.9374168392624717</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.005330505898001532</v>
+        <v>0.005330512889579681</v>
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="n">
-        <v>0.9482343494354788</v>
+        <v>0.9482341287657269</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.002324519793881028</v>
+        <v>0.002324524740709713</v>
       </c>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="n">
-        <v>0.8050630900901391</v>
+        <v>0.8050626038217311</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.01771919545651057</v>
+        <v>0.01771921756038426</v>
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
@@ -5783,25 +5783,25 @@
         <v>12.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4132915616414226</v>
+        <v>0.4132915619983448</v>
       </c>
       <c r="G51" t="n">
         <v>0.2602133749674733</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02750138666645612</v>
+        <v>0.02750138682641973</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2472592619614906</v>
+        <v>0.247259261508163</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05173441476315732</v>
+        <v>0.05173441469959904</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4812086802605804</v>
+        <v>0.4812090458799397</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5582457840330085</v>
+        <v>0.5582457985853087</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -5810,16 +5810,16 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.851059526098111</v>
+        <v>3.851062257943341</v>
       </c>
       <c r="P51" t="n">
-        <v>4.425622904874372</v>
+        <v>4.425623013431624</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.9284299964927997</v>
+        <v>0.9284302111968471</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01074432703134815</v>
+        <v>0.01074431091631254</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -5829,38 +5829,38 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>0.9295092822420135</v>
+        <v>0.9295097899543076</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.01569655784531013</v>
+        <v>0.01569650133491646</v>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>0.7965003248261033</v>
+        <v>0.7965002581684573</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.01440401834558218</v>
+        <v>0.01440402070464707</v>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="n">
-        <v>-0.8078403432370145</v>
+        <v>-0.8078417074611575</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.003372999102247724</v>
+        <v>0.003373000388212927</v>
       </c>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="n">
-        <v>0.8916714400390217</v>
+        <v>0.8916714729925945</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.01056733408254436</v>
+        <v>0.01056733245141099</v>
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="n">
-        <v>0.9956322801226107</v>
+        <v>0.9956322739637581</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.0005472399253436916</v>
+        <v>0.0005472403105589382</v>
       </c>
       <c r="AN51" t="inlineStr"/>
     </row>
@@ -5887,25 +5887,25 @@
         <v>28.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4153806106757402</v>
+        <v>0.4153806106021484</v>
       </c>
       <c r="G52" t="n">
         <v>0.1113895850737956</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3106906626687218</v>
+        <v>0.3106906628036006</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1579071580203451</v>
+        <v>0.1579071579734052</v>
       </c>
       <c r="J52" t="n">
-        <v>0.004631983561397277</v>
+        <v>0.004631983547050241</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5429836066241071</v>
+        <v>0.5429836102873031</v>
       </c>
       <c r="L52" t="n">
-        <v>0.5519809004860716</v>
+        <v>0.5519809006218619</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -5914,16 +5914,16 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.311963123218198</v>
+        <v>4.3119631505133</v>
       </c>
       <c r="P52" t="n">
-        <v>4.378988121467831</v>
+        <v>4.378988122480944</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.9652852496903884</v>
+        <v>0.9652852489118535</v>
       </c>
       <c r="R52" t="n">
-        <v>0.008997260360846616</v>
+        <v>0.008997260461854279</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
@@ -5933,38 +5933,38 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>0.9775778295623077</v>
+        <v>0.9775778307024698</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.006857003628598683</v>
+        <v>0.006857003452033116</v>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>0.9189528216211351</v>
+        <v>0.9189528149507483</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.002013919310586962</v>
+        <v>0.002013919393462274</v>
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="n">
-        <v>0.7873706895020927</v>
+        <v>0.7873706870413455</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.01655815742488062</v>
+        <v>0.01655815752584053</v>
       </c>
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="n">
-        <v>0.7108994128057953</v>
+        <v>0.710899385173644</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.008864422778274969</v>
+        <v>0.008864423224188109</v>
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="n">
-        <v>0.001044304216321068</v>
+        <v>0.001044365897988953</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.0009636035248012068</v>
+        <v>0.0009636034867096767</v>
       </c>
       <c r="AN52" t="inlineStr"/>
     </row>
@@ -5991,25 +5991,25 @@
         <v>26.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4510893860666219</v>
+        <v>0.4510893861537268</v>
       </c>
       <c r="G53" t="n">
         <v>0.1184553423359393</v>
       </c>
       <c r="H53" t="n">
-        <v>0.200863297038614</v>
+        <v>0.2008632968133135</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2264019040843809</v>
+        <v>0.2264019042000988</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00319007047444387</v>
+        <v>0.003190070496921492</v>
       </c>
       <c r="K53" t="n">
-        <v>0.4961096498617923</v>
+        <v>0.4961113824202693</v>
       </c>
       <c r="L53" t="n">
-        <v>0.5564428925727184</v>
+        <v>0.5564429890598448</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6018,16 +6018,16 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4.490422673838463</v>
+        <v>4.49042296350168</v>
       </c>
       <c r="P53" t="n">
-        <v>4.432275172228135</v>
+        <v>4.432275152726105</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.9857806244172354</v>
+        <v>0.9857806264083402</v>
       </c>
       <c r="R53" t="n">
-        <v>0.005126881192193562</v>
+        <v>0.005126880833651992</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -6037,38 +6037,38 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="n">
-        <v>0.9788109294893552</v>
+        <v>0.9788109137161028</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.008436266604643637</v>
+        <v>0.008436269748023925</v>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>0.7228101524293111</v>
+        <v>0.7228104658367653</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.005404659709356356</v>
+        <v>0.005404656653939402</v>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="n">
-        <v>0.9850331455528376</v>
+        <v>0.9850331555848526</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.003020391061388467</v>
+        <v>0.003020390046014981</v>
       </c>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="n">
-        <v>0.9819223089037094</v>
+        <v>0.9819223459084511</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.003915476017345877</v>
+        <v>0.003915472010666813</v>
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="n">
-        <v>0.8730747425828687</v>
+        <v>0.8730744897173892</v>
       </c>
       <c r="AM53" t="n">
-        <v>0.0001577791702849639</v>
+        <v>0.0001577793266854022</v>
       </c>
       <c r="AN53" t="inlineStr"/>
     </row>
@@ -6095,25 +6095,25 @@
         <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4286683890706328</v>
+        <v>0.4286683889482371</v>
       </c>
       <c r="G54" t="n">
         <v>0.1269841269841269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2576179527120835</v>
+        <v>0.2576179529315623</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1597790966902238</v>
+        <v>0.15977909662141</v>
       </c>
       <c r="J54" t="n">
-        <v>0.02695043454293275</v>
+        <v>0.02695043451466368</v>
       </c>
       <c r="K54" t="n">
-        <v>0.3258000977721075</v>
+        <v>0.3258004340263557</v>
       </c>
       <c r="L54" t="n">
-        <v>0.527541511323768</v>
+        <v>0.5275415652261125</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -6122,16 +6122,16 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>4.139890418693176</v>
+        <v>4.139890457854863</v>
       </c>
       <c r="P54" t="n">
-        <v>4.360447263399376</v>
+        <v>4.360447250697743</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.9441125306217791</v>
+        <v>0.9441125237522929</v>
       </c>
       <c r="R54" t="n">
-        <v>0.008584372139672728</v>
+        <v>0.008584372668376493</v>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
@@ -6141,38 +6141,38 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>0.9373580417392703</v>
+        <v>0.9373580630439386</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.0128950649015272</v>
+        <v>0.012895062699228</v>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>0.4217348810428259</v>
+        <v>0.4217350452838085</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.004385361528281823</v>
+        <v>0.004385360905508536</v>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="n">
-        <v>0.8209224712522627</v>
+        <v>0.8209223433199525</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.01254981010968369</v>
+        <v>0.01254981461463312</v>
       </c>
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="n">
-        <v>0.8511419103976374</v>
+        <v>0.8511419428842567</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.004943830368299336</v>
+        <v>0.004943829847060484</v>
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="n">
-        <v>0.8843393427070396</v>
+        <v>0.8843393738298425</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.001001967122203119</v>
+        <v>0.001001966985941971</v>
       </c>
       <c r="AN54" t="inlineStr"/>
     </row>
@@ -6199,25 +6199,25 @@
         <v>29</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4347068963260962</v>
+        <v>0.4347068963151978</v>
       </c>
       <c r="G55" t="n">
         <v>0.1094690749863163</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2837256736143648</v>
+        <v>0.2837256736186445</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1694315236798098</v>
+        <v>0.1694315237196296</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00266683139341308</v>
+        <v>0.002666831360211718</v>
       </c>
       <c r="K55" t="n">
-        <v>0.3243733482653745</v>
+        <v>0.3243715757543829</v>
       </c>
       <c r="L55" t="n">
-        <v>0.5195633213139152</v>
+        <v>0.519562772224521</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6226,16 +6226,16 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>4.37343702145688</v>
+        <v>4.373436424558091</v>
       </c>
       <c r="P55" t="n">
-        <v>4.410183567146585</v>
+        <v>4.410183599107658</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.9016826123858003</v>
+        <v>0.9016826106859919</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01264423070047798</v>
+        <v>0.01264423081125975</v>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
@@ -6245,38 +6245,38 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>0.8434473460713175</v>
+        <v>0.8434473491501111</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.01909922798992492</v>
+        <v>0.01909922779823855</v>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>0.1345516419215065</v>
+        <v>0.1345474263908323</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.004073262551423722</v>
+        <v>0.00407327247168191</v>
       </c>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="n">
-        <v>0.6267996862692629</v>
+        <v>0.6267996324584124</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.01956852920097032</v>
+        <v>0.01956853061640491</v>
       </c>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="n">
-        <v>0.8288765285861632</v>
+        <v>0.8288770891388388</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.005908393845408905</v>
+        <v>0.005908384175488231</v>
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="n">
-        <v>0.9091333760619739</v>
+        <v>0.9091336962774459</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.000417635593421625</v>
+        <v>0.0004176348574358707</v>
       </c>
       <c r="AN55" t="inlineStr"/>
     </row>
@@ -6303,25 +6303,25 @@
         <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3573142119608926</v>
+        <v>0.3573142119374196</v>
       </c>
       <c r="G56" t="n">
         <v>0.1595277977187525</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2647607177751945</v>
+        <v>0.2647607177672366</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1794591218770647</v>
+        <v>0.179459121882217</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03893815066809572</v>
+        <v>0.03893815069437438</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5097180810386136</v>
+        <v>0.5097180812285835</v>
       </c>
       <c r="L56" t="n">
-        <v>0.5518535577083454</v>
+        <v>0.5518535577063126</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -6330,16 +6330,16 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>4.063927352245716</v>
+        <v>4.063927353663189</v>
       </c>
       <c r="P56" t="n">
-        <v>4.378024103527062</v>
+        <v>4.378024103512052</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8290942444541722</v>
+        <v>0.8290942443754199</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01212977896087996</v>
+        <v>0.01212977896340412</v>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
@@ -6349,38 +6349,38 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0.7283256784225867</v>
+        <v>0.7283256773140883</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.01819792556061479</v>
+        <v>0.01819792558573751</v>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>-0.1642604336165421</v>
+        <v>-0.1642604344447396</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.009456969361349826</v>
+        <v>0.009456969364713437</v>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="n">
-        <v>0.6280877513406949</v>
+        <v>0.6280877531772295</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.01612351822136859</v>
+        <v>0.01612351819748031</v>
       </c>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="n">
-        <v>0.7483831336531044</v>
+        <v>0.7483831332446416</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.00729292864910951</v>
+        <v>0.007292928655823623</v>
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="n">
-        <v>0.915257761023231</v>
+        <v>0.9152577609598676</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.001379955025367335</v>
+        <v>0.00137995502558049</v>
       </c>
       <c r="AN56" t="inlineStr"/>
     </row>
@@ -6407,25 +6407,25 @@
         <v>13.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3569988198360919</v>
+        <v>0.3569988198034146</v>
       </c>
       <c r="G57" t="n">
         <v>0.2369106846718786</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1636235303975117</v>
+        <v>0.1636235302919157</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2180246773556286</v>
+        <v>0.2180246774233276</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02444228773888892</v>
+        <v>0.02444228780946331</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5362984060044483</v>
+        <v>0.5362984060841561</v>
       </c>
       <c r="L57" t="n">
-        <v>0.554455161301568</v>
+        <v>0.5544551612839508</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -6434,16 +6434,16 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4.26214400069415</v>
+        <v>4.262144001288224</v>
       </c>
       <c r="P57" t="n">
-        <v>4.397413072186263</v>
+        <v>4.397413072055139</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.9075211627563269</v>
+        <v>0.9075211626788839</v>
       </c>
       <c r="R57" t="n">
-        <v>0.009247306723752669</v>
+        <v>0.009247306725298221</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
@@ -6453,38 +6453,38 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
-        <v>0.817918593012726</v>
+        <v>0.8179185931687083</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.01615090791475431</v>
+        <v>0.01615090790159598</v>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>0.6169303172194858</v>
+        <v>0.6169303178994402</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.008922752914418243</v>
+        <v>0.008922752906499234</v>
       </c>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="n">
-        <v>0.7460658066096132</v>
+        <v>0.7460658037718496</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.007736042969368808</v>
+        <v>0.007736042997610403</v>
       </c>
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="n">
-        <v>0.9245547766948449</v>
+        <v>0.9245547762630314</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.00505468598589359</v>
+        <v>0.005054686009566027</v>
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="n">
-        <v>0.6597688663710393</v>
+        <v>0.6597688607359593</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.001303783315303731</v>
+        <v>0.00130378332796253</v>
       </c>
       <c r="AN57" t="inlineStr"/>
     </row>
@@ -6511,25 +6511,25 @@
         <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3897461385626112</v>
+        <v>0.3897461386008995</v>
       </c>
       <c r="G58" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2557628102080468</v>
+        <v>0.2557628103268892</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2061345128303654</v>
+        <v>0.2061345125957501</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02625641629885448</v>
+        <v>0.02625641637633904</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2359136518339272</v>
+        <v>0.2359135900857198</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5314496607071902</v>
+        <v>0.5314496450320229</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -6538,16 +6538,16 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>4.091754229257946</v>
+        <v>4.091754218681647</v>
       </c>
       <c r="P58" t="n">
-        <v>4.427388979875565</v>
+        <v>4.427388952360486</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.9753643174695377</v>
+        <v>0.9753643116901849</v>
       </c>
       <c r="R58" t="n">
-        <v>0.006600130964115387</v>
+        <v>0.006600131737551949</v>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
@@ -6557,38 +6557,38 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>0.9908778247480367</v>
+        <v>0.9908778204885443</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.005541755571874639</v>
+        <v>0.005541756867548949</v>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>0.954174277554766</v>
+        <v>0.9541743935797501</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.001970201701686497</v>
+        <v>0.001970199207533066</v>
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="n">
-        <v>0.97878329253977</v>
+        <v>0.9787832985253854</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.00559671269031568</v>
+        <v>0.005596711900891186</v>
       </c>
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="n">
-        <v>0.7700920248525112</v>
+        <v>0.7700919404925418</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.01230113677889452</v>
+        <v>0.01230113902838451</v>
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="n">
-        <v>0.9541800329657104</v>
+        <v>0.9541800326392943</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.0007581128957019003</v>
+        <v>0.0007581129016123601</v>
       </c>
       <c r="AN58" t="inlineStr"/>
     </row>
@@ -6615,25 +6615,25 @@
         <v>10.6506024096385</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4031657915982697</v>
+        <v>0.4031657917179133</v>
       </c>
       <c r="G59" t="n">
         <v>0.2980679451267702</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09858303468278869</v>
+        <v>0.098583034577217</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1793800069532604</v>
+        <v>0.1793800069472718</v>
       </c>
       <c r="J59" t="n">
-        <v>0.02080322163891103</v>
+        <v>0.02080322163082778</v>
       </c>
       <c r="K59" t="n">
-        <v>0.5293059348727757</v>
+        <v>0.529305935645196</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5537011020857625</v>
+        <v>0.553701101692763</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>4.210020762317669</v>
+        <v>4.210020768076263</v>
       </c>
       <c r="P59" t="n">
-        <v>4.391793516466226</v>
+        <v>4.39179351353965</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.7893019037545375</v>
+        <v>0.7893018896285579</v>
       </c>
       <c r="R59" t="n">
-        <v>0.01964749602167767</v>
+        <v>0.01964749668248941</v>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
@@ -6661,38 +6661,38 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>0.7511808006713493</v>
+        <v>0.7511807624920737</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.03127042221855022</v>
+        <v>0.03127042462895777</v>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
-        <v>0.456024180753672</v>
+        <v>0.4560241866266972</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.02279286721567782</v>
+        <v>0.02279286709263642</v>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="n">
-        <v>0.1390582692687956</v>
+        <v>0.1390582794964369</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.01076441605967704</v>
+        <v>0.01076441596643148</v>
       </c>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="n">
-        <v>-1.015799239317717</v>
+        <v>-1.015799154053648</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.01761129966795367</v>
+        <v>0.01761129929423078</v>
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="n">
-        <v>-0.662332675334125</v>
+        <v>-0.6623326364022384</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.00259535524947564</v>
+        <v>0.00259535522326054</v>
       </c>
       <c r="AN59" t="inlineStr"/>
     </row>
@@ -6719,25 +6719,25 @@
         <v>45.2784503631961</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6185024514073951</v>
+        <v>0.6185024514128479</v>
       </c>
       <c r="G60" t="n">
         <v>0.07011289364230544</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1901432799511997</v>
+        <v>0.1901432797896153</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1060804578008114</v>
+        <v>0.1060804579527164</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0151609171982884</v>
+        <v>0.015160917202515</v>
       </c>
       <c r="K60" t="n">
-        <v>0.520091897588902</v>
+        <v>0.5200918946229371</v>
       </c>
       <c r="L60" t="n">
-        <v>0.5419720878153651</v>
+        <v>0.5419720835506272</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -6746,16 +6746,16 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.141314459674549</v>
+        <v>4.141314437553916</v>
       </c>
       <c r="P60" t="n">
-        <v>4.304414026823678</v>
+        <v>4.304413995045782</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.8246015048840531</v>
+        <v>0.8246014103624506</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02604866526239791</v>
+        <v>0.02604867227997971</v>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
@@ -6765,38 +6765,38 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>0.34159354583436</v>
+        <v>0.3415931666269646</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.0568477079221997</v>
+        <v>0.05684772429543986</v>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>-1.724682159987728</v>
+        <v>-1.72468140026304</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.008748456186128822</v>
+        <v>0.00874845496646021</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="n">
-        <v>0.6533379756932023</v>
+        <v>0.6533377946428448</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.006493303028177932</v>
+        <v>0.00649330471258459</v>
       </c>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="n">
-        <v>-7.498498238228663</v>
+        <v>-7.498491217956332</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.006486444317226213</v>
+        <v>0.006486441684080717</v>
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="n">
-        <v>0.9388936035041684</v>
+        <v>0.9388935906796291</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.0004800875104764872</v>
+        <v>0.0004800875617407061</v>
       </c>
       <c r="AN60" t="inlineStr"/>
     </row>
@@ -6823,25 +6823,25 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G61" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4276854726398666</v>
+        <v>0.4276857654472169</v>
       </c>
       <c r="L61" t="n">
-        <v>0.5387062158005479</v>
+        <v>0.5387062430381778</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -6850,16 +6850,16 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>3.964762310542818</v>
+        <v>3.964763507400216</v>
       </c>
       <c r="P61" t="n">
-        <v>4.302246317661345</v>
+        <v>4.302246423450964</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.9764564161278908</v>
+        <v>0.9764567019849276</v>
       </c>
       <c r="R61" t="n">
-        <v>0.0109395948022426</v>
+        <v>0.01093952839001047</v>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
@@ -6871,38 +6871,38 @@
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
-        <v>0.9575418218156996</v>
+        <v>0.9575424149723462</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.02296450419028379</v>
+        <v>0.02296434377825885</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>0.09921825726618483</v>
+        <v>0.09921656208432961</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.005144863072379082</v>
+        <v>0.00514486785186138</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="n">
-        <v>0.6683998390589159</v>
+        <v>0.6683991603527266</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.005834495252819951</v>
+        <v>0.005834501234560592</v>
       </c>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="n">
-        <v>0.8976402994945234</v>
+        <v>0.8976405836019022</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.002557411000898167</v>
+        <v>0.002557407456222028</v>
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="n">
-        <v>0.3339938065814732</v>
+        <v>0.3339935467633507</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.00222315023235074</v>
+        <v>0.002223150649085405</v>
       </c>
       <c r="AN61" t="inlineStr"/>
     </row>
@@ -6929,25 +6929,25 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G62" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I62" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1560475317581405</v>
+        <v>0.1558892941267478</v>
       </c>
       <c r="L62" t="n">
-        <v>0.4542540445922373</v>
+        <v>0.4541252952197067</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -6956,16 +6956,16 @@
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>4.22633178824696</v>
+        <v>4.226186446895603</v>
       </c>
       <c r="P62" t="n">
-        <v>4.265401247070139</v>
+        <v>4.265347691290382</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.9902226006716003</v>
+        <v>0.9902244790951389</v>
       </c>
       <c r="R62" t="n">
-        <v>0.00652122888087008</v>
+        <v>0.00652060242524398</v>
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
@@ -6977,38 +6977,38 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>0.9866299560375427</v>
+        <v>0.986632312867296</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.01206056760800621</v>
+        <v>0.01205950456208336</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>-0.3328617033881316</v>
+        <v>-0.3337080455717636</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.00384335303761227</v>
+        <v>0.003844573066278858</v>
       </c>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="n">
-        <v>0.7850876997653191</v>
+        <v>0.7851880714620939</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.006206885096906208</v>
+        <v>0.006205435507578495</v>
       </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="n">
-        <v>0.948071503545309</v>
+        <v>0.9480975391055273</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.003383051443696128</v>
+        <v>0.003382203251597159</v>
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>0.8788222670363137</v>
+        <v>0.8788650195603253</v>
       </c>
       <c r="AM62" t="n">
-        <v>0.001743924205480003</v>
+        <v>0.001743616543922415</v>
       </c>
       <c r="AN62" t="inlineStr"/>
     </row>
@@ -7035,25 +7035,25 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G63" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I63" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K63" t="n">
-        <v>0.3712793451295304</v>
+        <v>0.371279416122849</v>
       </c>
       <c r="L63" t="n">
-        <v>0.52729018172343</v>
+        <v>0.527290164619862</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -7062,16 +7062,16 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>4.032785542367162</v>
+        <v>4.032786438210414</v>
       </c>
       <c r="P63" t="n">
-        <v>4.293305936567684</v>
+        <v>4.293305883020656</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9889576127993983</v>
+        <v>0.9889575851940843</v>
       </c>
       <c r="R63" t="n">
-        <v>0.007685741379523292</v>
+        <v>0.007685750986308491</v>
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
@@ -7083,38 +7083,38 @@
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>0.9780284592844997</v>
+        <v>0.978028399108542</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.01632187338921539</v>
+        <v>0.01632189574007112</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>0.7258897890726739</v>
+        <v>0.7258902690530082</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.002286162811083265</v>
+        <v>0.002286160797616172</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="n">
-        <v>0.9780994857142516</v>
+        <v>0.9780994316343975</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.001645855124601485</v>
+        <v>0.001645857158538429</v>
       </c>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
-        <v>0.7678883977110569</v>
+        <v>0.7678882402737268</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.004296650618390212</v>
+        <v>0.004296652082117013</v>
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="n">
-        <v>0.4016283054013692</v>
+        <v>0.4016286135028316</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.001786395044683362</v>
+        <v>0.001786394579288202</v>
       </c>
       <c r="AN63" t="inlineStr"/>
     </row>
@@ -7141,25 +7141,25 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G64" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2665008022242393</v>
+        <v>0.2664992806655571</v>
       </c>
       <c r="L64" t="n">
-        <v>0.5255162256578281</v>
+        <v>0.5255163364942647</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -7168,16 +7168,16 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.919470058378178</v>
+        <v>3.919452017702655</v>
       </c>
       <c r="P64" t="n">
-        <v>4.303284276620948</v>
+        <v>4.303284309736291</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.9782948641580993</v>
+        <v>0.9782948937772814</v>
       </c>
       <c r="R64" t="n">
-        <v>0.00987101664730056</v>
+        <v>0.009871009912688453</v>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
@@ -7189,38 +7189,38 @@
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>0.9657497827782375</v>
+        <v>0.9657498535433487</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.01954519404366117</v>
+        <v>0.01954517385334477</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>0.2942650832185683</v>
+        <v>0.2942655577836436</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.004536825970330232</v>
+        <v>0.004536824466850344</v>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="n">
-        <v>0.4937598639763084</v>
+        <v>0.4937589197201503</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.008657968206765608</v>
+        <v>0.008657976275266793</v>
       </c>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
-        <v>0.9731351093991819</v>
+        <v>0.9731351334509403</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.00236551452914697</v>
+        <v>0.002365513470043165</v>
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="n">
-        <v>0.8422841838162359</v>
+        <v>0.8422840507258107</v>
       </c>
       <c r="AM64" t="n">
-        <v>0.002244820624800383</v>
+        <v>0.002244821574603974</v>
       </c>
       <c r="AN64" t="inlineStr"/>
     </row>
@@ -7247,25 +7247,25 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G65" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I65" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K65" t="n">
-        <v>0.3705977767793169</v>
+        <v>0.3705978997527217</v>
       </c>
       <c r="L65" t="n">
-        <v>0.5335660846006467</v>
+        <v>0.53356600813042</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -7274,16 +7274,16 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.919437140445244</v>
+        <v>3.919438743173946</v>
       </c>
       <c r="P65" t="n">
-        <v>4.310184148305897</v>
+        <v>4.310183859100634</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.9777822818323934</v>
+        <v>0.9777820360131179</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01073649467768937</v>
+        <v>0.01073655407225609</v>
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
@@ -7295,38 +7295,38 @@
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="n">
-        <v>0.9627713869596259</v>
+        <v>0.9627708929798506</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.02205839104534131</v>
+        <v>0.02205853738906823</v>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>0.6674842826994962</v>
+        <v>0.6674853232030947</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.003904714556281373</v>
+        <v>0.003904708434965863</v>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="n">
-        <v>0.6715960039120876</v>
+        <v>0.6715964154032228</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.008066020964317635</v>
+        <v>0.008066015912686504</v>
       </c>
       <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="n">
-        <v>0.9093875573381727</v>
+        <v>0.909386846973226</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.002597147209296385</v>
+        <v>0.00259715739364753</v>
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="n">
-        <v>0.581132593361839</v>
+        <v>0.5811330415461431</v>
       </c>
       <c r="AM65" t="n">
-        <v>0.001849429209737506</v>
+        <v>0.00184942822052187</v>
       </c>
       <c r="AN65" t="inlineStr"/>
     </row>
@@ -7353,25 +7353,25 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G66" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K66" t="n">
-        <v>0.3123846531483918</v>
+        <v>0.3123839006204402</v>
       </c>
       <c r="L66" t="n">
-        <v>0.5296498294463413</v>
+        <v>0.5296498553261477</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -7380,16 +7380,16 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>4.0372004394865</v>
+        <v>4.037191967623349</v>
       </c>
       <c r="P66" t="n">
-        <v>4.306941228393627</v>
+        <v>4.306941317286697</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.9784700039257482</v>
+        <v>0.9784699522202083</v>
       </c>
       <c r="R66" t="n">
-        <v>0.009924657288851042</v>
+        <v>0.009924669206416154</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -7401,38 +7401,38 @@
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>0.9647740911636622</v>
+        <v>0.964773982210945</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.01975658735355412</v>
+        <v>0.01975661790778782</v>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>0.5424297723972302</v>
+        <v>0.5424300156313357</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.004169879700126315</v>
+        <v>0.004169878598692564</v>
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="n">
-        <v>0.6911480349487376</v>
+        <v>0.6911481061851881</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.008490864156873577</v>
+        <v>0.008490863174522873</v>
       </c>
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="n">
-        <v>0.9524169399192033</v>
+        <v>0.9524169402732606</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.003033819456986722</v>
+        <v>0.003033819445425627</v>
       </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="n">
-        <v>0.8578496290053969</v>
+        <v>0.8578495713306324</v>
       </c>
       <c r="AM66" t="n">
-        <v>0.002087054235492194</v>
+        <v>0.002087054660837078</v>
       </c>
       <c r="AN66" t="inlineStr"/>
     </row>
@@ -7459,25 +7459,25 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G67" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.5593936798993145</v>
+        <v>0.5593924454499485</v>
       </c>
       <c r="L67" t="n">
-        <v>0.5512003213762259</v>
+        <v>0.5512003233407264</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -7486,61 +7486,61 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>4.434199252443003</v>
+        <v>4.434190060020733</v>
       </c>
       <c r="P67" t="n">
-        <v>4.373177070109338</v>
+        <v>4.373177084612934</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.9015940609169077</v>
+        <v>0.9016107411643817</v>
       </c>
       <c r="R67" t="n">
-        <v>0.02268937459238491</v>
+        <v>0.02268745153658821</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
-        <v>0.7840874861795611</v>
+        <v>0.7840658789862538</v>
       </c>
       <c r="X67" t="n">
-        <v>0.0008077013323736372</v>
+        <v>0.0008077417462475488</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>0.7336078490036118</v>
+        <v>0.7336570859636553</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.05318264375510302</v>
+        <v>0.05317772867561557</v>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
-        <v>0.7404141677709583</v>
+        <v>0.7403882916276572</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.002791271922402073</v>
+        <v>0.002791411039301821</v>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="n">
-        <v>0.6497432520747137</v>
+        <v>0.6497410680316734</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.01298106405333017</v>
+        <v>0.01298110459202786</v>
       </c>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
-        <v>0.805658359473467</v>
+        <v>0.8056646826623068</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.009129706177855584</v>
+        <v>0.009129557614368953</v>
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="n">
-        <v>0.664722169751524</v>
+        <v>0.6646893654814032</v>
       </c>
       <c r="AM67" t="n">
-        <v>0.0001545317644025472</v>
+        <v>0.0001545393352139044</v>
       </c>
       <c r="AN67" t="inlineStr"/>
     </row>
@@ -7567,25 +7567,25 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G68" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.5709446758847706</v>
+        <v>0.5709446760465906</v>
       </c>
       <c r="L68" t="n">
-        <v>0.5513570310668608</v>
+        <v>0.5513570311596738</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -7594,61 +7594,61 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.520196890876156</v>
+        <v>4.520196892080668</v>
       </c>
       <c r="P68" t="n">
-        <v>4.374341291890712</v>
+        <v>4.374341292581766</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.7868225624667292</v>
+        <v>0.7868225481082818</v>
       </c>
       <c r="R68" t="n">
-        <v>0.03080013450233389</v>
+        <v>0.03080013553587546</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>0.5373268068139827</v>
+        <v>0.537326826243868</v>
       </c>
       <c r="X68" t="n">
-        <v>0.001112377307381705</v>
+        <v>0.001112377284024653</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>0.4243587182068744</v>
+        <v>0.4243586780517054</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.0738032038434403</v>
+        <v>0.07380320639485802</v>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
-        <v>0.517967293818874</v>
+        <v>0.5179673183798208</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.003705299664801253</v>
+        <v>0.003705299570403438</v>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="n">
-        <v>0.7400216559757031</v>
+        <v>0.7400216537798194</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.007497909433729451</v>
+        <v>0.007497909493016376</v>
       </c>
       <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="n">
-        <v>0.6598645649093471</v>
+        <v>0.6598645528047766</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.01315152390614106</v>
+        <v>0.01315152410800731</v>
       </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="n">
-        <v>0.07978784700122687</v>
+        <v>0.07978792074934393</v>
       </c>
       <c r="AM68" t="n">
-        <v>0.0008525565595529457</v>
+        <v>0.0008525565274278571</v>
       </c>
       <c r="AN68" t="inlineStr"/>
     </row>
@@ -7675,25 +7675,25 @@
         <v>51.72972972972973</v>
       </c>
       <c r="F69" t="n">
-        <v>0.387003570840844</v>
+        <v>0.3870035708733858</v>
       </c>
       <c r="G69" t="n">
         <v>0.06136902688626825</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3121616657195941</v>
+        <v>0.3121616658061397</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1933504308693656</v>
+        <v>0.1933504307114432</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04611530568392795</v>
+        <v>0.04611530572276303</v>
       </c>
       <c r="K69" t="n">
-        <v>0.4227647615340945</v>
+        <v>0.4227645132326192</v>
       </c>
       <c r="L69" t="n">
-        <v>0.5365480432054363</v>
+        <v>0.5365480105889356</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -7702,16 +7702,16 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>4.368894955962674</v>
+        <v>4.368895569985296</v>
       </c>
       <c r="P69" t="n">
-        <v>4.372337639764951</v>
+        <v>4.372337729774945</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.9678409253969988</v>
+        <v>0.9678409092095933</v>
       </c>
       <c r="R69" t="n">
-        <v>0.01051037782356906</v>
+        <v>0.01051038047005299</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
@@ -7721,38 +7721,38 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>0.9360477862573848</v>
+        <v>0.9360477223533291</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.01401007677178978</v>
+        <v>0.01401008377682736</v>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
-        <v>0.6619752013653453</v>
+        <v>0.6619755762764508</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.003692152831910198</v>
+        <v>0.003692150784383672</v>
       </c>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="n">
-        <v>0.8587090683356974</v>
+        <v>0.8587089801283747</v>
       </c>
       <c r="AG69" t="n">
-        <v>0.01522128501753176</v>
+        <v>0.01522128977187866</v>
       </c>
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
-        <v>0.8974250672104145</v>
+        <v>0.8974251246095596</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.009717595190113004</v>
+        <v>0.00971759246573972</v>
       </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="n">
-        <v>0.5714615671432348</v>
+        <v>0.5714614312617288</v>
       </c>
       <c r="AM69" t="n">
-        <v>0.004038166963040459</v>
+        <v>0.004038167607753719</v>
       </c>
       <c r="AN69" t="inlineStr"/>
     </row>
@@ -7779,25 +7779,25 @@
         <v>33.0828025477707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3260336956980185</v>
+        <v>0.3260336958414495</v>
       </c>
       <c r="G70" t="n">
         <v>0.09595931813875594</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3161491466910983</v>
+        <v>0.31614914647049</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2279586239396759</v>
+        <v>0.2279586239311767</v>
       </c>
       <c r="J70" t="n">
-        <v>0.03389921553245138</v>
+        <v>0.03389921561812766</v>
       </c>
       <c r="K70" t="n">
-        <v>0.5503708566416453</v>
+        <v>0.5503708593126074</v>
       </c>
       <c r="L70" t="n">
-        <v>0.5571388279955621</v>
+        <v>0.5571388295650735</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -7806,16 +7806,16 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>4.366998961487805</v>
+        <v>4.36699898138397</v>
       </c>
       <c r="P70" t="n">
-        <v>4.417406803997117</v>
+        <v>4.417406815686455</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.9577440876459358</v>
+        <v>0.9577440933429551</v>
       </c>
       <c r="R70" t="n">
-        <v>0.01008780000550043</v>
+        <v>0.01008779932543208</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
@@ -7825,38 +7825,38 @@
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>0.8854756377355057</v>
+        <v>0.8854756784958662</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.01511082379202798</v>
+        <v>0.01511082110804725</v>
       </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
-        <v>0.9253918248346422</v>
+        <v>0.9253918350395194</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.003168426386055833</v>
+        <v>0.003168426169367762</v>
       </c>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="n">
-        <v>0.9431770989989549</v>
+        <v>0.943177101382609</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.01082413293580442</v>
+        <v>0.01082413269763145</v>
       </c>
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="n">
-        <v>0.8105629049318468</v>
+        <v>0.8105628816400188</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.0121904795837367</v>
+        <v>0.0121904803383382</v>
       </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="n">
-        <v>0.7706955991884092</v>
+        <v>0.7706955697723902</v>
       </c>
       <c r="AM70" t="n">
-        <v>0.002161706969927251</v>
+        <v>0.002161707118333637</v>
       </c>
       <c r="AN70" t="inlineStr"/>
     </row>
@@ -7883,25 +7883,25 @@
         <v>47.07964601769911</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3936990724378037</v>
+        <v>0.3936990724969831</v>
       </c>
       <c r="G71" t="n">
         <v>0.06743048096431555</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2058669949880412</v>
+        <v>0.2058669949713333</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3043928180016056</v>
+        <v>0.3043928180135104</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02861063360823382</v>
+        <v>0.02861063355385755</v>
       </c>
       <c r="K71" t="n">
-        <v>0.5091634325943013</v>
+        <v>0.50916338686595</v>
       </c>
       <c r="L71" t="n">
-        <v>0.5591645399916279</v>
+        <v>0.5591645355667471</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>4.443210889445625</v>
+        <v>4.443210832107212</v>
       </c>
       <c r="P71" t="n">
-        <v>4.45157851663676</v>
+        <v>4.451578507678996</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.960905064904266</v>
+        <v>0.9609050661675627</v>
       </c>
       <c r="R71" t="n">
-        <v>0.01079606387328092</v>
+        <v>0.01079606369934772</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
@@ -7929,38 +7929,38 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>0.9409314163791648</v>
+        <v>0.9409314096066392</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.01446465051063864</v>
+        <v>0.01446465134402791</v>
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
-        <v>0.7624778062601361</v>
+        <v>0.7624778107653241</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.00431710829305459</v>
+        <v>0.004317108252112344</v>
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="n">
-        <v>0.9056837309667829</v>
+        <v>0.9056837305206771</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.009794850298019122</v>
+        <v>0.00979485031245589</v>
       </c>
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="n">
-        <v>0.8463330626188879</v>
+        <v>0.8463330882613026</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.01606674381958397</v>
+        <v>0.01606674248054115</v>
       </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="n">
-        <v>0.9454807641177289</v>
+        <v>0.9454807504139091</v>
       </c>
       <c r="AM71" t="n">
-        <v>0.000912188602309321</v>
+        <v>0.0009121887182378883</v>
       </c>
       <c r="AN71" t="inlineStr"/>
     </row>
@@ -7987,25 +7987,25 @@
         <v>37.36805555555556</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2796444532400447</v>
+        <v>0.279644453194911</v>
       </c>
       <c r="G72" t="n">
         <v>0.08495500039822655</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2106458171229023</v>
+        <v>0.2106458171994461</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3902452407206423</v>
+        <v>0.3902452407095023</v>
       </c>
       <c r="J72" t="n">
-        <v>0.03450948851818413</v>
+        <v>0.03450948849791399</v>
       </c>
       <c r="K72" t="n">
-        <v>0.5525686244778018</v>
+        <v>0.5525676405558657</v>
       </c>
       <c r="L72" t="n">
-        <v>0.5679527318392125</v>
+        <v>0.5679526872463373</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -8014,16 +8014,16 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>4.490464158932846</v>
+        <v>4.490463887273571</v>
       </c>
       <c r="P72" t="n">
-        <v>4.500406950239454</v>
+        <v>4.500406903774896</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.9585881834994068</v>
+        <v>0.9585882203031879</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01162095888323122</v>
+        <v>0.01162095371817092</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -8033,38 +8033,38 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>0.8574052485563871</v>
+        <v>0.8574051023779605</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.01577134025406268</v>
+        <v>0.01577134833602939</v>
       </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
-        <v>0.8481187305244917</v>
+        <v>0.848118247966413</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.004292743029630342</v>
+        <v>0.004292749849089353</v>
       </c>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="n">
-        <v>0.9509468533867654</v>
+        <v>0.9509470313176042</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.006940702485738673</v>
+        <v>0.006940689901183641</v>
       </c>
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
-        <v>0.8651300588873552</v>
+        <v>0.8651303373109237</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.01891746663331906</v>
+        <v>0.01891744710917793</v>
       </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="n">
-        <v>0.9025142005278294</v>
+        <v>0.9025142155873758</v>
       </c>
       <c r="AM72" t="n">
-        <v>0.001423627719109316</v>
+        <v>0.001423627606918923</v>
       </c>
       <c r="AN72" t="inlineStr"/>
     </row>
@@ -8091,25 +8091,25 @@
         <v>80.48333333333333</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4426967929782777</v>
+        <v>0.4426967930157429</v>
       </c>
       <c r="G73" t="n">
         <v>0.03944423078819433</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3881444762932012</v>
+        <v>0.388144476200794</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1098624187784432</v>
+        <v>0.1098624188419678</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01985208116188355</v>
+        <v>0.01985208115330091</v>
       </c>
       <c r="K73" t="n">
-        <v>0.5594245360474558</v>
+        <v>0.5594245356377607</v>
       </c>
       <c r="L73" t="n">
-        <v>0.5542545413407491</v>
+        <v>0.5542545411842409</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -8118,16 +8118,16 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.434429024992574</v>
+        <v>4.434429021941751</v>
       </c>
       <c r="P73" t="n">
-        <v>4.395925804706224</v>
+        <v>4.395925803540649</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9946561269747206</v>
+        <v>0.9946561277285454</v>
       </c>
       <c r="R73" t="n">
-        <v>0.004861610941357829</v>
+        <v>0.004861610598179521</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -8137,38 +8137,38 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>0.9546484981116624</v>
+        <v>0.9546484990535158</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.007311865610315094</v>
+        <v>0.007311865536529902</v>
       </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
-        <v>0.303953838942979</v>
+        <v>0.3039539153949712</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.001667765734048136</v>
+        <v>0.001667765642456497</v>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="n">
-        <v>0.9721215045196219</v>
+        <v>0.9721215196465306</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.00560206893016771</v>
+        <v>0.005602067405333839</v>
       </c>
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="n">
-        <v>0.8216023361476901</v>
+        <v>0.8216023260243521</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.005164272966801963</v>
+        <v>0.005164273122593451</v>
       </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="n">
-        <v>0.2548646921498328</v>
+        <v>0.2548646594986583</v>
       </c>
       <c r="AM73" t="n">
-        <v>0.001969414101880343</v>
+        <v>0.00196941414653197</v>
       </c>
       <c r="AN73" t="inlineStr"/>
     </row>
@@ -8195,25 +8195,25 @@
         <v>59.11538461538462</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2579745442485045</v>
+        <v>0.2579745444344787</v>
       </c>
       <c r="G74" t="n">
         <v>0.05370181037064575</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3841123147856094</v>
+        <v>0.384112314707</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2682526027331976</v>
+        <v>0.2682526026085332</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03595872786204279</v>
+        <v>0.0359587278793424</v>
       </c>
       <c r="K74" t="n">
-        <v>0.5539023206624197</v>
+        <v>0.5539023225854812</v>
       </c>
       <c r="L74" t="n">
-        <v>0.5600553689522942</v>
+        <v>0.5600553695589473</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8222,16 +8222,16 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>4.39330331686405</v>
+        <v>4.393303331187163</v>
       </c>
       <c r="P74" t="n">
-        <v>4.439125468698231</v>
+        <v>4.439125473216025</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.9676665625001474</v>
+        <v>0.967666563380972</v>
       </c>
       <c r="R74" t="n">
-        <v>0.008518072202447611</v>
+        <v>0.008518072085801734</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -8241,38 +8241,38 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>0.790650401322366</v>
+        <v>0.7906504162712987</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.01093148060661289</v>
+        <v>0.01093148022618082</v>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>0.8362110962657245</v>
+        <v>0.8362110746712291</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.001344899028102427</v>
+        <v>0.001344899116760492</v>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="n">
-        <v>0.8820519222157659</v>
+        <v>0.8820519234697812</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.01352325017015671</v>
+        <v>0.0135232500934289</v>
       </c>
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
-        <v>0.8658459154178477</v>
+        <v>0.8658459148292281</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.007405717519435522</v>
+        <v>0.007405717530499099</v>
       </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="n">
-        <v>0.730221247810467</v>
+        <v>0.7302212439451559</v>
       </c>
       <c r="AM74" t="n">
-        <v>0.001938762863191675</v>
+        <v>0.001938762877187819</v>
       </c>
       <c r="AN74" t="inlineStr"/>
     </row>
@@ -8299,25 +8299,25 @@
         <v>38.49019607843137</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3797999037751007</v>
+        <v>0.379799903884584</v>
       </c>
       <c r="G75" t="n">
         <v>0.0824782281735924</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2705342292388105</v>
+        <v>0.2705342288932795</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2132258416518971</v>
+        <v>0.2132258419102607</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05396179716059933</v>
+        <v>0.05396179713828334</v>
       </c>
       <c r="K75" t="n">
-        <v>0.5371232694513625</v>
+        <v>0.5371232677635055</v>
       </c>
       <c r="L75" t="n">
-        <v>0.5502296926302926</v>
+        <v>0.5502296938253242</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -8326,16 +8326,16 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>4.268291721388134</v>
+        <v>4.268291708808715</v>
       </c>
       <c r="P75" t="n">
-        <v>4.365943769511382</v>
+        <v>4.365943778412547</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.9676649476119463</v>
+        <v>0.9676649506922748</v>
       </c>
       <c r="R75" t="n">
-        <v>0.007101517478086479</v>
+        <v>0.007101517139413083</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -8345,38 +8345,38 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>0.8871496550952456</v>
+        <v>0.8871496705864591</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.01200392420158328</v>
+        <v>0.01200392338369892</v>
       </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
-        <v>0.8451492726607359</v>
+        <v>0.8451492312134663</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.002374419361649531</v>
+        <v>0.002374419679417469</v>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="n">
-        <v>0.9222494765015478</v>
+        <v>0.9222494813337405</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.007318194732568614</v>
+        <v>0.007318194489686056</v>
       </c>
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
-        <v>0.8654124041024618</v>
+        <v>0.8654124112991015</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.006958858806779673</v>
+        <v>0.006958858634519037</v>
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="n">
-        <v>0.9882558302454952</v>
+        <v>0.9882558295223647</v>
       </c>
       <c r="AM75" t="n">
-        <v>0.0006663324087990279</v>
+        <v>0.000666332429856609</v>
       </c>
       <c r="AN75" t="inlineStr"/>
     </row>
@@ -8403,25 +8403,25 @@
         <v>67.76923076923077</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3107335005383793</v>
+        <v>0.3107335004737291</v>
       </c>
       <c r="G76" t="n">
         <v>0.04684431472172675</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5076173756922413</v>
+        <v>0.5076173757282579</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1034441405229936</v>
+        <v>0.1034441405920671</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03136066852465918</v>
+        <v>0.03136066848421915</v>
       </c>
       <c r="K76" t="n">
-        <v>0.543770931818184</v>
+        <v>0.5437709213996799</v>
       </c>
       <c r="L76" t="n">
-        <v>0.5537060846224899</v>
+        <v>0.5537060836310214</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -8430,16 +8430,16 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>4.439776253946184</v>
+        <v>4.439776240423371</v>
       </c>
       <c r="P76" t="n">
-        <v>4.395647657598982</v>
+        <v>4.395647653585991</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.9927073085664859</v>
+        <v>0.9927073070891497</v>
       </c>
       <c r="R76" t="n">
-        <v>0.005358634836562376</v>
+        <v>0.005358635379282317</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -8449,38 +8449,38 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>0.9143295704973174</v>
+        <v>0.9143295718087385</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.008327531153341478</v>
+        <v>0.008327531085225956</v>
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
-        <v>0.9189787060359157</v>
+        <v>0.9189786968174182</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.0007847750562913786</v>
+        <v>0.0007847751009367207</v>
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="n">
-        <v>0.9597230179488534</v>
+        <v>0.9597230008340168</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.00847205966732008</v>
+        <v>0.008472061470199948</v>
       </c>
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
-        <v>0.9883601661096005</v>
+        <v>0.9883601699493264</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.0009067580050309622</v>
+        <v>0.0009067578561155009</v>
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="n">
-        <v>0.6879495991187494</v>
+        <v>0.687949637439905</v>
       </c>
       <c r="AM76" t="n">
-        <v>0.001006570649746</v>
+        <v>0.001006570584485869</v>
       </c>
       <c r="AN76" t="inlineStr"/>
     </row>
@@ -8507,25 +8507,25 @@
         <v>84.83333333333333</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2190992506065154</v>
+        <v>0.2190992505888929</v>
       </c>
       <c r="G77" t="n">
         <v>0.03742164842361306</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4560940070375605</v>
+        <v>0.4560940072232207</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2593330805653106</v>
+        <v>0.2593330804892675</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02805201336700053</v>
+        <v>0.02805201327500588</v>
       </c>
       <c r="K77" t="n">
-        <v>0.4954473192373093</v>
+        <v>0.4954568924422989</v>
       </c>
       <c r="L77" t="n">
-        <v>0.5482686032782675</v>
+        <v>0.5482694569371784</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -8534,16 +8534,16 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4.299272883877356</v>
+        <v>4.299271167020737</v>
       </c>
       <c r="P77" t="n">
-        <v>4.371525967068971</v>
+        <v>4.371525007247327</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.9767796259190831</v>
+        <v>0.9767792123209238</v>
       </c>
       <c r="R77" t="n">
-        <v>0.009137821119754757</v>
+        <v>0.009137902501720264</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -8553,38 +8553,38 @@
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>0.8215885909469113</v>
+        <v>0.8215869946708054</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.007695584440325635</v>
+        <v>0.007695618870017804</v>
       </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
-        <v>-3.620114111636158</v>
+        <v>-3.620030945062835</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.00210199442831366</v>
+        <v>0.002101975509250597</v>
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="n">
-        <v>0.9072882482877223</v>
+        <v>0.9072843939923476</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.0131994654869828</v>
+        <v>0.01319973985954427</v>
       </c>
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
-        <v>0.1970902304960034</v>
+        <v>0.1970914089068819</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.01338130735097165</v>
+        <v>0.01338129755901353</v>
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="n">
-        <v>0.8883987431838454</v>
+        <v>0.8883977621673624</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.0007570984514043576</v>
+        <v>0.0007571017752990018</v>
       </c>
       <c r="AN77" t="inlineStr"/>
     </row>
@@ -8611,25 +8611,25 @@
         <v>194.7286349979082</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1878797147510616</v>
+        <v>0.1878797146293589</v>
       </c>
       <c r="G78" t="n">
         <v>0.01630270337301587</v>
       </c>
       <c r="H78" t="n">
-        <v>0.486383629371598</v>
+        <v>0.48638362926571</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2989072313345766</v>
+        <v>0.2989072315377535</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01052672116974796</v>
+        <v>0.01052672119416169</v>
       </c>
       <c r="K78" t="n">
-        <v>0.4805966135072757</v>
+        <v>0.4805951846614072</v>
       </c>
       <c r="L78" t="n">
-        <v>0.5547396320628748</v>
+        <v>0.5547397125695298</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -8638,16 +8638,16 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>4.450858392300603</v>
+        <v>4.450860975036541</v>
       </c>
       <c r="P78" t="n">
-        <v>4.449312526961258</v>
+        <v>4.449314910951012</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.9825247110262895</v>
+        <v>0.9825248774199156</v>
       </c>
       <c r="R78" t="n">
-        <v>0.009599400135841075</v>
+        <v>0.00959935443598238</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -8657,38 +8657,38 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="n">
-        <v>0.3531126832467799</v>
+        <v>0.3531127504094392</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.009750179042274446</v>
+        <v>0.009750178542346192</v>
       </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
-        <v>0.1737835108794157</v>
+        <v>0.17376326994584</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.001063197235471501</v>
+        <v>0.001063210258676136</v>
       </c>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="n">
-        <v>0.8835301692370344</v>
+        <v>0.8835329598920616</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.01403465959329246</v>
+        <v>0.01403449146929249</v>
       </c>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
-        <v>-0.4823378456373797</v>
+        <v>-0.4823408094788961</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.01282659993310616</v>
+        <v>0.01282661282052</v>
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="n">
-        <v>-0.4003650099827274</v>
+        <v>-0.4003575477308459</v>
       </c>
       <c r="AM78" t="n">
-        <v>0.001747197578538527</v>
+        <v>0.001747192899229735</v>
       </c>
       <c r="AN78" t="inlineStr"/>
     </row>
@@ -8709,31 +8709,31 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E79" t="n">
         <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5078749311749362</v>
+        <v>0.507874931382013</v>
       </c>
       <c r="G79" t="n">
         <v>0.06886340942740074</v>
       </c>
       <c r="H79" t="n">
-        <v>0.224536369038535</v>
+        <v>0.2245363687099741</v>
       </c>
       <c r="I79" t="n">
-        <v>0.198725290359128</v>
+        <v>0.1987252904806123</v>
       </c>
       <c r="J79" t="n">
-        <v>3.234988232153624e-17</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.5610550899029443</v>
+        <v>0.5610551126721091</v>
       </c>
       <c r="L79" t="n">
-        <v>0.5628967104249973</v>
+        <v>0.5628959950745231</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -8742,58 +8742,58 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.446570697558703</v>
+        <v>4.446570867100849</v>
       </c>
       <c r="P79" t="n">
-        <v>4.460283018455883</v>
+        <v>4.460277692209527</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.982243384299494</v>
+        <v>0.9822434255416213</v>
       </c>
       <c r="R79" t="n">
-        <v>0.01960156198295226</v>
+        <v>0.01960153921930902</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
-        <v>0.9236410073665533</v>
+        <v>0.9236411507157651</v>
       </c>
       <c r="U79" t="n">
-        <v>0.04292100560411066</v>
+        <v>0.04292096531615636</v>
       </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="n">
-        <v>0.6981942464365025</v>
+        <v>0.6981936820282105</v>
       </c>
       <c r="X79" t="n">
-        <v>0.001546153495189306</v>
+        <v>0.001546154940922919</v>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>0.9839019855367579</v>
+        <v>0.9839022337717617</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.009915735517281758</v>
+        <v>0.009915659066030489</v>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
-        <v>0.874554951078451</v>
+        <v>0.8745544885032041</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.002676926985810397</v>
+        <v>0.002676931921354011</v>
       </c>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="n">
-        <v>0.988746861923252</v>
+        <v>0.9887469092312274</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.003403543318451284</v>
+        <v>0.003403536166916018</v>
       </c>
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
-        <v>0.895514667962212</v>
+        <v>0.895514590463224</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.008637824505324111</v>
+        <v>0.008637827698550413</v>
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
@@ -8817,31 +8817,31 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E80" t="n">
         <v>45.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3936300671811785</v>
+        <v>0.3936300668840204</v>
       </c>
       <c r="G80" t="n">
         <v>0.07039031429275332</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3139495076888332</v>
+        <v>0.3139495080876725</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2220301108372348</v>
+        <v>0.2220301107355537</v>
       </c>
       <c r="J80" t="n">
-        <v>7.592549229303372e-17</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.5606777633938705</v>
+        <v>0.560678124195241</v>
       </c>
       <c r="L80" t="n">
-        <v>0.5620907024490294</v>
+        <v>0.5620906741832195</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -8850,58 +8850,58 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.54003655508906</v>
+        <v>4.540036489764575</v>
       </c>
       <c r="P80" t="n">
-        <v>4.456206201223724</v>
+        <v>4.456205935890593</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.9956428303795127</v>
+        <v>0.9956428202948515</v>
       </c>
       <c r="R80" t="n">
-        <v>0.009123521339572144</v>
+        <v>0.009123531897703208</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="n">
-        <v>0.9860021967035142</v>
+        <v>0.9860021416742978</v>
       </c>
       <c r="U80" t="n">
-        <v>0.01878773082974619</v>
+        <v>0.01878776775957966</v>
       </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="n">
-        <v>0.9828196059631479</v>
+        <v>0.9828194854432936</v>
       </c>
       <c r="X80" t="n">
-        <v>0.0003506142104155993</v>
+        <v>0.0003506154401865636</v>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>0.9869570965409913</v>
+        <v>0.9869571923673971</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.00733242378844812</v>
+        <v>0.007332396843379995</v>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>0.9847105974336611</v>
+        <v>0.9847104964303053</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.001028816237539852</v>
+        <v>0.001028819635766842</v>
       </c>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="n">
-        <v>0.9892340751087918</v>
+        <v>0.9892340685026662</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.005503516828303766</v>
+        <v>0.005503518528840247</v>
       </c>
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
-        <v>0.9864324608827842</v>
+        <v>0.9864325670320475</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.003816067557802077</v>
+        <v>0.003816052626355827</v>
       </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
@@ -8925,31 +8925,31 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E81" t="n">
         <v>53.2</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3868686426861032</v>
+        <v>0.386868642759827</v>
       </c>
       <c r="G81" t="n">
         <v>0.05967299200381906</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2367160880230922</v>
+        <v>0.2367160880153139</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3167422772869857</v>
+        <v>0.3167422772210401</v>
       </c>
       <c r="J81" t="n">
-        <v>9.901399624920571e-18</v>
+        <v>1.098340305577317e-17</v>
       </c>
       <c r="K81" t="n">
-        <v>0.4048865563859553</v>
+        <v>0.4048866820430508</v>
       </c>
       <c r="L81" t="n">
-        <v>0.5485342861325764</v>
+        <v>0.5485344238977007</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -8958,54 +8958,54 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>4.610890896156159</v>
+        <v>4.610890901594733</v>
       </c>
       <c r="P81" t="n">
-        <v>4.50798211336803</v>
+        <v>4.507982990503063</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.9935903263366648</v>
+        <v>0.9935903435422746</v>
       </c>
       <c r="R81" t="n">
-        <v>0.01088013624163685</v>
+        <v>0.0108801216388719</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="n">
-        <v>0.9808214000644143</v>
+        <v>0.9808214685210002</v>
       </c>
       <c r="U81" t="n">
-        <v>0.02075371822057495</v>
+        <v>0.0207536811811152</v>
       </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>0.984272054509954</v>
+        <v>0.9842720617327367</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.008265365640124717</v>
+        <v>0.008265363743602795</v>
       </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
-        <v>0.9586624166745832</v>
+        <v>0.9586623204623383</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.001234603714788191</v>
+        <v>0.001234605151542788</v>
       </c>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="n">
-        <v>0.9727833946089174</v>
+        <v>0.9727833989760714</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.005292730945256697</v>
+        <v>0.005292730523762982</v>
       </c>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
-        <v>0.9730921609198954</v>
+        <v>0.9730921690136298</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.007957165754681318</v>
+        <v>0.007957164553056322</v>
       </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
@@ -9029,31 +9029,31 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E82" t="n">
         <v>57.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3730456209331519</v>
+        <v>0.3730456210575596</v>
       </c>
       <c r="G82" t="n">
         <v>0.05530667551573475</v>
       </c>
       <c r="H82" t="n">
-        <v>0.261472183194441</v>
+        <v>0.2614721829646628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3101755203566725</v>
+        <v>0.3101755204620427</v>
       </c>
       <c r="J82" t="n">
-        <v>1.336850539002381e-17</v>
+        <v>8.893357462748227e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2917254962962554</v>
+        <v>0.291725558480019</v>
       </c>
       <c r="L82" t="n">
-        <v>0.5166499751550074</v>
+        <v>0.5166500077782856</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -9062,54 +9062,54 @@
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>4.60546490597388</v>
+        <v>4.60546498201934</v>
       </c>
       <c r="P82" t="n">
-        <v>4.601134779146905</v>
+        <v>4.601134788351012</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.9806319072772055</v>
+        <v>0.9806319017082801</v>
       </c>
       <c r="R82" t="n">
-        <v>0.01877364021631047</v>
+        <v>0.0187736429155853</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="n">
-        <v>0.9507780796374334</v>
+        <v>0.9507780598097291</v>
       </c>
       <c r="U82" t="n">
-        <v>0.03463819251382697</v>
+        <v>0.03463819949035051</v>
       </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>0.9385329377813838</v>
+        <v>0.9385329377749264</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.01660060355951193</v>
+        <v>0.01660060356800095</v>
       </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
-        <v>-0.4500396261437978</v>
+        <v>-0.4500394134404742</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.003534225036395271</v>
+        <v>0.003534224777181169</v>
       </c>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="n">
-        <v>0.7940999877192783</v>
+        <v>0.7940999777660038</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.01632480351941912</v>
+        <v>0.01632480389138711</v>
       </c>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
-        <v>0.9971798253213455</v>
+        <v>0.997179820720474</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.002805968484642784</v>
+        <v>0.002805970774330623</v>
       </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
@@ -9133,29 +9133,29 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>0.3465778704093958</v>
+        <v>0.3465778699121797</v>
       </c>
       <c r="G83" t="n">
-        <v>0.07437667461883628</v>
+        <v>0.07437667876585422</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2955634795127128</v>
+        <v>0.2955634788718243</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2811992414815186</v>
+        <v>0.2811992393986867</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002282733977536599</v>
+        <v>0.002282733051455125</v>
       </c>
       <c r="K83" t="n">
-        <v>0.5433397409012656</v>
+        <v>0.5433397459150067</v>
       </c>
       <c r="L83" t="n">
-        <v>0.5678007693909581</v>
+        <v>0.5678018445914279</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -9164,54 +9164,54 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4.643199327406445</v>
+        <v>4.643205446022499</v>
       </c>
       <c r="P83" t="n">
-        <v>4.506586517990205</v>
+        <v>4.506594746161333</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.9773604326208327</v>
+        <v>0.9773605788826856</v>
       </c>
       <c r="R83" t="n">
-        <v>0.01801427710008432</v>
+        <v>0.01801421889907159</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="n">
-        <v>0.9288854542269736</v>
+        <v>0.9288861684070717</v>
       </c>
       <c r="U83" t="n">
-        <v>0.0345611040369481</v>
+        <v>0.03456093049358663</v>
       </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>0.955749412226038</v>
+        <v>0.9557491540765531</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.01014368153048852</v>
+        <v>0.01014371109285321</v>
       </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
-        <v>0.6714075996782407</v>
+        <v>0.6714080092555899</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.006406783260828276</v>
+        <v>0.006406779444677907</v>
       </c>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="n">
-        <v>0.9248154943371998</v>
+        <v>0.9248153354903039</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.01052582334709004</v>
+        <v>0.01052583442623835</v>
       </c>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
-        <v>0.8752597591225428</v>
+        <v>0.8752592327957434</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.01316688577694108</v>
+        <v>0.01316691338846006</v>
       </c>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
@@ -9235,29 +9235,29 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.4410213099976569</v>
+        <v>0.4410213107040933</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0196358885772423</v>
+        <v>0.01963588269307707</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3091324863805823</v>
+        <v>0.3091324872855457</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2286307167377633</v>
+        <v>0.2286307196912758</v>
       </c>
       <c r="J84" t="n">
-        <v>0.001579598306755124</v>
+        <v>0.001579599626008144</v>
       </c>
       <c r="K84" t="n">
-        <v>0.3162631075751625</v>
+        <v>0.3162642480996137</v>
       </c>
       <c r="L84" t="n">
-        <v>0.5351320396311876</v>
+        <v>0.5351320833481786</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -9266,54 +9266,54 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>4.586521951223069</v>
+        <v>4.586544988422995</v>
       </c>
       <c r="P84" t="n">
-        <v>4.464050665003252</v>
+        <v>4.46405273450526</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.9983855038885692</v>
+        <v>0.9983855817879242</v>
       </c>
       <c r="R84" t="n">
-        <v>0.004718557440247502</v>
+        <v>0.004718443610154019</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="n">
-        <v>0.999198213570286</v>
+        <v>0.9991985532886724</v>
       </c>
       <c r="U84" t="n">
-        <v>0.003787150114489743</v>
+        <v>0.003786347718248776</v>
       </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>0.9902632093078262</v>
+        <v>0.9902631014202872</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.00673192859624555</v>
+        <v>0.006731965905677156</v>
       </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
-        <v>0.9644759828324329</v>
+        <v>0.9644759249253931</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.001706410563302213</v>
+        <v>0.001706412173800912</v>
       </c>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="n">
-        <v>0.9715663539084161</v>
+        <v>0.9715662645993951</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.006949577205247874</v>
+        <v>0.00694958815068929</v>
       </c>
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
-        <v>0.9995623387168208</v>
+        <v>0.9995622944807361</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.0006738639534036706</v>
+        <v>0.0006738980199052064</v>
       </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -9337,29 +9337,31 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>46.1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0.5131512316840431</v>
+        <v>0.510053670891675</v>
       </c>
       <c r="G85" t="n">
-        <v>6.514458245503142e-16</v>
+        <v>0.06886340942740074</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2632803536988662</v>
+        <v>0.2213241491814443</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2235684146170903</v>
+        <v>0.19975877049948</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-17</v>
       </c>
       <c r="K85" t="n">
-        <v>0.4976135263187853</v>
+        <v>0.4915819063210994</v>
       </c>
       <c r="L85" t="n">
-        <v>0.5644886621821832</v>
+        <v>0.5543935767155622</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -9368,54 +9370,54 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>4.548143428306743</v>
+        <v>4.449872865454893</v>
       </c>
       <c r="P85" t="n">
-        <v>4.489765718580981</v>
+        <v>4.420908493294408</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.9938663389452655</v>
+        <v>0.994416555305362</v>
       </c>
       <c r="R85" t="n">
-        <v>0.009787824069591307</v>
+        <v>0.009452752164532667</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="n">
-        <v>0.9810790972934864</v>
+        <v>0.9828197952007199</v>
       </c>
       <c r="U85" t="n">
-        <v>0.01765928863517425</v>
+        <v>0.01849902225010328</v>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="n">
-        <v>0.9883479579565141</v>
+        <v>0.9947920744169905</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.008318493263601066</v>
+        <v>0.00586962338991321</v>
       </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
-        <v>0.7560744652676666</v>
+        <v>0.8335521849633003</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.007717845228511201</v>
+        <v>0.003249398060129326</v>
       </c>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="n">
-        <v>0.9688679758640638</v>
+        <v>0.9528315610324792</v>
       </c>
       <c r="AG85" t="n">
-        <v>0.005698785702661338</v>
+        <v>0.006678997786682209</v>
       </c>
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="n">
-        <v>0.9927357984343882</v>
+        <v>0.9771285539267466</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.00243277647005917</v>
+        <v>0.003865063425543562</v>
       </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
@@ -9439,29 +9441,31 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>21</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>45.1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0.3947553823403973</v>
+        <v>0.3945200239537214</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0245670665763035</v>
+        <v>0.07039031429275332</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3466305638791009</v>
+        <v>0.3115441195160394</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2327646937884924</v>
+        <v>0.2235455422374857</v>
       </c>
       <c r="J86" t="n">
-        <v>0.001282293415705915</v>
+        <v>4.155543639229597e-17</v>
       </c>
       <c r="K86" t="n">
-        <v>0.5001855836882525</v>
+        <v>0.4578443045975882</v>
       </c>
       <c r="L86" t="n">
-        <v>0.5639737205055934</v>
+        <v>0.5537295607223878</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -9470,54 +9474,54 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4.655189285584574</v>
+        <v>4.558363897467068</v>
       </c>
       <c r="P86" t="n">
-        <v>4.489666769931012</v>
+        <v>4.457584569676453</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.9959748287961132</v>
+        <v>0.9927940070248661</v>
       </c>
       <c r="R86" t="n">
-        <v>0.007566815146635277</v>
+        <v>0.01055843976025405</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="n">
-        <v>0.9927018621214131</v>
+        <v>0.9822539071308791</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01187478003392466</v>
+        <v>0.02071770441667875</v>
       </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
-        <v>0.996496038256767</v>
+        <v>0.9899434735282594</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.003443241342889964</v>
+        <v>0.006377470309602051</v>
       </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
-        <v>0.6186588172610236</v>
+        <v>0.9404405402620295</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.009243450533327643</v>
+        <v>0.002051339386779324</v>
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="n">
-        <v>0.9904405870625187</v>
+        <v>0.9723496473447527</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.004998724419040988</v>
+        <v>0.008692853305918154</v>
       </c>
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
-        <v>0.978234866820092</v>
+        <v>0.9928809149686321</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.004794634703256448</v>
+        <v>0.002781034902671733</v>
       </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
@@ -9541,29 +9545,31 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57.4</v>
+      </c>
       <c r="F87" t="n">
-        <v>0.3717923415656336</v>
+        <v>0.3694757755244492</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.05530667551573475</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3014084132402625</v>
+        <v>0.2674527900009642</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3267992451941039</v>
+        <v>0.3077647589588519</v>
       </c>
       <c r="J87" t="n">
-        <v>1.327388309752159e-16</v>
+        <v>2.355429219724758e-17</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1801165461460996</v>
+        <v>0.2964562122809249</v>
       </c>
       <c r="L87" t="n">
-        <v>0.5035595819689067</v>
+        <v>0.5256607831125155</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -9572,54 +9578,54 @@
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>4.683999502138008</v>
+        <v>4.607564071222449</v>
       </c>
       <c r="P87" t="n">
-        <v>4.634575928036571</v>
+        <v>4.600604993107503</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9840376906873116</v>
+        <v>0.9782064236372134</v>
       </c>
       <c r="R87" t="n">
-        <v>0.01416368685130138</v>
+        <v>0.01974169278427642</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="n">
-        <v>0.966041525995557</v>
+        <v>0.9504201105023863</v>
       </c>
       <c r="U87" t="n">
-        <v>0.02389429756705195</v>
+        <v>0.0367285899773318</v>
       </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="n">
-        <v>0.948935077828046</v>
+        <v>0.9441713466259984</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.01262993268470194</v>
+        <v>0.01620729092505623</v>
       </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
-        <v>0.8831468287147135</v>
+        <v>-0.3521846706434006</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.004006886792308986</v>
+        <v>0.004549108718279842</v>
       </c>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="n">
-        <v>0.8090116094486198</v>
+        <v>0.8092437820839041</v>
       </c>
       <c r="AG87" t="n">
-        <v>0.01544088859105175</v>
+        <v>0.01745318385558823</v>
       </c>
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="n">
-        <v>0.9928407063740644</v>
+        <v>0.9960757735473821</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.00425691061898865</v>
+        <v>0.00342031464396118</v>
       </c>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
@@ -9643,29 +9649,31 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>21</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E88" t="n">
+        <v>53.2</v>
+      </c>
       <c r="F88" t="n">
-        <v>0.3917057203335357</v>
+        <v>0.3890440313612025</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.05967299200381906</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2685425476164555</v>
+        <v>0.2320759063377122</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3397517320500086</v>
+        <v>0.3192070702972664</v>
       </c>
       <c r="J88" t="n">
-        <v>1.912261794240524e-16</v>
+        <v>2.419504177564497e-17</v>
       </c>
       <c r="K88" t="n">
-        <v>0.1739893793974186</v>
+        <v>0.3754603734848492</v>
       </c>
       <c r="L88" t="n">
-        <v>0.5289535724632448</v>
+        <v>0.5429037500037664</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -9674,54 +9682,54 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>4.663409450690607</v>
+        <v>4.61250856617769</v>
       </c>
       <c r="P88" t="n">
-        <v>4.538878988034735</v>
+        <v>4.527420856876226</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.9926910668379216</v>
+        <v>0.9921067024902752</v>
       </c>
       <c r="R88" t="n">
-        <v>0.01002343689410575</v>
+        <v>0.01195282849207868</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="n">
-        <v>0.9794723805860036</v>
+        <v>0.9783626250856046</v>
       </c>
       <c r="U88" t="n">
-        <v>0.01805779057204282</v>
+        <v>0.02285537092012653</v>
       </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="n">
-        <v>0.9829718696440537</v>
+        <v>0.980614447883207</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.007383240839219295</v>
+        <v>0.009471107416012002</v>
       </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
-        <v>0.06882594369813955</v>
+        <v>0.9693129037068263</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.006019342886717594</v>
+        <v>0.001073697470420165</v>
       </c>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="n">
-        <v>0.9852304917887408</v>
+        <v>0.9733192853854589</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.003622365251437063</v>
+        <v>0.005343688648582446</v>
       </c>
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
-        <v>0.965103940150055</v>
+        <v>0.9717896685175474</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.008508605726805693</v>
+        <v>0.008518970277683859</v>
       </c>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
@@ -9745,29 +9753,29 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>0.468689526729295</v>
+        <v>0.4686895267262085</v>
       </c>
       <c r="G89" t="n">
-        <v>3.650881409255485e-16</v>
+        <v>2.428629807026475e-16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1956707823068736</v>
+        <v>0.1956707823126708</v>
       </c>
       <c r="I89" t="n">
-        <v>0.335639690963831</v>
+        <v>0.3356396909611205</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.2744023045987236</v>
+        <v>0.2736747903302026</v>
       </c>
       <c r="L89" t="n">
-        <v>0.5396384876006752</v>
+        <v>0.539546977620506</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -9776,54 +9784,54 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>4.565818894645068</v>
+        <v>4.565354349996714</v>
       </c>
       <c r="P89" t="n">
-        <v>4.509829245498081</v>
+        <v>4.510407876013224</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.9977408577930305</v>
+        <v>0.997771819295595</v>
       </c>
       <c r="R89" t="n">
-        <v>0.005624743844317256</v>
+        <v>0.005586067370717596</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="n">
-        <v>0.9976048310363318</v>
+        <v>0.9977465044600746</v>
       </c>
       <c r="U89" t="n">
-        <v>0.006688220080037116</v>
+        <v>0.006487402279514408</v>
       </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
-        <v>0.9993522401326416</v>
+        <v>0.9992861492290028</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.001939570307149694</v>
+        <v>0.002036114631911141</v>
       </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
-        <v>0.911902219092205</v>
+        <v>0.9118299703670227</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.002876454600932586</v>
+        <v>0.002877633576104106</v>
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="n">
-        <v>0.9950895817913649</v>
+        <v>0.9950745897343605</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.001702514800958786</v>
+        <v>0.001705111811118335</v>
       </c>
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="n">
-        <v>0.9524244462078089</v>
+        <v>0.9523865571976107</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.009925822285172442</v>
+        <v>0.009929773961863919</v>
       </c>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
@@ -9849,27 +9857,29 @@
       <c r="D90" t="n">
         <v>12.8</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>30.13605442176871</v>
+      </c>
       <c r="F90" t="n">
-        <v>0.6963378304438156</v>
+        <v>0.6739262842370797</v>
       </c>
       <c r="G90" t="n">
-        <v>0.06121827372612768</v>
+        <v>0.1053423626787058</v>
       </c>
       <c r="H90" t="n">
-        <v>0.04157121397092656</v>
+        <v>0.01105388716074765</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1708251520974169</v>
+        <v>0.1819763294359777</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03004752976171331</v>
+        <v>0.02770113648748916</v>
       </c>
       <c r="K90" t="n">
-        <v>0.2308034783562465</v>
+        <v>0.465001354613409</v>
       </c>
       <c r="L90" t="n">
-        <v>0.4969469837414318</v>
+        <v>0.5369633271432462</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -9878,54 +9888,56 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>4.504155908456531</v>
+        <v>4.563163426097284</v>
       </c>
       <c r="P90" t="n">
-        <v>4.287955954220703</v>
+        <v>4.298789843094707</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.9851109387161933</v>
+        <v>0.9841559811896458</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01613516631784879</v>
+        <v>0.01494486925749941</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
-        <v>0.9678592635158081</v>
+        <v>0.9648223071937911</v>
       </c>
       <c r="U90" t="n">
-        <v>0.0290344630605909</v>
+        <v>0.02731584043596161</v>
       </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
+      <c r="X90" t="n">
+        <v>5.204170427930421e-18</v>
+      </c>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
-        <v>0.9923571513487364</v>
+        <v>0.9900350041488793</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.01129360753018157</v>
+        <v>0.0108480405289519</v>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>0.7985577305534821</v>
+        <v>0.8675549453549001</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.005113545539360988</v>
+        <v>0.00565861148973051</v>
       </c>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="n">
-        <v>0.9869662170171315</v>
+        <v>0.9481419356268621</v>
       </c>
       <c r="AG90" t="n">
-        <v>0.0008695716598774213</v>
+        <v>0.0007518013448059933</v>
       </c>
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="n">
-        <v>0.9879562958590633</v>
+        <v>0.9843964533330956</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.003597167614908986</v>
+        <v>0.00384182805519061</v>
       </c>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>
